--- a/src/data/properties.xlsx
+++ b/src/data/properties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B802C4-04E2-48E2-A792-F7C5E817F335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D74E83-75FE-408F-B58F-BE308A074E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9150" yWindow="2730" windowWidth="26340" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11330" yWindow="2340" windowWidth="26980" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="204">
   <si>
     <t>status</t>
   </si>
@@ -585,14 +585,81 @@
     <t>https://res.cloudinary.com/qogrq7ve/image/upload/v1790284064/samples/ecommerce/analog-classic.jpg</t>
   </si>
   <si>
-    <t>Yes</t>
+    <t>https://images.unsplash.com/photo-1724100688250-44853bbada21?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwyN3x8aW50ZXJpb3IlMjBwaG90b3xlbnwwfHx8fDE3OTIxNzQzMzl8MA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1724100688254-4038b53a7567?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwyOHx8aW50ZXJpb3IlMjBwaG90b3xlbnwwfHx8fDE3OTIxNzQzMzl8MA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1731445549627-67b0aaa4aba7?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwzMHx8aW50ZXJpb3IlMjBwaG90b3xlbnwwfHx8fDE3OTIxNzQzMzl8MA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1618832479672-07d622002c20?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHw2fHxpbnRlcmlvciUyMHBob3RvfGVufDB8fHx8MTc5MjE3NDMzOXww&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1724861233646-0f469e9ee27f?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHw4fHxpbnRlcmlvciUyMHBob3RvfGVufDB8fHx8MTc5MjE3NDMzOXww&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1467385829985-2b0fb82b5193?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwxMHx8ZXh0ZXJpb3J8ZW58MHx8fHwxNzkyMTc1MDgxfDA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1605276374104-dee2a0ed3cd6?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwxM3x8ZXh0ZXJpb3J8ZW58MHx8fHwxNzkyMTc1MDgxfDA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1560184897-ae75f418493e?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwxNHx8ZXh0ZXJpb3J8ZW58MHx8fHwxNzkyMTc1MDgxfDA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1647579350413-a6ada4e480ed?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwyMXx8ZXh0ZXJpb3J8ZW58MHx8fHwxNzkyMTc1MDgxfDA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1532323544230-7191fd51bc1b?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwyOHx8ZXh0ZXJpb3J8ZW58MHx8fHwxNzkyMTc1MDgxfDA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1787094497609-5efe6029b950?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwxNXx8aG91c2V8ZW58MHx8fHwxNzkyMTc1MjE4fDA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1567496898669-ee935f5f647a?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwzMHx8aG9tZXN8ZW58MHx8fHwxNzkyMTc1NDMyfDA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1531971589569-0d9370cbe1e5?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwyfHxsdXh1cnklMjBob21lfGVufDB8fHx8MTc5MjE3NTgwNHww&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1781795414968-8ece31826420?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHw5fHxsdXh1cnklMjBob21lfGVufDB8fHx8MTc5MjE3NTgwNHww&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1582268611958-ebfd161ef9cf?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwxNHx8bHV4dXJ5JTIwaG9tZXxlbnwwfHx8fDE3OTIxNzU4MDR8MA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1583608205776-bfd35f0d9f83?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwxMHx8aG91c2V8ZW58MHx8fHwxNzkyMTc1MjE4fDA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1568605114967-8130f3a36994?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwxMXx8aG9tZXxlbnwwfHx8fDE3OTIxNzU5NjN8MA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1523217582562-09d0def993a6?ixid=M3w4MjcwNjd8MHwxfHNlYXJjaHwyMHx8aG9tZXxlbnwwfHx8fDE3OTIxNzU5NjN8MA&amp;ixlib=rb-4.1.0&amp;w=1200&amp;fit=max&amp;q=80</t>
+  </si>
+  <si>
+    <t>Deciding whether to sell or stay in your home is one of the biggest choices you will make. It takes careful planning to get the highest return on your equity.
+## What It Can Take To Stay Put
+**Important Notice:** Wanting to stay in a home you love makes sense, but most properties require *significant* updates to make single-level living truly functional long-term.
+&gt; "A home gets the highest buyer attention in its first ten days on the market."
+Here are three essential factors to evaluate:
+- Single-story living options and step-free entries
+- Doorway and hallway clearances
+Strategic bathroom modifications
+---
+### Additional Perspectives
+Before making any major renovations, read the latest research from the [Harvard Housing Studies](https://www.jchs.harvard.edu) to see which improvements offer real value.</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,8 +686,20 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,8 +724,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -669,11 +754,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -723,11 +821,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1031,482 +1141,496 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DL21"/>
+  <dimension ref="A1:DM21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="7" width="9.1796875" customWidth="1"/>
-    <col min="8" max="9" width="10.6328125" customWidth="1"/>
-    <col min="10" max="10" width="11.36328125" customWidth="1"/>
-    <col min="11" max="12" width="13.54296875" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.81640625" customWidth="1"/>
-    <col min="16" max="16" width="28.36328125" customWidth="1"/>
-    <col min="17" max="17" width="8.7265625" customWidth="1"/>
-    <col min="22" max="22" width="8.7265625" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" customWidth="1"/>
+    <col min="6" max="6" width="6.7265625" customWidth="1"/>
+    <col min="7" max="8" width="9.1796875" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" customWidth="1"/>
+    <col min="12" max="12" width="12.81640625" customWidth="1"/>
+    <col min="13" max="13" width="13.54296875" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="42.36328125" customWidth="1"/>
+    <col min="17" max="17" width="28.36328125" customWidth="1"/>
+    <col min="18" max="18" width="8.7265625" customWidth="1"/>
+    <col min="23" max="23" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:116" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:117" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="R1" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="S1" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="T1" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="U1" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="V1" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="V1" s="13" t="s">
+      <c r="W1" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="W1" s="13" t="s">
+      <c r="X1" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="X1" s="13" t="s">
+      <c r="Y1" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="Y1" s="13" t="s">
+      <c r="Z1" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AA1" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AB1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AC1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AC1" s="13" t="s">
+      <c r="AD1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AD1" s="13" t="s">
+      <c r="AE1" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="AE1" s="13" t="s">
+      <c r="AF1" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="AF1" s="13" t="s">
+      <c r="AG1" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="AG1" s="13" t="s">
+      <c r="AH1" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AH1" s="13" t="s">
+      <c r="AI1" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="AI1" s="13" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="AJ1" s="13" t="s">
+      <c r="AK1" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AK1" s="13" t="s">
+      <c r="AL1" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="AL1" s="13" t="s">
+      <c r="AM1" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AM1" s="13" t="s">
+      <c r="AN1" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AN1" s="13" t="s">
+      <c r="AO1" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="AO1" s="13" t="s">
+      <c r="AP1" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="AP1" s="13" t="s">
+      <c r="AQ1" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AQ1" s="13" t="s">
+      <c r="AR1" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AR1" s="13" t="s">
+      <c r="AS1" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AS1" s="13" t="s">
+      <c r="AT1" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="AT1" s="13" t="s">
+      <c r="AU1" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="AU1" s="13" t="s">
+      <c r="AV1" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="AV1" s="13" t="s">
+      <c r="AW1" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="AW1" s="13" t="s">
+      <c r="AX1" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="AX1" s="13" t="s">
+      <c r="AY1" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AY1" s="13" t="s">
+      <c r="AZ1" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="AZ1" s="13" t="s">
+      <c r="BA1" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="BA1" s="13" t="s">
+      <c r="BB1" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="BB1" s="13" t="s">
+      <c r="BC1" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="BC1" s="13" t="s">
+      <c r="BD1" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="BD1" s="13" t="s">
+      <c r="BE1" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="BE1" s="13" t="s">
+      <c r="BF1" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="BF1" s="13" t="s">
+      <c r="BG1" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="BG1" s="13" t="s">
+      <c r="BH1" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="BH1" s="13" t="s">
+      <c r="BI1" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BI1" s="13" t="s">
+      <c r="BJ1" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BJ1" s="13" t="s">
+      <c r="BK1" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BK1" s="13" t="s">
+      <c r="BL1" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BL1" s="13" t="s">
+      <c r="BM1" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM1" s="13" t="s">
+      <c r="BN1" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="BN1" s="13" t="s">
+      <c r="BO1" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="BO1" s="13" t="s">
+      <c r="BP1" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="BP1" s="13" t="s">
+      <c r="BQ1" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="BQ1" s="13" t="s">
+      <c r="BR1" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="BR1" s="13" t="s">
+      <c r="BS1" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="BS1" s="13" t="s">
+      <c r="BT1" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="BT1" s="13" t="s">
+      <c r="BU1" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="BU1" s="13" t="s">
+      <c r="BV1" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="BV1" s="13" t="s">
+      <c r="BW1" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="BW1" s="13" t="s">
+      <c r="BX1" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="BX1" s="13" t="s">
+      <c r="BY1" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="BY1" s="13" t="s">
+      <c r="BZ1" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="BZ1" s="13" t="s">
+      <c r="CA1" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="CA1" s="13" t="s">
+      <c r="CB1" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="CB1" s="13" t="s">
+      <c r="CC1" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="CC1" s="13" t="s">
+      <c r="CD1" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="CD1" s="13" t="s">
+      <c r="CE1" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="CE1" s="13" t="s">
+      <c r="CF1" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="CF1" s="13" t="s">
+      <c r="CG1" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="CG1" s="13" t="s">
+      <c r="CH1" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="CH1" s="13" t="s">
+      <c r="CI1" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="CI1" s="13" t="s">
+      <c r="CJ1" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="CJ1" s="13" t="s">
+      <c r="CK1" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="CK1" s="13" t="s">
+      <c r="CL1" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="CL1" s="13" t="s">
+      <c r="CM1" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="CM1" s="13" t="s">
+      <c r="CN1" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="CN1" s="13" t="s">
+      <c r="CO1" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="CO1" s="13" t="s">
+      <c r="CP1" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="CP1" s="13" t="s">
+      <c r="CQ1" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="CQ1" s="13" t="s">
+      <c r="CR1" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="CR1" s="13" t="s">
+      <c r="CS1" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="CS1" s="13" t="s">
+      <c r="CT1" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="CT1" s="13" t="s">
+      <c r="CU1" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="CU1" s="13" t="s">
+      <c r="CV1" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="CV1" s="13" t="s">
+      <c r="CW1" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="CW1" s="13" t="s">
+      <c r="CX1" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="CX1" s="13" t="s">
+      <c r="CY1" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="CY1" s="13" t="s">
+      <c r="CZ1" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="CZ1" s="13" t="s">
+      <c r="DA1" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="DA1" s="13" t="s">
+      <c r="DB1" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="DB1" s="13" t="s">
+      <c r="DC1" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="DC1" s="13" t="s">
+      <c r="DD1" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="DD1" s="13" t="s">
+      <c r="DE1" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="DE1" s="13" t="s">
+      <c r="DF1" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="DF1" s="13" t="s">
+      <c r="DG1" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="DG1" s="13" t="s">
+      <c r="DH1" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="DH1" s="13" t="s">
+      <c r="DI1" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="DI1" s="13" t="s">
+      <c r="DJ1" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="DJ1" s="13" t="s">
+      <c r="DK1" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="DK1" s="13" t="s">
+      <c r="DL1" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="DL1" s="13" t="s">
+      <c r="DM1" s="13" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10">
+        <f>MAX(A3:A1000) + 1</f>
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>7</v>
       </c>
-      <c r="H2" s="12">
+      <c r="I2" s="12">
         <v>8400</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="4">
+      <c r="J2" s="12">
+        <v>12000</v>
+      </c>
+      <c r="K2" s="4">
         <v>14850000</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
         <v>1970</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="10" t="str">
-        <f>IF(M2="YES", COUNTIF($M$2:M2, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M2, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="O2" s="10" t="str">
+        <f>IF(N2="YES", COUNTIF($N$2:N2, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N2, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>1st</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(B2), " ", "-")&amp;C2&amp;"-"&amp;D2&amp;"-"&amp;E2)</f>
+      <c r="P2" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q2" s="19" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C2), " ", "-")&amp;D2&amp;"-"&amp;E2&amp;"-"&amp;F2)</f>
         <v>5678-montalvo-ridgesaratoga-ca-95070</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="R2" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="W2" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="X2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="Y2" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="Z2" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="AA2" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="AB2" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="AC2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="AD2" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="Y2" s="14" t="s">
+      <c r="AE2" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="AF2" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AG2" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AH2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AI2" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AK2" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="AF2" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="AG2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="AH2" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI2" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="AJ2" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK2" s="14"/>
       <c r="AL2" s="14"/>
       <c r="AM2" s="14"/>
       <c r="AN2" s="14"/>
@@ -1586,56 +1710,60 @@
       <c r="DJ2" s="14"/>
       <c r="DK2" s="14"/>
       <c r="DL2" s="14"/>
+      <c r="DM2" s="14"/>
     </row>
-    <row r="3" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="22">
+        <f t="shared" ref="A3:A21" si="0">MAX(A4:A1001) + 1</f>
+        <v>19</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="5">
+      <c r="G3" s="5">
         <v>6</v>
       </c>
-      <c r="G3" s="5">
+      <c r="H3" s="5">
         <v>8</v>
       </c>
-      <c r="H3" s="5">
+      <c r="I3" s="5">
         <v>10200</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="7">
+      <c r="J3" s="5"/>
+      <c r="K3" s="7">
         <v>12500000</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L3" s="5">
+      <c r="M3" s="5">
         <v>1980</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="11" t="str">
-        <f>IF(M3="YES", COUNTIF($M$2:M3, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M3, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N3" s="5"/>
+      <c r="O3" s="11" t="str">
+        <f>IF(N3="YES", COUNTIF($N$2:N3, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N3, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="18" t="str">
-        <f t="shared" ref="P3:P21" si="0">LOWER(SUBSTITUTE(TRIM(B3), " ", "-")&amp;C3&amp;"-"&amp;D3&amp;"-"&amp;E3)</f>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="20" t="str">
+        <f t="shared" ref="Q3:Q21" si="1">LOWER(SUBSTITUTE(TRIM(C3), " ", "-")&amp;D3&amp;"-"&amp;E3&amp;"-"&amp;F3)</f>
         <v>81-bear-creek-ridgelos gatos-ca-95033</v>
       </c>
-      <c r="Q3" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="R3" s="15"/>
+      <c r="R3" s="15" t="s">
+        <v>196</v>
+      </c>
       <c r="S3" s="15"/>
       <c r="T3" s="15"/>
       <c r="U3" s="15"/>
@@ -1734,59 +1862,63 @@
       <c r="DJ3" s="15"/>
       <c r="DK3" s="15"/>
       <c r="DL3" s="15"/>
+      <c r="DM3" s="15"/>
     </row>
-    <row r="4" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>4</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>6</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>7150</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="4">
+      <c r="J4" s="2"/>
+      <c r="K4" s="4">
         <v>9200000</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
         <v>1960</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="10" t="str">
-        <f>IF(M4="YES", COUNTIF($M$2:M4, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M4, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N4" s="2"/>
+      <c r="O4" s="10" t="str">
+        <f>IF(N4="YES", COUNTIF($N$2:N4, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N4, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O4" s="10"/>
-      <c r="P4" s="17" t="str">
-        <f t="shared" si="0"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>330-via-santa-teresamonte sereno-ca-95030</v>
       </c>
-      <c r="Q4" s="14" t="s">
-        <v>163</v>
-      </c>
       <c r="R4" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="S4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="14"/>
       <c r="T4" s="14"/>
       <c r="U4" s="14"/>
       <c r="V4" s="14"/>
@@ -1884,64 +2016,68 @@
       <c r="DJ4" s="14"/>
       <c r="DK4" s="14"/>
       <c r="DL4" s="14"/>
+      <c r="DM4" s="14"/>
     </row>
-    <row r="5" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="22">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="5">
+      <c r="G5" s="5">
         <v>4</v>
       </c>
-      <c r="G5" s="5">
+      <c r="H5" s="5">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="I5" s="5">
         <v>5890</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="7">
+      <c r="J5" s="5"/>
+      <c r="K5" s="7">
         <v>7400000</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L5" s="5">
+      <c r="M5" s="5">
         <v>1931</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="11" t="str">
-        <f>IF(M5="YES", COUNTIF($M$2:M5, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M5, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="O5" s="11" t="str">
+        <f>IF(N5="YES", COUNTIF($N$2:N5, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N5, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>2nd</v>
       </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>3271-silver-creek-vistasan jose-ca-95138</v>
       </c>
-      <c r="Q5" s="15" t="s">
-        <v>164</v>
-      </c>
       <c r="R5" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="S5" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="S5" s="15" t="s">
+      <c r="T5" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="T5" s="15"/>
       <c r="U5" s="15"/>
       <c r="V5" s="15"/>
       <c r="W5" s="15"/>
@@ -2038,67 +2174,71 @@
       <c r="DJ5" s="15"/>
       <c r="DK5" s="15"/>
       <c r="DL5" s="15"/>
+      <c r="DM5" s="15"/>
     </row>
-    <row r="6" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>5</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>7</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>9100</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="4">
+      <c r="J6" s="2"/>
+      <c r="K6" s="4">
         <v>16750000</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
         <v>1990</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N6" s="10" t="str">
-        <f>IF(M6="YES", COUNTIF($M$2:M6, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M6, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="O6" s="10" t="str">
+        <f>IF(N6="YES", COUNTIF($N$2:N6, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N6, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>3rd</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="17" t="str">
-        <f t="shared" si="0"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>5045-crescent-park-manorpalo alto-ca-94301</v>
       </c>
-      <c r="Q6" s="14" t="s">
-        <v>165</v>
-      </c>
       <c r="R6" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="S6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="14" t="s">
+      <c r="T6" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="T6" s="14" t="s">
+      <c r="U6" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="U6" s="14"/>
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
       <c r="X6" s="14"/>
@@ -2194,70 +2334,74 @@
       <c r="DJ6" s="14"/>
       <c r="DK6" s="14"/>
       <c r="DL6" s="14"/>
+      <c r="DM6" s="14"/>
     </row>
-    <row r="7" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="22">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="F7" s="5">
-        <v>5</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
       </c>
       <c r="H7" s="5">
+        <v>5</v>
+      </c>
+      <c r="I7" s="5">
         <v>5450</v>
       </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="7">
+      <c r="J7" s="5"/>
+      <c r="K7" s="7">
         <v>6900000</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="L7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L7" s="5">
+      <c r="M7" s="5">
         <v>2001</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="N7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="11" t="str">
-        <f>IF(M7="YES", COUNTIF($M$2:M7, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M7, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="O7" s="11" t="str">
+        <f>IF(N7="YES", COUNTIF($N$2:N7, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N7, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>4th</v>
       </c>
-      <c r="O7" s="11"/>
-      <c r="P7" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>3044-almaden-country-clubsan jose-ca-95120</v>
       </c>
-      <c r="Q7" s="15" t="s">
-        <v>166</v>
-      </c>
       <c r="R7" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="S7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="S7" s="15" t="s">
+      <c r="T7" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="T7" s="15" t="s">
+      <c r="U7" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="U7" s="15" t="s">
+      <c r="V7" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="V7" s="15"/>
       <c r="W7" s="15"/>
       <c r="X7" s="15"/>
       <c r="Y7" s="15"/>
@@ -2352,113 +2496,117 @@
       <c r="DJ7" s="15"/>
       <c r="DK7" s="15"/>
       <c r="DL7" s="15"/>
+      <c r="DM7" s="15"/>
     </row>
-    <row r="8" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>5</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <v>6</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>7800</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="4">
+      <c r="J8" s="2"/>
+      <c r="K8" s="4">
         <v>11200000</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <v>2006</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="10" t="str">
-        <f>IF(M8="YES", COUNTIF($M$2:M8, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M8, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N8" s="2"/>
+      <c r="O8" s="10" t="str">
+        <f>IF(N8="YES", COUNTIF($N$2:N8, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N8, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="17" t="str">
-        <f t="shared" si="0"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>14550-big-basin-waysaratoga-ca-95070</v>
       </c>
-      <c r="Q8" s="14" t="s">
+      <c r="R8" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="S8" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="V8" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="W8" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="R8" s="14" t="s">
+      <c r="X8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="S8" s="14" t="s">
+      <c r="Y8" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="T8" s="14" t="s">
+      <c r="Z8" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="U8" s="14" t="s">
+      <c r="AA8" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="V8" s="14" t="s">
+      <c r="AB8" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="W8" s="14" t="s">
+      <c r="AC8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="X8" s="14" t="s">
+      <c r="AD8" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="Y8" s="14" t="s">
+      <c r="AE8" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="Z8" s="14" t="s">
+      <c r="AF8" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="AA8" s="14" t="s">
+      <c r="AG8" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="AB8" s="14" t="s">
+      <c r="AH8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AC8" s="14" t="s">
+      <c r="AI8" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="AD8" s="14" t="s">
+      <c r="AJ8" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="AE8" s="14" t="s">
+      <c r="AK8" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="AF8" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="AG8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="AH8" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI8" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="AJ8" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="AK8" s="14"/>
       <c r="AL8" s="14"/>
       <c r="AM8" s="14"/>
       <c r="AN8" s="14"/>
@@ -2538,113 +2686,117 @@
       <c r="DJ8" s="14"/>
       <c r="DK8" s="14"/>
       <c r="DL8" s="14"/>
+      <c r="DM8" s="14"/>
     </row>
-    <row r="9" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="22">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="5">
+      <c r="G9" s="5">
         <v>4</v>
       </c>
-      <c r="G9" s="5">
+      <c r="H9" s="5">
         <v>5</v>
       </c>
-      <c r="H9" s="5">
+      <c r="I9" s="5">
         <v>6400</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="7">
+      <c r="J9" s="5"/>
+      <c r="K9" s="7">
         <v>8650000</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L9" s="5">
+      <c r="M9" s="5">
         <v>2021</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="11" t="str">
-        <f>IF(M9="YES", COUNTIF($M$2:M9, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M9, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N9" s="5"/>
+      <c r="O9" s="11" t="str">
+        <f>IF(N9="YES", COUNTIF($N$2:N9, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N9, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>210-shannon-roadlos gatos-ca-95032</v>
       </c>
-      <c r="Q9" s="15" t="s">
+      <c r="R9" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="U9" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="V9" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="W9" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="R9" s="15" t="s">
+      <c r="X9" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="S9" s="15" t="s">
+      <c r="Y9" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="T9" s="15" t="s">
+      <c r="Z9" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="U9" s="15" t="s">
+      <c r="AA9" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="V9" s="15" t="s">
+      <c r="AB9" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="W9" s="15" t="s">
+      <c r="AC9" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="X9" s="15" t="s">
+      <c r="AD9" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="Y9" s="15" t="s">
+      <c r="AE9" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="Z9" s="15" t="s">
+      <c r="AF9" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="AA9" s="15" t="s">
+      <c r="AG9" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="AB9" s="15" t="s">
+      <c r="AH9" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="AC9" s="15" t="s">
+      <c r="AI9" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="AD9" s="15" t="s">
+      <c r="AJ9" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AE9" s="15" t="s">
+      <c r="AK9" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="AF9" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="AG9" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH9" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="AI9" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="AJ9" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="AK9" s="15"/>
       <c r="AL9" s="15"/>
       <c r="AM9" s="15"/>
       <c r="AN9" s="15"/>
@@ -2724,113 +2876,117 @@
       <c r="DJ9" s="15"/>
       <c r="DK9" s="15"/>
       <c r="DL9" s="15"/>
+      <c r="DM9" s="15"/>
     </row>
-    <row r="10" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <v>6</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="2">
         <v>7</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>9600</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="4">
+      <c r="J10" s="2"/>
+      <c r="K10" s="4">
         <v>13800000</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
         <v>1945</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="10" t="str">
-        <f>IF(M10="YES", COUNTIF($M$2:M10, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M10, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N10" s="2"/>
+      <c r="O10" s="10" t="str">
+        <f>IF(N10="YES", COUNTIF($N$2:N10, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N10, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="17" t="str">
-        <f t="shared" si="0"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>16200-greenwood-lanemonte sereno-ca-95030</v>
       </c>
-      <c r="Q10" s="14" t="s">
+      <c r="R10" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="S10" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="T10" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="V10" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="W10" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="R10" s="14" t="s">
+      <c r="X10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="S10" s="14" t="s">
+      <c r="Y10" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="T10" s="14" t="s">
+      <c r="Z10" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="U10" s="14" t="s">
+      <c r="AA10" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="V10" s="14" t="s">
+      <c r="AB10" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="W10" s="14" t="s">
+      <c r="AC10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="X10" s="14" t="s">
+      <c r="AD10" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="Y10" s="14" t="s">
+      <c r="AE10" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="Z10" s="14" t="s">
+      <c r="AF10" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="AA10" s="14" t="s">
+      <c r="AG10" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="AB10" s="14" t="s">
+      <c r="AH10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="AC10" s="14" t="s">
+      <c r="AI10" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="AD10" s="14" t="s">
+      <c r="AJ10" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="AE10" s="14" t="s">
+      <c r="AK10" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="AF10" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH10" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="AI10" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="AJ10" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="AK10" s="14"/>
       <c r="AL10" s="14"/>
       <c r="AM10" s="14"/>
       <c r="AN10" s="14"/>
@@ -2910,115 +3066,117 @@
       <c r="DJ10" s="14"/>
       <c r="DK10" s="14"/>
       <c r="DL10" s="14"/>
+      <c r="DM10" s="14"/>
     </row>
-    <row r="11" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="22">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="5">
+      <c r="G11" s="5">
         <v>4</v>
       </c>
-      <c r="G11" s="5">
+      <c r="H11" s="5">
         <v>4.5</v>
       </c>
-      <c r="H11" s="5">
+      <c r="I11" s="5">
         <v>5100</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="7">
+      <c r="J11" s="5"/>
+      <c r="K11" s="7">
         <v>7950000</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="L11" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L11" s="5">
+      <c r="M11" s="5">
         <v>1950</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="N11" s="11" t="str">
-        <f>IF(M11="YES", COUNTIF($M$2:M11, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M11, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v>5th</v>
-      </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="11" t="str">
+        <f>IF(N11="YES", COUNTIF($N$2:N11, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N11, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+        <v/>
+      </c>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>389-university-avenuelos altos-ca-94022</v>
       </c>
-      <c r="Q11" s="15" t="s">
-        <v>174</v>
-      </c>
       <c r="R11" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="S11" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="S11" s="15" t="s">
-        <v>176</v>
       </c>
       <c r="T11" s="15" t="s">
         <v>176</v>
       </c>
       <c r="U11" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="V11" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="V11" s="15" t="s">
+      <c r="W11" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="W11" s="15" t="s">
+      <c r="X11" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="X11" s="15" t="s">
-        <v>176</v>
       </c>
       <c r="Y11" s="15" t="s">
         <v>176</v>
       </c>
       <c r="Z11" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA11" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="AA11" s="15" t="s">
+      <c r="AB11" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="AB11" s="15" t="s">
+      <c r="AC11" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="AC11" s="15" t="s">
-        <v>176</v>
       </c>
       <c r="AD11" s="15" t="s">
         <v>176</v>
       </c>
       <c r="AE11" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF11" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="AF11" s="15" t="s">
+      <c r="AG11" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="AG11" s="15" t="s">
+      <c r="AH11" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="AH11" s="15" t="s">
-        <v>176</v>
       </c>
       <c r="AI11" s="15" t="s">
         <v>176</v>
       </c>
       <c r="AJ11" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK11" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="AK11" s="15"/>
       <c r="AL11" s="15"/>
       <c r="AM11" s="15"/>
       <c r="AN11" s="15"/>
@@ -3098,113 +3256,117 @@
       <c r="DJ11" s="15"/>
       <c r="DK11" s="15"/>
       <c r="DL11" s="15"/>
+      <c r="DM11" s="15"/>
     </row>
-    <row r="12" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>5</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <v>6</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <v>8100</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="4">
+      <c r="J12" s="2"/>
+      <c r="K12" s="4">
         <v>15200000</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <v>1940</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="10" t="str">
-        <f>IF(M12="YES", COUNTIF($M$2:M12, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M12, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N12" s="2"/>
+      <c r="O12" s="10" t="str">
+        <f>IF(N12="YES", COUNTIF($N$2:N12, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N12, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O12" s="10"/>
-      <c r="P12" s="17" t="str">
-        <f t="shared" si="0"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>1050-waverley-streetpalo alto-ca-94301</v>
       </c>
-      <c r="Q12" s="14" t="s">
+      <c r="R12" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="S12" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="T12" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="U12" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="V12" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="W12" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="R12" s="14" t="s">
+      <c r="X12" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="S12" s="14" t="s">
+      <c r="Y12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="T12" s="14" t="s">
+      <c r="Z12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="U12" s="14" t="s">
+      <c r="AA12" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="V12" s="14" t="s">
+      <c r="AB12" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="W12" s="14" t="s">
+      <c r="AC12" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="X12" s="14" t="s">
+      <c r="AD12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="Y12" s="14" t="s">
+      <c r="AE12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="Z12" s="14" t="s">
+      <c r="AF12" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="AA12" s="14" t="s">
+      <c r="AG12" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="AB12" s="14" t="s">
+      <c r="AH12" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="AC12" s="14" t="s">
+      <c r="AI12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="AD12" s="14" t="s">
+      <c r="AJ12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="AE12" s="14" t="s">
+      <c r="AK12" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="AF12" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="AG12" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH12" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="AI12" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="AJ12" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AK12" s="14"/>
       <c r="AL12" s="14"/>
       <c r="AM12" s="14"/>
       <c r="AN12" s="14"/>
@@ -3284,115 +3446,117 @@
       <c r="DJ12" s="14"/>
       <c r="DK12" s="14"/>
       <c r="DL12" s="14"/>
+      <c r="DM12" s="14"/>
     </row>
-    <row r="13" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="22">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="5">
+      <c r="G13" s="5">
         <v>4</v>
       </c>
-      <c r="G13" s="5">
+      <c r="H13" s="5">
         <v>5</v>
       </c>
-      <c r="H13" s="5">
+      <c r="I13" s="5">
         <v>5300</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="7">
+      <c r="J13" s="5"/>
+      <c r="K13" s="7">
         <v>6450000</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="L13" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L13" s="5">
+      <c r="M13" s="5">
         <v>1931</v>
       </c>
-      <c r="M13" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="N13" s="11" t="str">
-        <f>IF(M13="YES", COUNTIF($M$2:M13, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M13, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v>6th</v>
-      </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="11" t="str">
+        <f>IF(N13="YES", COUNTIF($N$2:N13, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N13, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+        <v/>
+      </c>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>6220-country-club-pkwysan jose-ca-95138</v>
       </c>
-      <c r="Q13" s="15" t="s">
+      <c r="R13" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="T13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="R13" s="15" t="s">
+      <c r="U13" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="V13" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="W13" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="X13" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="S13" s="15" t="s">
+      <c r="Y13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="T13" s="15" t="s">
+      <c r="Z13" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="U13" s="15" t="s">
+      <c r="AA13" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="V13" s="15" t="s">
+      <c r="AB13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="W13" s="15" t="s">
+      <c r="AC13" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="X13" s="15" t="s">
+      <c r="AD13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="Y13" s="15" t="s">
+      <c r="AE13" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="Z13" s="15" t="s">
+      <c r="AF13" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="AA13" s="15" t="s">
+      <c r="AG13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AB13" s="15" t="s">
+      <c r="AH13" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="AC13" s="15" t="s">
+      <c r="AI13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AD13" s="15" t="s">
+      <c r="AJ13" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="AE13" s="15" t="s">
+      <c r="AK13" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="AF13" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG13" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="AH13" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI13" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="AJ13" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="AK13" s="15"/>
       <c r="AL13" s="15"/>
       <c r="AM13" s="15"/>
       <c r="AN13" s="15"/>
@@ -3472,113 +3636,117 @@
       <c r="DJ13" s="15"/>
       <c r="DK13" s="15"/>
       <c r="DL13" s="15"/>
+      <c r="DM13" s="15"/>
     </row>
-    <row r="14" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <v>5</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="2">
         <v>6.5</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <v>7650</v>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="4">
+      <c r="J14" s="2"/>
+      <c r="K14" s="4">
         <v>10950000</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
         <v>1950</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="10" t="str">
-        <f>IF(M14="YES", COUNTIF($M$2:M14, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M14, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N14" s="2"/>
+      <c r="O14" s="10" t="str">
+        <f>IF(N14="YES", COUNTIF($N$2:N14, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N14, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="str">
-        <f t="shared" si="0"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>19540-glen-una-drivesaratoga-ca-95070</v>
       </c>
-      <c r="Q14" s="14" t="s">
+      <c r="R14" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="S14" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="T14" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="U14" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="V14" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="W14" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="R14" s="14" t="s">
+      <c r="X14" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="S14" s="14" t="s">
+      <c r="Y14" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="T14" s="14" t="s">
+      <c r="Z14" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="U14" s="14" t="s">
+      <c r="AA14" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="V14" s="14" t="s">
+      <c r="AB14" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="W14" s="14" t="s">
+      <c r="AC14" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="X14" s="14" t="s">
+      <c r="AD14" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="Y14" s="14" t="s">
+      <c r="AE14" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="Z14" s="14" t="s">
+      <c r="AF14" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="AA14" s="14" t="s">
+      <c r="AG14" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="AB14" s="14" t="s">
+      <c r="AH14" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="AC14" s="14" t="s">
+      <c r="AI14" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="AD14" s="14" t="s">
+      <c r="AJ14" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AE14" s="14" t="s">
+      <c r="AK14" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="AF14" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="AG14" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="AH14" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="AI14" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AJ14" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="AK14" s="14"/>
       <c r="AL14" s="14"/>
       <c r="AM14" s="14"/>
       <c r="AN14" s="14"/>
@@ -3658,113 +3826,117 @@
       <c r="DJ14" s="14"/>
       <c r="DK14" s="14"/>
       <c r="DL14" s="14"/>
+      <c r="DM14" s="14"/>
     </row>
-    <row r="15" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="22">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="5">
+      <c r="G15" s="5">
         <v>4</v>
       </c>
-      <c r="G15" s="5">
+      <c r="H15" s="5">
         <v>4.5</v>
       </c>
-      <c r="H15" s="5">
+      <c r="I15" s="5">
         <v>4920</v>
       </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="7">
+      <c r="J15" s="5"/>
+      <c r="K15" s="7">
         <v>5850000</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="L15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L15" s="5">
+      <c r="M15" s="5">
         <v>1960</v>
       </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="11" t="str">
-        <f>IF(M15="YES", COUNTIF($M$2:M15, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M15, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N15" s="5"/>
+      <c r="O15" s="11" t="str">
+        <f>IF(N15="YES", COUNTIF($N$2:N15, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N15, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>15420-francis-oaks-waylos gatos-ca-95032</v>
       </c>
-      <c r="Q15" s="15" t="s">
+      <c r="R15" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="S15" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="T15" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="U15" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="V15" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="W15" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="R15" s="15" t="s">
+      <c r="X15" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="Y15" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="T15" s="15" t="s">
+      <c r="Z15" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="U15" s="15" t="s">
+      <c r="AA15" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="V15" s="15" t="s">
+      <c r="AB15" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="W15" s="15" t="s">
+      <c r="AC15" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="X15" s="15" t="s">
+      <c r="AD15" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="Y15" s="15" t="s">
+      <c r="AE15" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="Z15" s="15" t="s">
+      <c r="AF15" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="AA15" s="15" t="s">
+      <c r="AG15" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AB15" s="15" t="s">
+      <c r="AH15" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="AC15" s="15" t="s">
+      <c r="AI15" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="AD15" s="15" t="s">
+      <c r="AJ15" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="AE15" s="15" t="s">
+      <c r="AK15" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="AF15" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG15" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="AH15" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI15" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="AJ15" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="AK15" s="15"/>
       <c r="AL15" s="15"/>
       <c r="AM15" s="15"/>
       <c r="AN15" s="15"/>
@@ -3844,113 +4016,117 @@
       <c r="DJ15" s="15"/>
       <c r="DK15" s="15"/>
       <c r="DL15" s="15"/>
+      <c r="DM15" s="15"/>
     </row>
-    <row r="16" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="F16" s="2">
-        <v>4</v>
       </c>
       <c r="G16" s="2">
         <v>4</v>
       </c>
       <c r="H16" s="2">
+        <v>4</v>
+      </c>
+      <c r="I16" s="2">
         <v>4200</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="4">
+      <c r="J16" s="2"/>
+      <c r="K16" s="4">
         <v>5200000</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L16" s="2">
+      <c r="M16" s="2">
         <v>1951</v>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="10" t="str">
-        <f>IF(M16="YES", COUNTIF($M$2:M16, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M16, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N16" s="2"/>
+      <c r="O16" s="10" t="str">
+        <f>IF(N16="YES", COUNTIF($N$2:N16, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N16, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O16" s="10"/>
-      <c r="P16" s="17" t="str">
-        <f t="shared" si="0"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>18230-daves-avenuemonte sereno-ca-95030</v>
       </c>
-      <c r="Q16" s="14" t="s">
+      <c r="R16" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="S16" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="T16" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="U16" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="V16" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="W16" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="R16" s="14" t="s">
+      <c r="X16" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="S16" s="14" t="s">
+      <c r="Y16" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="T16" s="14" t="s">
+      <c r="Z16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="U16" s="14" t="s">
+      <c r="AA16" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="V16" s="14" t="s">
+      <c r="AB16" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="W16" s="14" t="s">
+      <c r="AC16" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="X16" s="14" t="s">
+      <c r="AD16" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="Y16" s="14" t="s">
+      <c r="AE16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="Z16" s="14" t="s">
+      <c r="AF16" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="AA16" s="14" t="s">
+      <c r="AG16" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="AB16" s="14" t="s">
+      <c r="AH16" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="AC16" s="14" t="s">
+      <c r="AI16" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AD16" s="14" t="s">
+      <c r="AJ16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="AE16" s="14" t="s">
+      <c r="AK16" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="AF16" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="AG16" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="AH16" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AI16" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="AJ16" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="AK16" s="14"/>
       <c r="AL16" s="14"/>
       <c r="AM16" s="14"/>
       <c r="AN16" s="14"/>
@@ -4030,113 +4206,117 @@
       <c r="DJ16" s="14"/>
       <c r="DK16" s="14"/>
       <c r="DL16" s="14"/>
+      <c r="DM16" s="14"/>
     </row>
-    <row r="17" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="22">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="5">
+      <c r="G17" s="5">
         <v>6</v>
       </c>
-      <c r="G17" s="5">
+      <c r="H17" s="5">
         <v>7</v>
       </c>
-      <c r="H17" s="5">
+      <c r="I17" s="5">
         <v>8800</v>
       </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="7">
+      <c r="J17" s="5"/>
+      <c r="K17" s="7">
         <v>12900000</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="L17" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L17" s="5">
+      <c r="M17" s="5">
         <v>2023</v>
       </c>
-      <c r="M17" s="5"/>
-      <c r="N17" s="11" t="str">
-        <f>IF(M17="YES", COUNTIF($M$2:M17, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M17, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N17" s="5"/>
+      <c r="O17" s="11" t="str">
+        <f>IF(N17="YES", COUNTIF($N$2:N17, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N17, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>23000-congress-springs-rdsaratoga-ca-95070</v>
       </c>
-      <c r="Q17" s="15" t="s">
+      <c r="R17" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="S17" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="T17" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="U17" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="V17" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="W17" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="R17" s="15" t="s">
+      <c r="X17" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="S17" s="15" t="s">
+      <c r="Y17" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="T17" s="15" t="s">
+      <c r="Z17" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="U17" s="15" t="s">
+      <c r="AA17" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="V17" s="15" t="s">
+      <c r="AB17" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="W17" s="15" t="s">
+      <c r="AC17" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="X17" s="15" t="s">
+      <c r="AD17" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="Y17" s="15" t="s">
+      <c r="AE17" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="Z17" s="15" t="s">
+      <c r="AF17" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="AA17" s="15" t="s">
+      <c r="AG17" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="AB17" s="15" t="s">
+      <c r="AH17" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="AC17" s="15" t="s">
+      <c r="AI17" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="AD17" s="15" t="s">
+      <c r="AJ17" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="AE17" s="15" t="s">
+      <c r="AK17" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="AF17" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="AG17" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="AH17" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI17" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="AJ17" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="AK17" s="15"/>
       <c r="AL17" s="15"/>
       <c r="AM17" s="15"/>
       <c r="AN17" s="15"/>
@@ -4216,113 +4396,117 @@
       <c r="DJ17" s="15"/>
       <c r="DK17" s="15"/>
       <c r="DL17" s="15"/>
+      <c r="DM17" s="15"/>
     </row>
-    <row r="18" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>5</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>5.5</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>6100</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="4">
+      <c r="J18" s="2"/>
+      <c r="K18" s="4">
         <v>9400000</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <v>1997</v>
       </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="10" t="str">
-        <f>IF(M18="YES", COUNTIF($M$2:M18, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M18, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N18" s="2"/>
+      <c r="O18" s="10" t="str">
+        <f>IF(N18="YES", COUNTIF($N$2:N18, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N18, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="17" t="str">
-        <f t="shared" si="0"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>750-university-avenuelos altos-ca-94022</v>
       </c>
-      <c r="Q18" s="14" t="s">
+      <c r="R18" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="S18" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="T18" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="U18" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="V18" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="W18" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="R18" s="14" t="s">
+      <c r="X18" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="S18" s="14" t="s">
+      <c r="Y18" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="T18" s="14" t="s">
+      <c r="Z18" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="U18" s="14" t="s">
+      <c r="AA18" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="V18" s="14" t="s">
+      <c r="AB18" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="W18" s="14" t="s">
+      <c r="AC18" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="X18" s="14" t="s">
+      <c r="AD18" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="Y18" s="14" t="s">
+      <c r="AE18" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="Z18" s="14" t="s">
+      <c r="AF18" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="AA18" s="14" t="s">
+      <c r="AG18" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AB18" s="14" t="s">
+      <c r="AH18" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="AC18" s="14" t="s">
+      <c r="AI18" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="AD18" s="14" t="s">
+      <c r="AJ18" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="AE18" s="14" t="s">
+      <c r="AK18" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="AF18" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AG18" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="AH18" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI18" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="AJ18" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="AK18" s="14"/>
       <c r="AL18" s="14"/>
       <c r="AM18" s="14"/>
       <c r="AN18" s="14"/>
@@ -4402,113 +4586,117 @@
       <c r="DJ18" s="14"/>
       <c r="DK18" s="14"/>
       <c r="DL18" s="14"/>
+      <c r="DM18" s="14"/>
     </row>
-    <row r="19" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="22">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="F19" s="5">
-        <v>4</v>
       </c>
       <c r="G19" s="5">
         <v>4</v>
       </c>
       <c r="H19" s="5">
+        <v>4</v>
+      </c>
+      <c r="I19" s="5">
         <v>4800</v>
       </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="7">
+      <c r="J19" s="5"/>
+      <c r="K19" s="7">
         <v>6150000</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="L19" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L19" s="5">
+      <c r="M19" s="5">
         <v>1994</v>
       </c>
-      <c r="M19" s="5"/>
-      <c r="N19" s="11" t="str">
-        <f>IF(M19="YES", COUNTIF($M$2:M19, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M19, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N19" s="5"/>
+      <c r="O19" s="11" t="str">
+        <f>IF(N19="YES", COUNTIF($N$2:N19, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N19, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O19" s="11"/>
-      <c r="P19" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>16100-kennedy-roadlos gatos-ca-95032</v>
       </c>
-      <c r="Q19" s="15" t="s">
+      <c r="R19" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="S19" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="T19" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="U19" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="V19" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="W19" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="R19" s="15" t="s">
+      <c r="X19" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="S19" s="15" t="s">
+      <c r="Y19" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="T19" s="15" t="s">
+      <c r="Z19" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="U19" s="15" t="s">
+      <c r="AA19" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="V19" s="15" t="s">
+      <c r="AB19" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="W19" s="15" t="s">
+      <c r="AC19" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="X19" s="15" t="s">
+      <c r="AD19" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="Y19" s="15" t="s">
+      <c r="AE19" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="Z19" s="15" t="s">
+      <c r="AF19" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="AA19" s="15" t="s">
+      <c r="AG19" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="AB19" s="15" t="s">
+      <c r="AH19" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="AC19" s="15" t="s">
+      <c r="AI19" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="AD19" s="15" t="s">
+      <c r="AJ19" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="AE19" s="15" t="s">
+      <c r="AK19" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="AF19" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="AG19" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH19" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI19" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="AJ19" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="AK19" s="15"/>
       <c r="AL19" s="15"/>
       <c r="AM19" s="15"/>
       <c r="AN19" s="15"/>
@@ -4588,113 +4776,117 @@
       <c r="DJ19" s="15"/>
       <c r="DK19" s="15"/>
       <c r="DL19" s="15"/>
+      <c r="DM19" s="15"/>
     </row>
-    <row r="20" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="F20" s="2">
-        <v>5</v>
       </c>
       <c r="G20" s="2">
         <v>5</v>
       </c>
       <c r="H20" s="2">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2">
         <v>5600</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="4">
+      <c r="J20" s="2"/>
+      <c r="K20" s="4">
         <v>5750000</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
         <v>1980</v>
       </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="10" t="str">
-        <f>IF(M20="YES", COUNTIF($M$2:M20, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M20, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N20" s="2"/>
+      <c r="O20" s="10" t="str">
+        <f>IF(N20="YES", COUNTIF($N$2:N20, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N20, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O20" s="10"/>
-      <c r="P20" s="17" t="str">
-        <f t="shared" si="0"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>21540-almaden-roadsan jose-ca-95120</v>
       </c>
-      <c r="Q20" s="14" t="s">
+      <c r="R20" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="S20" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="T20" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="U20" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="V20" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="W20" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="R20" s="14" t="s">
+      <c r="X20" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="S20" s="14" t="s">
+      <c r="Y20" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="T20" s="14" t="s">
+      <c r="Z20" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="U20" s="14" t="s">
+      <c r="AA20" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="V20" s="14" t="s">
+      <c r="AB20" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="W20" s="14" t="s">
+      <c r="AC20" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="X20" s="14" t="s">
+      <c r="AD20" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="Y20" s="14" t="s">
+      <c r="AE20" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="Z20" s="14" t="s">
+      <c r="AF20" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="AA20" s="14" t="s">
+      <c r="AG20" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="AB20" s="14" t="s">
+      <c r="AH20" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="AC20" s="14" t="s">
+      <c r="AI20" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="AD20" s="14" t="s">
+      <c r="AJ20" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="AE20" s="14" t="s">
+      <c r="AK20" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="AF20" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="AG20" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="AH20" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="AI20" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="AJ20" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="AK20" s="14"/>
       <c r="AL20" s="14"/>
       <c r="AM20" s="14"/>
       <c r="AN20" s="14"/>
@@ -4774,113 +4966,117 @@
       <c r="DJ20" s="14"/>
       <c r="DK20" s="14"/>
       <c r="DL20" s="14"/>
+      <c r="DM20" s="14"/>
     </row>
-    <row r="21" spans="1:116" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="5">
+      <c r="G21" s="5">
         <v>4</v>
       </c>
-      <c r="G21" s="5">
+      <c r="H21" s="5">
         <v>4.5</v>
       </c>
-      <c r="H21" s="5">
+      <c r="I21" s="5">
         <v>4350</v>
       </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="7">
+      <c r="J21" s="5"/>
+      <c r="K21" s="7">
         <v>6800000</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="L21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L21" s="5">
+      <c r="M21" s="5">
         <v>1951</v>
       </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="11" t="str">
-        <f>IF(M21="YES", COUNTIF($M$2:M21, "YES") &amp; CHOOSE(MIN(COUNTIF($M$2:M21, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N21" s="5"/>
+      <c r="O21" s="11" t="str">
+        <f>IF(N21="YES", COUNTIF($N$2:N21, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N21, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="O21" s="11"/>
-      <c r="P21" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>4120-miranda-avenuepalo alto-ca-94306</v>
       </c>
-      <c r="Q21" s="15" t="s">
+      <c r="R21" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="S21" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="T21" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="U21" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="V21" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="W21" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="R21" s="15" t="s">
+      <c r="X21" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="S21" s="15" t="s">
+      <c r="Y21" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="T21" s="15" t="s">
+      <c r="Z21" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="U21" s="15" t="s">
+      <c r="AA21" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="V21" s="15" t="s">
+      <c r="AB21" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="W21" s="15" t="s">
+      <c r="AC21" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="X21" s="15" t="s">
+      <c r="AD21" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="Y21" s="15" t="s">
+      <c r="AE21" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="Z21" s="15" t="s">
+      <c r="AF21" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="AA21" s="15" t="s">
+      <c r="AG21" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="AB21" s="15" t="s">
+      <c r="AH21" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="AC21" s="15" t="s">
+      <c r="AI21" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="AD21" s="15" t="s">
+      <c r="AJ21" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="AE21" s="15" t="s">
+      <c r="AK21" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="AF21" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="AG21" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="AH21" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI21" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="AJ21" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="AK21" s="15"/>
       <c r="AL21" s="15"/>
       <c r="AM21" s="15"/>
       <c r="AN21" s="15"/>
@@ -4960,6 +5156,7 @@
       <c r="DJ21" s="15"/>
       <c r="DK21" s="15"/>
       <c r="DL21" s="15"/>
+      <c r="DM21" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/data/properties.xlsx
+++ b/src/data/properties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D74E83-75FE-408F-B58F-BE308A074E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5DFA30-EDAB-487F-BFB9-6203F1237B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11330" yWindow="2340" windowWidth="26980" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6570" yWindow="2700" windowWidth="26980" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="205">
   <si>
     <t>status</t>
   </si>
@@ -202,9 +202,6 @@
   </si>
   <si>
     <t>CA</t>
-  </si>
-  <si>
-    <t>5678 Montalvo Ridge</t>
   </si>
   <si>
     <t>image-01</t>
@@ -653,6 +650,12 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>55 E Hamilton Ave</t>
+  </si>
+  <si>
+    <t>Campbell</t>
   </si>
 </sst>
 </file>
@@ -824,7 +827,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1165,7 +1168,7 @@
   <sheetData>
     <row r="1" spans="1:117" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1192,328 +1195,328 @@
         <v>7</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R1" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="S1" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="T1" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="U1" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="V1" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="13" t="s">
+      <c r="W1" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="13" t="s">
+      <c r="X1" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="X1" s="13" t="s">
+      <c r="Y1" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="Y1" s="13" t="s">
+      <c r="Z1" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AA1" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AB1" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AC1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AC1" s="13" t="s">
+      <c r="AD1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AD1" s="13" t="s">
+      <c r="AE1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AE1" s="13" t="s">
+      <c r="AF1" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="AF1" s="13" t="s">
+      <c r="AG1" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="AG1" s="13" t="s">
+      <c r="AH1" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="AH1" s="13" t="s">
+      <c r="AI1" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="AI1" s="13" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="AJ1" s="13" t="s">
+      <c r="AK1" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="AK1" s="13" t="s">
+      <c r="AL1" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AL1" s="13" t="s">
+      <c r="AM1" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="AM1" s="13" t="s">
+      <c r="AN1" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AN1" s="13" t="s">
+      <c r="AO1" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AO1" s="13" t="s">
+      <c r="AP1" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="AP1" s="13" t="s">
+      <c r="AQ1" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="AQ1" s="13" t="s">
+      <c r="AR1" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AR1" s="13" t="s">
+      <c r="AS1" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AS1" s="13" t="s">
+      <c r="AT1" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AT1" s="13" t="s">
+      <c r="AU1" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="AU1" s="13" t="s">
+      <c r="AV1" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="AV1" s="13" t="s">
+      <c r="AW1" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="AW1" s="13" t="s">
+      <c r="AX1" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="AX1" s="13" t="s">
+      <c r="AY1" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="AY1" s="13" t="s">
+      <c r="AZ1" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AZ1" s="13" t="s">
+      <c r="BA1" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="BA1" s="13" t="s">
+      <c r="BB1" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="BB1" s="13" t="s">
+      <c r="BC1" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="BC1" s="13" t="s">
+      <c r="BD1" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="BD1" s="13" t="s">
+      <c r="BE1" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="BE1" s="13" t="s">
+      <c r="BF1" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="BF1" s="13" t="s">
+      <c r="BG1" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="BG1" s="13" t="s">
+      <c r="BH1" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="BH1" s="13" t="s">
+      <c r="BI1" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="BI1" s="13" t="s">
+      <c r="BJ1" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BJ1" s="13" t="s">
+      <c r="BK1" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BK1" s="13" t="s">
+      <c r="BL1" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BL1" s="13" t="s">
+      <c r="BM1" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="BM1" s="13" t="s">
+      <c r="BN1" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BN1" s="13" t="s">
+      <c r="BO1" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="BO1" s="13" t="s">
+      <c r="BP1" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="BP1" s="13" t="s">
+      <c r="BQ1" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="BQ1" s="13" t="s">
+      <c r="BR1" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="BR1" s="13" t="s">
+      <c r="BS1" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="BS1" s="13" t="s">
+      <c r="BT1" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="BT1" s="13" t="s">
+      <c r="BU1" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="BU1" s="13" t="s">
+      <c r="BV1" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="BV1" s="13" t="s">
+      <c r="BW1" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="BW1" s="13" t="s">
+      <c r="BX1" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="BX1" s="13" t="s">
+      <c r="BY1" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="BY1" s="13" t="s">
+      <c r="BZ1" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="BZ1" s="13" t="s">
+      <c r="CA1" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="CA1" s="13" t="s">
+      <c r="CB1" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="CB1" s="13" t="s">
+      <c r="CC1" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="CC1" s="13" t="s">
+      <c r="CD1" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="CD1" s="13" t="s">
+      <c r="CE1" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="CE1" s="13" t="s">
+      <c r="CF1" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="CF1" s="13" t="s">
+      <c r="CG1" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="CG1" s="13" t="s">
+      <c r="CH1" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="CH1" s="13" t="s">
+      <c r="CI1" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="CI1" s="13" t="s">
+      <c r="CJ1" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="CJ1" s="13" t="s">
+      <c r="CK1" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="CK1" s="13" t="s">
+      <c r="CL1" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="CL1" s="13" t="s">
+      <c r="CM1" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="CM1" s="13" t="s">
+      <c r="CN1" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="CN1" s="13" t="s">
+      <c r="CO1" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="CO1" s="13" t="s">
+      <c r="CP1" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="CP1" s="13" t="s">
+      <c r="CQ1" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="CQ1" s="13" t="s">
+      <c r="CR1" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="CR1" s="13" t="s">
+      <c r="CS1" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="CS1" s="13" t="s">
+      <c r="CT1" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="CT1" s="13" t="s">
+      <c r="CU1" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="CU1" s="13" t="s">
+      <c r="CV1" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="CV1" s="13" t="s">
+      <c r="CW1" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="CW1" s="13" t="s">
+      <c r="CX1" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="CX1" s="13" t="s">
+      <c r="CY1" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="CY1" s="13" t="s">
+      <c r="CZ1" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="CZ1" s="13" t="s">
+      <c r="DA1" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="DA1" s="13" t="s">
+      <c r="DB1" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="DB1" s="13" t="s">
+      <c r="DC1" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="DC1" s="13" t="s">
+      <c r="DD1" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="DD1" s="13" t="s">
+      <c r="DE1" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="DE1" s="13" t="s">
+      <c r="DF1" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="DF1" s="13" t="s">
+      <c r="DG1" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="DG1" s="13" t="s">
+      <c r="DH1" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="DH1" s="13" t="s">
+      <c r="DI1" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="DI1" s="13" t="s">
+      <c r="DJ1" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="DJ1" s="13" t="s">
+      <c r="DK1" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="DK1" s="13" t="s">
+      <c r="DL1" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="DL1" s="13" t="s">
+      <c r="DM1" s="13" t="s">
         <v>156</v>
-      </c>
-      <c r="DM1" s="13" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:117" ht="44" customHeight="1" x14ac:dyDescent="0.35">
@@ -1525,16 +1528,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
+      <c r="F2" s="2">
+        <v>95008</v>
       </c>
       <c r="G2" s="2">
         <v>5</v>
@@ -1552,7 +1555,7 @@
         <v>14850000</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M2" s="2">
         <v>1970</v>
@@ -1565,71 +1568,71 @@
         <v>1st</v>
       </c>
       <c r="P2" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q2" s="19" t="str">
         <f>LOWER(SUBSTITUTE(TRIM(C2), " ", "-")&amp;D2&amp;"-"&amp;E2&amp;"-"&amp;F2)</f>
-        <v>5678-montalvo-ridgesaratoga-ca-95070</v>
+        <v>55-e-hamilton-avecampbell-ca-95008</v>
       </c>
       <c r="R2" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="S2" s="14" t="s">
         <v>23</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="U2" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="V2" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="V2" s="14" t="s">
-        <v>166</v>
-      </c>
       <c r="W2" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X2" s="14" t="s">
         <v>23</v>
       </c>
       <c r="Y2" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Z2" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA2" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="AA2" s="14" t="s">
-        <v>166</v>
-      </c>
       <c r="AB2" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AC2" s="14" t="s">
         <v>23</v>
       </c>
       <c r="AD2" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AE2" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="AF2" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="AF2" s="14" t="s">
-        <v>166</v>
-      </c>
       <c r="AG2" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH2" s="14" t="s">
         <v>23</v>
       </c>
       <c r="AI2" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AJ2" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK2" s="14" t="s">
         <v>165</v>
-      </c>
-      <c r="AK2" s="14" t="s">
-        <v>166</v>
       </c>
       <c r="AL2" s="14"/>
       <c r="AM2" s="14"/>
@@ -1746,7 +1749,7 @@
         <v>12500000</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M3" s="5">
         <v>1980</v>
@@ -1762,7 +1765,7 @@
         <v>81-bear-creek-ridgelos gatos-ca-95033</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="S3" s="15"/>
       <c r="T3" s="15"/>
@@ -1898,7 +1901,7 @@
         <v>9200000</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M4" s="2">
         <v>1960</v>
@@ -1914,7 +1917,7 @@
         <v>330-via-santa-teresamonte sereno-ca-95030</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>39</v>
@@ -2052,7 +2055,7 @@
         <v>7400000</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M5" s="5">
         <v>1931</v>
@@ -2070,13 +2073,13 @@
         <v>3271-silver-creek-vistasan jose-ca-95138</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S5" s="15" t="s">
         <v>41</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U5" s="15"/>
       <c r="V5" s="15"/>
@@ -2210,7 +2213,7 @@
         <v>16750000</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M6" s="2">
         <v>1990</v>
@@ -2228,16 +2231,16 @@
         <v>5045-crescent-park-manorpalo alto-ca-94301</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>13</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U6" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
@@ -2370,7 +2373,7 @@
         <v>6900000</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M7" s="5">
         <v>2001</v>
@@ -2388,19 +2391,19 @@
         <v>3044-almaden-country-clubsan jose-ca-95120</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S7" s="15" t="s">
         <v>18</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U7" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="V7" s="15" t="s">
         <v>174</v>
-      </c>
-      <c r="V7" s="15" t="s">
-        <v>175</v>
       </c>
       <c r="W7" s="15"/>
       <c r="X7" s="15"/>
@@ -2532,7 +2535,7 @@
         <v>11200000</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M8" s="2">
         <v>2006</v>
@@ -2548,64 +2551,64 @@
         <v>14550-big-basin-waysaratoga-ca-95070</v>
       </c>
       <c r="R8" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>23</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U8" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="V8" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="V8" s="14" t="s">
-        <v>176</v>
-      </c>
       <c r="W8" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X8" s="14" t="s">
         <v>23</v>
       </c>
       <c r="Y8" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Z8" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA8" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="AA8" s="14" t="s">
-        <v>176</v>
-      </c>
       <c r="AB8" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC8" s="14" t="s">
         <v>23</v>
       </c>
       <c r="AD8" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AE8" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="AF8" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="AF8" s="14" t="s">
-        <v>176</v>
-      </c>
       <c r="AG8" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH8" s="14" t="s">
         <v>23</v>
       </c>
       <c r="AI8" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AJ8" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="AK8" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="AK8" s="14" t="s">
-        <v>176</v>
       </c>
       <c r="AL8" s="14"/>
       <c r="AM8" s="14"/>
@@ -2722,7 +2725,7 @@
         <v>8650000</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M9" s="5">
         <v>2021</v>
@@ -2738,64 +2741,64 @@
         <v>210-shannon-roadlos gatos-ca-95032</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S9" s="15" t="s">
         <v>27</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="U9" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="V9" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="V9" s="15" t="s">
-        <v>177</v>
-      </c>
       <c r="W9" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="X9" s="15" t="s">
         <v>27</v>
       </c>
       <c r="Y9" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Z9" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA9" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AA9" s="15" t="s">
-        <v>177</v>
-      </c>
       <c r="AB9" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC9" s="15" t="s">
         <v>27</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AE9" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="AF9" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AF9" s="15" t="s">
-        <v>177</v>
-      </c>
       <c r="AG9" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AH9" s="15" t="s">
         <v>27</v>
       </c>
       <c r="AI9" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AJ9" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="AK9" s="15" t="s">
         <v>176</v>
-      </c>
-      <c r="AK9" s="15" t="s">
-        <v>177</v>
       </c>
       <c r="AL9" s="15"/>
       <c r="AM9" s="15"/>
@@ -2912,7 +2915,7 @@
         <v>13800000</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M10" s="2">
         <v>1945</v>
@@ -2928,64 +2931,64 @@
         <v>16200-greenwood-lanemonte sereno-ca-95030</v>
       </c>
       <c r="R10" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S10" s="14" t="s">
         <v>31</v>
       </c>
       <c r="T10" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="V10" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="U10" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="V10" s="14" t="s">
-        <v>176</v>
-      </c>
       <c r="W10" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="X10" s="14" t="s">
         <v>31</v>
       </c>
       <c r="Y10" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z10" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA10" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="Z10" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA10" s="14" t="s">
-        <v>176</v>
-      </c>
       <c r="AB10" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AC10" s="14" t="s">
         <v>31</v>
       </c>
       <c r="AD10" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="AE10" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF10" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="AE10" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="AF10" s="14" t="s">
-        <v>176</v>
-      </c>
       <c r="AG10" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH10" s="14" t="s">
         <v>31</v>
       </c>
       <c r="AI10" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="AJ10" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK10" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="AJ10" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="AK10" s="14" t="s">
-        <v>176</v>
       </c>
       <c r="AL10" s="14"/>
       <c r="AM10" s="14"/>
@@ -3102,7 +3105,7 @@
         <v>7950000</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M11" s="5">
         <v>1950</v>
@@ -3118,64 +3121,64 @@
         <v>389-university-avenuelos altos-ca-94022</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S11" s="15" t="s">
         <v>34</v>
       </c>
       <c r="T11" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U11" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="V11" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W11" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="X11" s="15" t="s">
         <v>34</v>
       </c>
       <c r="Y11" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Z11" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA11" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB11" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AC11" s="15" t="s">
         <v>34</v>
       </c>
       <c r="AD11" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AE11" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AF11" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG11" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AH11" s="15" t="s">
         <v>34</v>
       </c>
       <c r="AI11" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AJ11" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AK11" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AL11" s="15"/>
       <c r="AM11" s="15"/>
@@ -3292,7 +3295,7 @@
         <v>15200000</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M12" s="2">
         <v>1940</v>
@@ -3308,64 +3311,64 @@
         <v>1050-waverley-streetpalo alto-ca-94301</v>
       </c>
       <c r="R12" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S12" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="T12" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="U12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="U12" s="14" t="s">
+      <c r="V12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="V12" s="14" t="s">
-        <v>179</v>
-      </c>
       <c r="W12" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="X12" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y12" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="Z12" s="14" t="s">
+      <c r="AA12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="AA12" s="14" t="s">
-        <v>179</v>
-      </c>
       <c r="AB12" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AC12" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AD12" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="AE12" s="14" t="s">
+      <c r="AF12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="AF12" s="14" t="s">
-        <v>179</v>
-      </c>
       <c r="AG12" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AH12" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AI12" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="AJ12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="AJ12" s="14" t="s">
+      <c r="AK12" s="14" t="s">
         <v>178</v>
-      </c>
-      <c r="AK12" s="14" t="s">
-        <v>179</v>
       </c>
       <c r="AL12" s="14"/>
       <c r="AM12" s="14"/>
@@ -3482,7 +3485,7 @@
         <v>6450000</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M13" s="5">
         <v>1931</v>
@@ -3498,64 +3501,64 @@
         <v>6220-country-club-pkwysan jose-ca-95138</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="S13" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="T13" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U13" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="V13" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="V13" s="15" t="s">
-        <v>180</v>
-      </c>
       <c r="W13" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="X13" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y13" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Z13" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AA13" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="AA13" s="15" t="s">
-        <v>180</v>
-      </c>
       <c r="AB13" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AC13" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AE13" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AF13" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="AF13" s="15" t="s">
-        <v>180</v>
-      </c>
       <c r="AG13" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AH13" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AI13" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AJ13" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AK13" s="15" t="s">
         <v>179</v>
-      </c>
-      <c r="AK13" s="15" t="s">
-        <v>180</v>
       </c>
       <c r="AL13" s="15"/>
       <c r="AM13" s="15"/>
@@ -3672,7 +3675,7 @@
         <v>10950000</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M14" s="2">
         <v>1950</v>
@@ -3688,64 +3691,64 @@
         <v>19540-glen-una-drivesaratoga-ca-95070</v>
       </c>
       <c r="R14" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S14" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="U14" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="V14" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="V14" s="14" t="s">
-        <v>181</v>
-      </c>
       <c r="W14" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="X14" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y14" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="X14" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y14" s="14" t="s">
-        <v>178</v>
-      </c>
       <c r="Z14" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="AA14" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AA14" s="14" t="s">
-        <v>181</v>
-      </c>
       <c r="AB14" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="AC14" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD14" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="AC14" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="AD14" s="14" t="s">
-        <v>178</v>
-      </c>
       <c r="AE14" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF14" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AF14" s="14" t="s">
-        <v>181</v>
-      </c>
       <c r="AG14" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="AH14" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI14" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="AH14" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI14" s="14" t="s">
-        <v>178</v>
-      </c>
       <c r="AJ14" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="AK14" s="14" t="s">
         <v>180</v>
-      </c>
-      <c r="AK14" s="14" t="s">
-        <v>181</v>
       </c>
       <c r="AL14" s="14"/>
       <c r="AM14" s="14"/>
@@ -3862,7 +3865,7 @@
         <v>5850000</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M15" s="5">
         <v>1960</v>
@@ -3878,64 +3881,64 @@
         <v>15420-francis-oaks-waylos gatos-ca-95032</v>
       </c>
       <c r="R15" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S15" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T15" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U15" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="V15" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="V15" s="15" t="s">
-        <v>182</v>
-      </c>
       <c r="W15" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="X15" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y15" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z15" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA15" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="AA15" s="15" t="s">
-        <v>182</v>
-      </c>
       <c r="AB15" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AC15" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AD15" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AE15" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF15" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="AF15" s="15" t="s">
-        <v>182</v>
-      </c>
       <c r="AG15" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AH15" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI15" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AJ15" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK15" s="15" t="s">
         <v>181</v>
-      </c>
-      <c r="AK15" s="15" t="s">
-        <v>182</v>
       </c>
       <c r="AL15" s="15"/>
       <c r="AM15" s="15"/>
@@ -4052,7 +4055,7 @@
         <v>5200000</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M16" s="2">
         <v>1951</v>
@@ -4068,64 +4071,64 @@
         <v>18230-daves-avenuemonte sereno-ca-95030</v>
       </c>
       <c r="R16" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S16" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="U16" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="V16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="V16" s="14" t="s">
-        <v>183</v>
-      </c>
       <c r="W16" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="X16" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y16" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Z16" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="AA16" s="14" t="s">
-        <v>183</v>
-      </c>
       <c r="AB16" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AD16" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE16" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="AF16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="AF16" s="14" t="s">
-        <v>183</v>
-      </c>
       <c r="AG16" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH16" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AI16" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AJ16" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="AK16" s="14" t="s">
         <v>182</v>
-      </c>
-      <c r="AK16" s="14" t="s">
-        <v>183</v>
       </c>
       <c r="AL16" s="14"/>
       <c r="AM16" s="14"/>
@@ -4242,7 +4245,7 @@
         <v>12900000</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M17" s="5">
         <v>2023</v>
@@ -4258,64 +4261,64 @@
         <v>23000-congress-springs-rdsaratoga-ca-95070</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="S17" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T17" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="U17" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V17" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W17" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="X17" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y17" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z17" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AA17" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AB17" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC17" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AD17" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AE17" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AF17" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG17" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AH17" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AI17" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AJ17" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AK17" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AL17" s="15"/>
       <c r="AM17" s="15"/>
@@ -4432,7 +4435,7 @@
         <v>9400000</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M18" s="2">
         <v>1997</v>
@@ -4448,64 +4451,64 @@
         <v>750-university-avenuelos altos-ca-94022</v>
       </c>
       <c r="R18" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="S18" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U18" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="V18" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="V18" s="14" t="s">
-        <v>162</v>
-      </c>
       <c r="W18" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="X18" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y18" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z18" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA18" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="AA18" s="14" t="s">
-        <v>162</v>
-      </c>
       <c r="AB18" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC18" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AD18" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE18" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AF18" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="AF18" s="14" t="s">
-        <v>162</v>
-      </c>
       <c r="AG18" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AH18" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AI18" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AJ18" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK18" s="14" t="s">
         <v>161</v>
-      </c>
-      <c r="AK18" s="14" t="s">
-        <v>162</v>
       </c>
       <c r="AL18" s="14"/>
       <c r="AM18" s="14"/>
@@ -4622,7 +4625,7 @@
         <v>6150000</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M19" s="5">
         <v>1994</v>
@@ -4638,64 +4641,64 @@
         <v>16100-kennedy-roadlos gatos-ca-95032</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="S19" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U19" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="V19" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="V19" s="15" t="s">
-        <v>163</v>
-      </c>
       <c r="W19" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y19" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z19" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA19" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="AA19" s="15" t="s">
-        <v>163</v>
-      </c>
       <c r="AB19" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC19" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AD19" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE19" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="AF19" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="AF19" s="15" t="s">
-        <v>163</v>
-      </c>
       <c r="AG19" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AH19" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AI19" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AJ19" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK19" s="15" t="s">
         <v>162</v>
-      </c>
-      <c r="AK19" s="15" t="s">
-        <v>163</v>
       </c>
       <c r="AL19" s="15"/>
       <c r="AM19" s="15"/>
@@ -4812,7 +4815,7 @@
         <v>5750000</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M20" s="2">
         <v>1980</v>
@@ -4828,64 +4831,64 @@
         <v>21540-almaden-roadsan jose-ca-95120</v>
       </c>
       <c r="R20" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="S20" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="U20" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="V20" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="V20" s="14" t="s">
-        <v>164</v>
-      </c>
       <c r="W20" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X20" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y20" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Z20" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA20" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="AA20" s="14" t="s">
-        <v>164</v>
-      </c>
       <c r="AB20" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AD20" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AE20" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF20" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="AF20" s="14" t="s">
-        <v>164</v>
-      </c>
       <c r="AG20" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AH20" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AI20" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AJ20" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="AK20" s="14" t="s">
         <v>163</v>
-      </c>
-      <c r="AK20" s="14" t="s">
-        <v>164</v>
       </c>
       <c r="AL20" s="14"/>
       <c r="AM20" s="14"/>
@@ -5002,7 +5005,7 @@
         <v>6800000</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M21" s="5">
         <v>1951</v>
@@ -5018,64 +5021,64 @@
         <v>4120-miranda-avenuepalo alto-ca-94306</v>
       </c>
       <c r="R21" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="S21" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T21" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="U21" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="V21" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="V21" s="15" t="s">
-        <v>165</v>
-      </c>
       <c r="W21" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X21" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y21" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Z21" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA21" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="AA21" s="15" t="s">
-        <v>165</v>
-      </c>
       <c r="AB21" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AC21" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AD21" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AE21" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AF21" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="AF21" s="15" t="s">
-        <v>165</v>
-      </c>
       <c r="AG21" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AH21" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AI21" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AJ21" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AK21" s="15" t="s">
         <v>164</v>
-      </c>
-      <c r="AK21" s="15" t="s">
-        <v>165</v>
       </c>
       <c r="AL21" s="15"/>
       <c r="AM21" s="15"/>

--- a/src/data/properties.xlsx
+++ b/src/data/properties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D698F8-04C9-44EC-8AFC-EA3F46F75AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D225288A-9638-48E3-930F-ABB7DA6AC64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="2950" windowWidth="26980" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5800" yWindow="3000" windowWidth="26980" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="204">
   <si>
     <t>status</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>Pending</t>
-  </si>
-  <si>
-    <t>330 Via Santa Teresa</t>
   </si>
   <si>
     <t>Monte Sereno</t>
@@ -655,10 +652,7 @@
     <t>duplicated-slug</t>
   </si>
   <si>
-    <t>zip-with-sub-num</t>
-  </si>
-  <si>
-    <t>95008-2</t>
+    <t>95008</t>
   </si>
 </sst>
 </file>
@@ -852,9 +846,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -863,6 +854,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1166,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DO21"/>
+  <dimension ref="A1:DN21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1180,19 +1174,18 @@
     <col min="11" max="11" width="9.81640625" customWidth="1"/>
     <col min="12" max="12" width="12.81640625" customWidth="1"/>
     <col min="13" max="13" width="13.54296875" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="42.36328125" customWidth="1"/>
-    <col min="17" max="17" width="28.36328125" customWidth="1"/>
-    <col min="18" max="18" width="9.90625" customWidth="1"/>
-    <col min="19" max="19" width="17.36328125" customWidth="1"/>
-    <col min="20" max="20" width="8.7265625" customWidth="1"/>
-    <col min="25" max="25" width="8.7265625" customWidth="1"/>
+    <col min="14" max="14" width="42.36328125" customWidth="1"/>
+    <col min="15" max="15" width="28.36328125" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.7265625" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:119" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:118" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1219,34 +1212,34 @@
         <v>7</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="O1" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="P1" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q1" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="R1" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="S1" s="25" t="s">
-        <v>204</v>
+      <c r="S1" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="T1" s="12" t="s">
         <v>55</v>
@@ -1545,11 +1538,8 @@
       <c r="DN1" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="DO1" s="12" t="s">
-        <v>154</v>
-      </c>
     </row>
-    <row r="2" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
         <f>MAX(A3:A1000) + 1</f>
         <v>20</v>
@@ -1558,13 +1548,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2" s="2">
         <v>95008</v>
@@ -1585,93 +1575,90 @@
         <v>14850000</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M2" s="2">
         <v>1970</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O2" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C2)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D2)," ","-")&amp;"-"&amp;E2&amp;"-"&amp;F2))</f>
+        <v>55-e-hamilton-ave-campbell-ca-95008</v>
+      </c>
+      <c r="P2" s="21" t="str">
+        <f t="shared" ref="P2:P3" si="0">IF(COUNTIF(O:O, TRIM(O2)) &gt; 1, "Yes", "---")</f>
+        <v>Yes</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f>IF(N2="YES", COUNTIF($N$2:N2, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N2, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="R2" s="9" t="str">
+        <f>IF(Q2="YES", COUNTIF($Q$2:Q2, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q2, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>1st</v>
       </c>
-      <c r="P2" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q2" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C2), " ", "-")&amp;D2&amp;"-"&amp;E2&amp;"-"&amp;F2)</f>
-        <v>55-e-hamilton-avecampbell-ca-95008</v>
-      </c>
-      <c r="R2" s="21" t="str">
-        <f>IF(COUNTIF(Q:Q, Q2) &gt; 1, "Yes", "-")</f>
-        <v>-</v>
-      </c>
-      <c r="S2" s="21" t="str">
-        <f>IF(LEN(F2)&gt;5, "More than 5 digits", "-")</f>
-        <v>-</v>
+      <c r="S2" s="13" t="s">
+        <v>191</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="U2" s="13" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="V2" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="W2" s="13" t="s">
         <v>162</v>
       </c>
       <c r="X2" s="13" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="Y2" s="13" t="s">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="Z2" s="13" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="AA2" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB2" s="13" t="s">
         <v>162</v>
       </c>
       <c r="AC2" s="13" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AD2" s="13" t="s">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="AE2" s="13" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="AF2" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG2" s="13" t="s">
         <v>162</v>
       </c>
       <c r="AH2" s="13" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AI2" s="13" t="s">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="AJ2" s="13" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="AK2" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AL2" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="AM2" s="13" t="s">
-        <v>163</v>
-      </c>
+      <c r="AM2" s="13"/>
       <c r="AN2" s="13"/>
       <c r="AO2" s="13"/>
       <c r="AP2" s="13"/>
@@ -1751,27 +1738,26 @@
       <c r="DL2" s="13"/>
       <c r="DM2" s="13"/>
       <c r="DN2" s="13"/>
-      <c r="DO2" s="13"/>
     </row>
-    <row r="3" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20">
-        <f t="shared" ref="A3:A21" si="0">MAX(A4:A1001) + 1</f>
+        <f t="shared" ref="A3:A21" si="1">MAX(A4:A1001) + 1</f>
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>205</v>
+        <v>53</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>203</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -1787,32 +1773,29 @@
         <v>12500000</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M3" s="5">
         <v>1980</v>
       </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="10" t="str">
-        <f>IF(N3="YES", COUNTIF($N$2:N3, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N3, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N3" s="16"/>
+      <c r="O3" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C3)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D3)," ","-")&amp;"-"&amp;E3&amp;"-"&amp;F3))</f>
+        <v>55-e-hamilton-ave-campbell-ca-95008</v>
+      </c>
+      <c r="P3" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="10" t="str">
+        <f>IF(Q3="YES", COUNTIF($Q$2:Q3, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q3, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="18" t="str">
-        <f t="shared" ref="Q3:Q21" si="1">LOWER(SUBSTITUTE(TRIM(C3), " ", "-")&amp;D3&amp;"-"&amp;E3&amp;"-"&amp;F3)</f>
-        <v>55-e-hamilton-avecampbell-ca-95008-2</v>
-      </c>
-      <c r="R3" s="23" t="str">
-        <f t="shared" ref="R3:R21" si="2">IF(COUNTIF(Q:Q, Q3) &gt; 1, "Yes", "-")</f>
-        <v>-</v>
-      </c>
-      <c r="S3" s="22" t="str">
-        <f>IF(LEN(F3)&gt;5, "More than 5 digits", "-")</f>
-        <v>More than 5 digits</v>
-      </c>
-      <c r="T3" s="14" t="s">
-        <v>193</v>
-      </c>
+      <c r="S3" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="T3" s="14"/>
       <c r="U3" s="14"/>
       <c r="V3" s="14"/>
       <c r="W3" s="14"/>
@@ -1911,27 +1894,26 @@
       <c r="DL3" s="14"/>
       <c r="DM3" s="14"/>
       <c r="DN3" s="14"/>
-      <c r="DO3" s="14"/>
     </row>
-    <row r="4" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>201</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="G4" s="2">
         <v>4</v>
@@ -1947,35 +1929,32 @@
         <v>9200000</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M4" s="2">
         <v>1960</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="9" t="str">
-        <f>IF(N4="YES", COUNTIF($N$2:N4, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N4, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N4" s="15"/>
+      <c r="O4" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C4)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D4)," ","-")&amp;"-"&amp;E4&amp;"-"&amp;F4))</f>
+        <v>55-e-hamilton-ave-campbell-ca-95008</v>
+      </c>
+      <c r="P4" s="21" t="str">
+        <f>IF(COUNTIF(O:O, TRIM(O4)) &gt; 1, "Yes", "---")</f>
+        <v>Yes</v>
+      </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="9" t="str">
+        <f>IF(Q4="YES", COUNTIF($Q$2:Q4, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q4, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>330-via-santa-teresamonte sereno-ca-95030</v>
-      </c>
-      <c r="R4" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S4" s="21" t="str">
-        <f t="shared" ref="S4:S21" si="3">IF(LEN(F4)&gt;5, "More than 5 digits", "-")</f>
-        <v>-</v>
+      <c r="S4" s="13" t="s">
+        <v>193</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="U4" s="13" t="s">
-        <v>37</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="U4" s="13"/>
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
@@ -2073,27 +2052,26 @@
       <c r="DL4" s="13"/>
       <c r="DM4" s="13"/>
       <c r="DN4" s="13"/>
-      <c r="DO4" s="13"/>
     </row>
-    <row r="5" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -2109,40 +2087,37 @@
         <v>7400000</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M5" s="5">
         <v>1931</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="16"/>
+      <c r="O5" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C5)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D5)," ","-")&amp;"-"&amp;E5&amp;"-"&amp;F5))</f>
+        <v>3271-silver-creek-vista-san-jose-ca-95138</v>
+      </c>
+      <c r="P5" s="22" t="str">
+        <f t="shared" ref="P5:P21" si="2">IF(COUNTIF(O:O, TRIM(O5)) &gt; 1, "Yes", "---")</f>
+        <v>---</v>
+      </c>
+      <c r="Q5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="10" t="str">
-        <f>IF(N5="YES", COUNTIF($N$2:N5, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N5, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="R5" s="10" t="str">
+        <f>IF(Q5="YES", COUNTIF($Q$2:Q5, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q5, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>2nd</v>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>3271-silver-creek-vistasan jose-ca-95138</v>
-      </c>
-      <c r="R5" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S5" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S5" s="14" t="s">
+        <v>194</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="V5" s="14" t="s">
-        <v>163</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="V5" s="14"/>
       <c r="W5" s="14"/>
       <c r="X5" s="14"/>
       <c r="Y5" s="14"/>
@@ -2239,27 +2214,26 @@
       <c r="DL5" s="14"/>
       <c r="DM5" s="14"/>
       <c r="DN5" s="14"/>
-      <c r="DO5" s="14"/>
     </row>
-    <row r="6" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="G6" s="2">
         <v>5</v>
@@ -2275,43 +2249,40 @@
         <v>16750000</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M6" s="2">
         <v>1990</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="15"/>
+      <c r="O6" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C6)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D6)," ","-")&amp;"-"&amp;E6&amp;"-"&amp;F6))</f>
+        <v>5045-crescent-park-manor-palo-alto-ca-94301</v>
+      </c>
+      <c r="P6" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="9" t="str">
-        <f>IF(N6="YES", COUNTIF($N$2:N6, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N6, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="R6" s="9" t="str">
+        <f>IF(Q6="YES", COUNTIF($Q$2:Q6, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q6, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>3rd</v>
       </c>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>5045-crescent-park-manorpalo alto-ca-94301</v>
-      </c>
-      <c r="R6" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S6" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S6" s="13" t="s">
+        <v>195</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>196</v>
+        <v>13</v>
       </c>
       <c r="U6" s="13" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
       <c r="V6" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="W6" s="13" t="s">
-        <v>166</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
       <c r="Z6" s="13"/>
@@ -2407,27 +2378,26 @@
       <c r="DL6" s="13"/>
       <c r="DM6" s="13"/>
       <c r="DN6" s="13"/>
-      <c r="DO6" s="13"/>
     </row>
-    <row r="7" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
@@ -2443,46 +2413,43 @@
         <v>6900000</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M7" s="5">
         <v>2001</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="N7" s="16"/>
+      <c r="O7" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C7)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D7)," ","-")&amp;"-"&amp;E7&amp;"-"&amp;F7))</f>
+        <v>3044-almaden-country-club-san-jose-ca-95120</v>
+      </c>
+      <c r="P7" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="10" t="str">
-        <f>IF(N7="YES", COUNTIF($N$2:N7, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N7, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="R7" s="10" t="str">
+        <f>IF(Q7="YES", COUNTIF($Q$2:Q7, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q7, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>4th</v>
       </c>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>3044-almaden-country-clubsan jose-ca-95120</v>
-      </c>
-      <c r="R7" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S7" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S7" s="14" t="s">
+        <v>197</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="W7" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="X7" s="14" t="s">
-        <v>172</v>
-      </c>
+      <c r="X7" s="14"/>
       <c r="Y7" s="14"/>
       <c r="Z7" s="14"/>
       <c r="AA7" s="14"/>
@@ -2577,24 +2544,23 @@
       <c r="DL7" s="14"/>
       <c r="DM7" s="14"/>
       <c r="DN7" s="14"/>
-      <c r="DO7" s="14"/>
     </row>
-    <row r="8" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>12</v>
@@ -2613,89 +2579,86 @@
         <v>11200000</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M8" s="2">
         <v>2006</v>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="9" t="str">
-        <f>IF(N8="YES", COUNTIF($N$2:N8, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N8, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N8" s="15"/>
+      <c r="O8" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C8)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D8)," ","-")&amp;"-"&amp;E8&amp;"-"&amp;F8))</f>
+        <v>14550-big-basin-way-saratoga-ca-95070</v>
+      </c>
+      <c r="P8" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="9" t="str">
+        <f>IF(Q8="YES", COUNTIF($Q$2:Q8, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q8, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>14550-big-basin-waysaratoga-ca-95070</v>
-      </c>
-      <c r="R8" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S8" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S8" s="13" t="s">
+        <v>196</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="U8" s="13" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="V8" s="13" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="W8" s="13" t="s">
         <v>172</v>
       </c>
       <c r="X8" s="13" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="Y8" s="13" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="Z8" s="13" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AA8" s="13" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AB8" s="13" t="s">
         <v>172</v>
       </c>
       <c r="AC8" s="13" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="AD8" s="13" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AE8" s="13" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AF8" s="13" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AG8" s="13" t="s">
         <v>172</v>
       </c>
       <c r="AH8" s="13" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="AI8" s="13" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ8" s="13" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AK8" s="13" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AL8" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AM8" s="13" t="s">
-        <v>173</v>
-      </c>
+      <c r="AM8" s="13"/>
       <c r="AN8" s="13"/>
       <c r="AO8" s="13"/>
       <c r="AP8" s="13"/>
@@ -2775,27 +2738,26 @@
       <c r="DL8" s="13"/>
       <c r="DM8" s="13"/>
       <c r="DN8" s="13"/>
-      <c r="DO8" s="13"/>
     </row>
-    <row r="9" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="5">
         <v>4</v>
@@ -2811,89 +2773,86 @@
         <v>8650000</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M9" s="5">
         <v>2021</v>
       </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="10" t="str">
-        <f>IF(N9="YES", COUNTIF($N$2:N9, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N9, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N9" s="16"/>
+      <c r="O9" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C9)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D9)," ","-")&amp;"-"&amp;E9&amp;"-"&amp;F9))</f>
+        <v>210-shannon-road-los-gatos-ca-95032</v>
+      </c>
+      <c r="P9" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="10" t="str">
+        <f>IF(Q9="YES", COUNTIF($Q$2:Q9, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q9, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>210-shannon-roadlos gatos-ca-95032</v>
-      </c>
-      <c r="R9" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S9" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S9" s="14" t="s">
+        <v>180</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="U9" s="14" t="s">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="V9" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="W9" s="14" t="s">
         <v>173</v>
       </c>
       <c r="X9" s="14" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="Y9" s="14" t="s">
-        <v>165</v>
+        <v>24</v>
       </c>
       <c r="Z9" s="14" t="s">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="AA9" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AB9" s="14" t="s">
         <v>173</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AD9" s="14" t="s">
-        <v>165</v>
+        <v>24</v>
       </c>
       <c r="AE9" s="14" t="s">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="AF9" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG9" s="14" t="s">
         <v>173</v>
       </c>
       <c r="AH9" s="14" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AI9" s="14" t="s">
-        <v>165</v>
+        <v>24</v>
       </c>
       <c r="AJ9" s="14" t="s">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="AK9" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL9" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="AM9" s="14" t="s">
-        <v>174</v>
-      </c>
+      <c r="AM9" s="14"/>
       <c r="AN9" s="14"/>
       <c r="AO9" s="14"/>
       <c r="AP9" s="14"/>
@@ -2973,27 +2932,26 @@
       <c r="DL9" s="14"/>
       <c r="DM9" s="14"/>
       <c r="DN9" s="14"/>
-      <c r="DO9" s="14"/>
     </row>
-    <row r="10" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="G10" s="2">
         <v>6</v>
@@ -3009,89 +2967,86 @@
         <v>13800000</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M10" s="2">
         <v>1945</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="9" t="str">
-        <f>IF(N10="YES", COUNTIF($N$2:N10, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N10, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N10" s="15"/>
+      <c r="O10" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C10)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D10)," ","-")&amp;"-"&amp;E10&amp;"-"&amp;F10))</f>
+        <v>16200-greenwood-lane-monte-sereno-ca-95030</v>
+      </c>
+      <c r="P10" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="9" t="str">
+        <f>IF(Q10="YES", COUNTIF($Q$2:Q10, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q10, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>16200-greenwood-lanemonte sereno-ca-95030</v>
-      </c>
-      <c r="R10" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S10" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S10" s="13" t="s">
+        <v>181</v>
       </c>
       <c r="T10" s="13" t="s">
-        <v>182</v>
+        <v>28</v>
       </c>
       <c r="U10" s="13" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="V10" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="W10" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="W10" s="13" t="s">
-        <v>174</v>
-      </c>
       <c r="X10" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y10" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z10" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA10" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="Y10" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="Z10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA10" s="13" t="s">
+      <c r="AB10" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AB10" s="13" t="s">
-        <v>174</v>
-      </c>
       <c r="AC10" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD10" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE10" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF10" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AD10" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF10" s="13" t="s">
+      <c r="AG10" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AG10" s="13" t="s">
-        <v>174</v>
-      </c>
       <c r="AH10" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI10" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ10" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK10" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AI10" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AJ10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK10" s="13" t="s">
+      <c r="AL10" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AL10" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM10" s="13" t="s">
-        <v>173</v>
-      </c>
+      <c r="AM10" s="13"/>
       <c r="AN10" s="13"/>
       <c r="AO10" s="13"/>
       <c r="AP10" s="13"/>
@@ -3171,27 +3126,26 @@
       <c r="DL10" s="13"/>
       <c r="DM10" s="13"/>
       <c r="DN10" s="13"/>
-      <c r="DO10" s="13"/>
     </row>
-    <row r="11" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="G11" s="5">
         <v>4</v>
@@ -3207,89 +3161,86 @@
         <v>7950000</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M11" s="5">
         <v>1950</v>
       </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="10" t="str">
-        <f>IF(N11="YES", COUNTIF($N$2:N11, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N11, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N11" s="16"/>
+      <c r="O11" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C11)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D11)," ","-")&amp;"-"&amp;E11&amp;"-"&amp;F11))</f>
+        <v>389-university-avenue-los-altos-ca-94022</v>
+      </c>
+      <c r="P11" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="10" t="str">
+        <f>IF(Q11="YES", COUNTIF($Q$2:Q11, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q11, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>389-university-avenuelos altos-ca-94022</v>
-      </c>
-      <c r="R11" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S11" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S11" s="14" t="s">
+        <v>182</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="U11" s="14" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="V11" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W11" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="X11" s="14" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="Y11" s="14" t="s">
-        <v>171</v>
+        <v>31</v>
       </c>
       <c r="Z11" s="14" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="AA11" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB11" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AD11" s="14" t="s">
-        <v>171</v>
+        <v>31</v>
       </c>
       <c r="AE11" s="14" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="AF11" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG11" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AH11" s="14" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AI11" s="14" t="s">
-        <v>171</v>
+        <v>31</v>
       </c>
       <c r="AJ11" s="14" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="AK11" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AL11" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AM11" s="14" t="s">
-        <v>175</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="AM11" s="14"/>
       <c r="AN11" s="14"/>
       <c r="AO11" s="14"/>
       <c r="AP11" s="14"/>
@@ -3369,27 +3320,26 @@
       <c r="DL11" s="14"/>
       <c r="DM11" s="14"/>
       <c r="DN11" s="14"/>
-      <c r="DO11" s="14"/>
     </row>
-    <row r="12" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="G12" s="2">
         <v>5</v>
@@ -3405,34 +3355,33 @@
         <v>15200000</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M12" s="2">
         <v>1940</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="9" t="str">
-        <f>IF(N12="YES", COUNTIF($N$2:N12, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N12, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N12" s="15"/>
+      <c r="O12" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C12)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D12)," ","-")&amp;"-"&amp;E12&amp;"-"&amp;F12))</f>
+        <v>1050-waverley-street-palo-alto-ca-94301</v>
+      </c>
+      <c r="P12" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="9" t="str">
+        <f>IF(Q12="YES", COUNTIF($Q$2:Q12, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q12, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>1050-waverley-streetpalo alto-ca-94301</v>
-      </c>
-      <c r="R12" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S12" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S12" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="U12" s="13" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="V12" s="13" t="s">
         <v>174</v>
@@ -3441,13 +3390,13 @@
         <v>175</v>
       </c>
       <c r="X12" s="13" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="Y12" s="13" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="Z12" s="13" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="AA12" s="13" t="s">
         <v>174</v>
@@ -3456,13 +3405,13 @@
         <v>175</v>
       </c>
       <c r="AC12" s="13" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="AD12" s="13" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="AE12" s="13" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="AF12" s="13" t="s">
         <v>174</v>
@@ -3471,13 +3420,13 @@
         <v>175</v>
       </c>
       <c r="AH12" s="13" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="AI12" s="13" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="AJ12" s="13" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="AK12" s="13" t="s">
         <v>174</v>
@@ -3485,9 +3434,7 @@
       <c r="AL12" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AM12" s="13" t="s">
-        <v>176</v>
-      </c>
+      <c r="AM12" s="13"/>
       <c r="AN12" s="13"/>
       <c r="AO12" s="13"/>
       <c r="AP12" s="13"/>
@@ -3567,27 +3514,26 @@
       <c r="DL12" s="13"/>
       <c r="DM12" s="13"/>
       <c r="DN12" s="13"/>
-      <c r="DO12" s="13"/>
     </row>
-    <row r="13" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="G13" s="5">
         <v>4</v>
@@ -3603,89 +3549,86 @@
         <v>6450000</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M13" s="5">
         <v>1931</v>
       </c>
-      <c r="N13" s="5"/>
-      <c r="O13" s="10" t="str">
-        <f>IF(N13="YES", COUNTIF($N$2:N13, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N13, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N13" s="16"/>
+      <c r="O13" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C13)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D13)," ","-")&amp;"-"&amp;E13&amp;"-"&amp;F13))</f>
+        <v>6220-country-club-pkwy-san-jose-ca-95138</v>
+      </c>
+      <c r="P13" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="10" t="str">
+        <f>IF(Q13="YES", COUNTIF($Q$2:Q13, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q13, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>6220-country-club-pkwysan jose-ca-95138</v>
-      </c>
-      <c r="R13" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S13" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S13" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="U13" s="14" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="V13" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="W13" s="14" t="s">
         <v>176</v>
       </c>
       <c r="X13" s="14" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y13" s="14" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="Z13" s="14" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="AA13" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AB13" s="14" t="s">
         <v>176</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="AD13" s="14" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="AE13" s="14" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="AF13" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG13" s="14" t="s">
         <v>176</v>
       </c>
       <c r="AH13" s="14" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="AI13" s="14" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="AJ13" s="14" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="AK13" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AL13" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="AM13" s="14" t="s">
-        <v>177</v>
-      </c>
+      <c r="AM13" s="14"/>
       <c r="AN13" s="14"/>
       <c r="AO13" s="14"/>
       <c r="AP13" s="14"/>
@@ -3765,24 +3708,23 @@
       <c r="DL13" s="14"/>
       <c r="DM13" s="14"/>
       <c r="DN13" s="14"/>
-      <c r="DO13" s="14"/>
     </row>
-    <row r="14" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>12</v>
@@ -3801,89 +3743,86 @@
         <v>10950000</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M14" s="2">
         <v>1950</v>
       </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="9" t="str">
-        <f>IF(N14="YES", COUNTIF($N$2:N14, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N14, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N14" s="15"/>
+      <c r="O14" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C14)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D14)," ","-")&amp;"-"&amp;E14&amp;"-"&amp;F14))</f>
+        <v>19540-glen-una-drive-saratoga-ca-95070</v>
+      </c>
+      <c r="P14" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="9" t="str">
+        <f>IF(Q14="YES", COUNTIF($Q$2:Q14, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q14, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>19540-glen-una-drivesaratoga-ca-95070</v>
-      </c>
-      <c r="R14" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S14" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S14" s="13" t="s">
+        <v>185</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="U14" s="13" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="V14" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W14" s="13" t="s">
         <v>177</v>
       </c>
       <c r="X14" s="13" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Y14" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z14" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="Z14" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="AA14" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AB14" s="13" t="s">
         <v>177</v>
       </c>
       <c r="AC14" s="13" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="AD14" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AE14" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AE14" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="AF14" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG14" s="13" t="s">
         <v>177</v>
       </c>
       <c r="AH14" s="13" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="AI14" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AJ14" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AJ14" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="AK14" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AL14" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AM14" s="13" t="s">
-        <v>178</v>
-      </c>
+      <c r="AM14" s="13"/>
       <c r="AN14" s="13"/>
       <c r="AO14" s="13"/>
       <c r="AP14" s="13"/>
@@ -3963,27 +3902,26 @@
       <c r="DL14" s="13"/>
       <c r="DM14" s="13"/>
       <c r="DN14" s="13"/>
-      <c r="DO14" s="13"/>
     </row>
-    <row r="15" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" s="5">
         <v>4</v>
@@ -3999,89 +3937,86 @@
         <v>5850000</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M15" s="5">
         <v>1960</v>
       </c>
-      <c r="N15" s="5"/>
-      <c r="O15" s="10" t="str">
-        <f>IF(N15="YES", COUNTIF($N$2:N15, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N15, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N15" s="16"/>
+      <c r="O15" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C15)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D15)," ","-")&amp;"-"&amp;E15&amp;"-"&amp;F15))</f>
+        <v>15420-francis-oaks-way-los-gatos-ca-95032</v>
+      </c>
+      <c r="P15" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="10" t="str">
+        <f>IF(Q15="YES", COUNTIF($Q$2:Q15, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q15, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>15420-francis-oaks-waylos gatos-ca-95032</v>
-      </c>
-      <c r="R15" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S15" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S15" s="14" t="s">
+        <v>186</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="U15" s="14" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="V15" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W15" s="14" t="s">
         <v>178</v>
       </c>
       <c r="X15" s="14" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Y15" s="14" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="Z15" s="14" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="AA15" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB15" s="14" t="s">
         <v>178</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AD15" s="14" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="AE15" s="14" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="AF15" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG15" s="14" t="s">
         <v>178</v>
       </c>
       <c r="AH15" s="14" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AI15" s="14" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="AJ15" s="14" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="AK15" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL15" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="AM15" s="14" t="s">
-        <v>179</v>
-      </c>
+      <c r="AM15" s="14"/>
       <c r="AN15" s="14"/>
       <c r="AO15" s="14"/>
       <c r="AP15" s="14"/>
@@ -4161,27 +4096,26 @@
       <c r="DL15" s="14"/>
       <c r="DM15" s="14"/>
       <c r="DN15" s="14"/>
-      <c r="DO15" s="14"/>
     </row>
-    <row r="16" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="G16" s="2">
         <v>4</v>
@@ -4197,89 +4131,86 @@
         <v>5200000</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M16" s="2">
         <v>1951</v>
       </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="9" t="str">
-        <f>IF(N16="YES", COUNTIF($N$2:N16, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N16, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N16" s="15"/>
+      <c r="O16" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C16)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D16)," ","-")&amp;"-"&amp;E16&amp;"-"&amp;F16))</f>
+        <v>18230-daves-avenue-monte-sereno-ca-95030</v>
+      </c>
+      <c r="P16" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="9" t="str">
+        <f>IF(Q16="YES", COUNTIF($Q$2:Q16, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q16, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>18230-daves-avenuemonte sereno-ca-95030</v>
-      </c>
-      <c r="R16" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S16" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S16" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="T16" s="13" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="U16" s="13" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="V16" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W16" s="13" t="s">
         <v>179</v>
       </c>
       <c r="X16" s="13" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="Y16" s="13" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="Z16" s="13" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="AA16" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AB16" s="13" t="s">
         <v>179</v>
       </c>
       <c r="AC16" s="13" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="AD16" s="13" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="AE16" s="13" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="AF16" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG16" s="13" t="s">
         <v>179</v>
       </c>
       <c r="AH16" s="13" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="AI16" s="13" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="AJ16" s="13" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="AK16" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL16" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AM16" s="13" t="s">
-        <v>180</v>
-      </c>
+      <c r="AM16" s="13"/>
       <c r="AN16" s="13"/>
       <c r="AO16" s="13"/>
       <c r="AP16" s="13"/>
@@ -4359,24 +4290,23 @@
       <c r="DL16" s="13"/>
       <c r="DM16" s="13"/>
       <c r="DN16" s="13"/>
-      <c r="DO16" s="13"/>
     </row>
-    <row r="17" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>12</v>
@@ -4395,89 +4325,86 @@
         <v>12900000</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M17" s="5">
         <v>2023</v>
       </c>
-      <c r="N17" s="5"/>
-      <c r="O17" s="10" t="str">
-        <f>IF(N17="YES", COUNTIF($N$2:N17, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N17, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N17" s="16"/>
+      <c r="O17" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C17)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D17)," ","-")&amp;"-"&amp;E17&amp;"-"&amp;F17))</f>
+        <v>23000-congress-springs-rd-saratoga-ca-95070</v>
+      </c>
+      <c r="P17" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="10" t="str">
+        <f>IF(Q17="YES", COUNTIF($Q$2:Q17, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q17, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>23000-congress-springs-rdsaratoga-ca-95070</v>
-      </c>
-      <c r="R17" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S17" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S17" s="14" t="s">
+        <v>188</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="U17" s="14" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="V17" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="W17" s="14" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="X17" s="14" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="Y17" s="14" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="Z17" s="14" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="AA17" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AB17" s="14" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="AD17" s="14" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="AE17" s="14" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="AF17" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG17" s="14" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="AH17" s="14" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="AI17" s="14" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="AJ17" s="14" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="AK17" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL17" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AM17" s="14" t="s">
-        <v>158</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="AM17" s="14"/>
       <c r="AN17" s="14"/>
       <c r="AO17" s="14"/>
       <c r="AP17" s="14"/>
@@ -4557,27 +4484,26 @@
       <c r="DL17" s="14"/>
       <c r="DM17" s="14"/>
       <c r="DN17" s="14"/>
-      <c r="DO17" s="14"/>
     </row>
-    <row r="18" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="G18" s="2">
         <v>5</v>
@@ -4593,89 +4519,86 @@
         <v>9400000</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M18" s="2">
         <v>1997</v>
       </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="9" t="str">
-        <f>IF(N18="YES", COUNTIF($N$2:N18, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N18, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N18" s="15"/>
+      <c r="O18" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C18)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D18)," ","-")&amp;"-"&amp;E18&amp;"-"&amp;F18))</f>
+        <v>750-university-avenue-los-altos-ca-94022</v>
+      </c>
+      <c r="P18" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="9" t="str">
+        <f>IF(Q18="YES", COUNTIF($Q$2:Q18, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q18, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>750-university-avenuelos altos-ca-94022</v>
-      </c>
-      <c r="R18" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S18" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S18" s="13" t="s">
+        <v>189</v>
       </c>
       <c r="T18" s="13" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="U18" s="13" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="V18" s="13" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="W18" s="13" t="s">
         <v>158</v>
       </c>
       <c r="X18" s="13" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="Y18" s="13" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="Z18" s="13" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="AA18" s="13" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AB18" s="13" t="s">
         <v>158</v>
       </c>
       <c r="AC18" s="13" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="AD18" s="13" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="AE18" s="13" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="AF18" s="13" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AG18" s="13" t="s">
         <v>158</v>
       </c>
       <c r="AH18" s="13" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="AI18" s="13" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="AJ18" s="13" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="AK18" s="13" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AL18" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AM18" s="13" t="s">
-        <v>159</v>
-      </c>
+      <c r="AM18" s="13"/>
       <c r="AN18" s="13"/>
       <c r="AO18" s="13"/>
       <c r="AP18" s="13"/>
@@ -4755,27 +4678,26 @@
       <c r="DL18" s="13"/>
       <c r="DM18" s="13"/>
       <c r="DN18" s="13"/>
-      <c r="DO18" s="13"/>
     </row>
-    <row r="19" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" s="5">
         <v>4</v>
@@ -4791,89 +4713,86 @@
         <v>6150000</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M19" s="5">
         <v>1994</v>
       </c>
-      <c r="N19" s="5"/>
-      <c r="O19" s="10" t="str">
-        <f>IF(N19="YES", COUNTIF($N$2:N19, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N19, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N19" s="16"/>
+      <c r="O19" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C19)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D19)," ","-")&amp;"-"&amp;E19&amp;"-"&amp;F19))</f>
+        <v>16100-kennedy-road-los-gatos-ca-95032</v>
+      </c>
+      <c r="P19" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="10" t="str">
+        <f>IF(Q19="YES", COUNTIF($Q$2:Q19, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q19, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>16100-kennedy-roadlos gatos-ca-95032</v>
-      </c>
-      <c r="R19" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S19" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S19" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="U19" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="V19" s="14" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="W19" s="14" t="s">
         <v>159</v>
       </c>
       <c r="X19" s="14" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="Y19" s="14" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="Z19" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AA19" s="14" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="AB19" s="14" t="s">
         <v>159</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="AD19" s="14" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="AE19" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AF19" s="14" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="AG19" s="14" t="s">
         <v>159</v>
       </c>
       <c r="AH19" s="14" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="AI19" s="14" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="AJ19" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AK19" s="14" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="AL19" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="AM19" s="14" t="s">
-        <v>160</v>
-      </c>
+      <c r="AM19" s="14"/>
       <c r="AN19" s="14"/>
       <c r="AO19" s="14"/>
       <c r="AP19" s="14"/>
@@ -4953,27 +4872,26 @@
       <c r="DL19" s="14"/>
       <c r="DM19" s="14"/>
       <c r="DN19" s="14"/>
-      <c r="DO19" s="14"/>
     </row>
-    <row r="20" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="2">
         <v>5</v>
@@ -4989,89 +4907,86 @@
         <v>5750000</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M20" s="2">
         <v>1980</v>
       </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="9" t="str">
-        <f>IF(N20="YES", COUNTIF($N$2:N20, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N20, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N20" s="15"/>
+      <c r="O20" s="17" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C20)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D20)," ","-")&amp;"-"&amp;E20&amp;"-"&amp;F20))</f>
+        <v>21540-almaden-road-san-jose-ca-95120</v>
+      </c>
+      <c r="P20" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="9" t="str">
+        <f>IF(Q20="YES", COUNTIF($Q$2:Q20, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q20, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>21540-almaden-roadsan jose-ca-95120</v>
-      </c>
-      <c r="R20" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S20" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S20" s="13" t="s">
+        <v>189</v>
       </c>
       <c r="T20" s="13" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="U20" s="13" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="V20" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W20" s="13" t="s">
         <v>160</v>
       </c>
       <c r="X20" s="13" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="Y20" s="13" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="Z20" s="13" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="AA20" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AB20" s="13" t="s">
         <v>160</v>
       </c>
       <c r="AC20" s="13" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="AD20" s="13" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="AE20" s="13" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="AF20" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG20" s="13" t="s">
         <v>160</v>
       </c>
       <c r="AH20" s="13" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="AI20" s="13" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="AJ20" s="13" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="AK20" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL20" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AM20" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="AM20" s="13"/>
       <c r="AN20" s="13"/>
       <c r="AO20" s="13"/>
       <c r="AP20" s="13"/>
@@ -5151,27 +5066,26 @@
       <c r="DL20" s="13"/>
       <c r="DM20" s="13"/>
       <c r="DN20" s="13"/>
-      <c r="DO20" s="13"/>
     </row>
-    <row r="21" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="G21" s="5">
         <v>4</v>
@@ -5187,89 +5101,86 @@
         <v>6800000</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M21" s="5">
         <v>1951</v>
       </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="10" t="str">
-        <f>IF(N21="YES", COUNTIF($N$2:N21, "YES") &amp; CHOOSE(MIN(COUNTIF($N$2:N21, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="N21" s="16"/>
+      <c r="O21" s="18" t="str">
+        <f>LOWER(SUBSTITUTE(TRIM(C21)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D21)," ","-")&amp;"-"&amp;E21&amp;"-"&amp;F21))</f>
+        <v>4120-miranda-avenue-palo-alto-ca-94306</v>
+      </c>
+      <c r="P21" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>---</v>
+      </c>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="10" t="str">
+        <f>IF(Q21="YES", COUNTIF($Q$2:Q21, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q21, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>4120-miranda-avenuepalo alto-ca-94306</v>
-      </c>
-      <c r="R21" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-      <c r="S21" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
+      <c r="S21" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="U21" s="14" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="V21" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="W21" s="14" t="s">
         <v>161</v>
       </c>
       <c r="X21" s="14" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="Y21" s="14" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="Z21" s="14" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="AA21" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AB21" s="14" t="s">
         <v>161</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="AD21" s="14" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="AE21" s="14" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="AF21" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG21" s="14" t="s">
         <v>161</v>
       </c>
       <c r="AH21" s="14" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="AI21" s="14" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="AJ21" s="14" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="AK21" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AL21" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="AM21" s="14" t="s">
-        <v>162</v>
-      </c>
+      <c r="AM21" s="14"/>
       <c r="AN21" s="14"/>
       <c r="AO21" s="14"/>
       <c r="AP21" s="14"/>
@@ -5349,7 +5260,6 @@
       <c r="DL21" s="14"/>
       <c r="DM21" s="14"/>
       <c r="DN21" s="14"/>
-      <c r="DO21" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/data/properties.xlsx
+++ b/src/data/properties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D225288A-9638-48E3-930F-ABB7DA6AC64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE74AFD8-EF86-4A44-A666-41FE82E0E531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5800" yWindow="3000" windowWidth="26980" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9680" yWindow="2990" windowWidth="26980" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="204">
   <si>
     <t>status</t>
   </si>
@@ -649,10 +649,10 @@
     <t>Campbell</t>
   </si>
   <si>
-    <t>duplicated-slug</t>
-  </si>
-  <si>
     <t>95008</t>
+  </si>
+  <si>
+    <t>check-duplicated-slug</t>
   </si>
 </sst>
 </file>
@@ -778,7 +778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -800,9 +800,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -857,6 +854,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1160,31 +1170,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DN21"/>
+  <dimension ref="A1:DO22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" customWidth="1"/>
-    <col min="6" max="6" width="7.6328125" customWidth="1"/>
-    <col min="7" max="8" width="9.1796875" customWidth="1"/>
-    <col min="9" max="9" width="10.6328125" customWidth="1"/>
-    <col min="10" max="10" width="9.90625" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" customWidth="1"/>
-    <col min="12" max="12" width="12.81640625" customWidth="1"/>
-    <col min="13" max="13" width="13.54296875" customWidth="1"/>
-    <col min="14" max="14" width="42.36328125" customWidth="1"/>
-    <col min="15" max="15" width="28.36328125" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6328125" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" customWidth="1"/>
+    <col min="6" max="6" width="6.08984375" customWidth="1"/>
+    <col min="7" max="8" width="5.54296875" customWidth="1"/>
+    <col min="9" max="10" width="6.453125" customWidth="1"/>
+    <col min="11" max="11" width="8.90625" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="14" width="31.6328125" customWidth="1"/>
+    <col min="15" max="15" width="21.36328125" customWidth="1"/>
+    <col min="16" max="16" width="10.1796875" customWidth="1"/>
+    <col min="17" max="18" width="9.1796875" customWidth="1"/>
     <col min="19" max="19" width="8.7265625" customWidth="1"/>
     <col min="24" max="24" width="8.7265625" customWidth="1"/>
+    <col min="119" max="119" width="2.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:118" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:119" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="18" t="s">
         <v>199</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1211,343 +1221,344 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>154</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="O1" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="P1" s="24" t="s">
-        <v>202</v>
+      <c r="P1" s="27" t="s">
+        <v>203</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="25" t="s">
+      <c r="R1" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="S1" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="T1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="W1" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="X1" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Y1" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="Z1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="AA1" s="12" t="s">
+      <c r="AA1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="AB1" s="12" t="s">
+      <c r="AB1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AC1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="AD1" s="12" t="s">
+      <c r="AD1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AE1" s="12" t="s">
+      <c r="AE1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="AF1" s="12" t="s">
+      <c r="AF1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="AG1" s="12" t="s">
+      <c r="AG1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AH1" s="12" t="s">
+      <c r="AH1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="AI1" s="12" t="s">
+      <c r="AI1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AJ1" s="12" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AK1" s="12" t="s">
+      <c r="AK1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AL1" s="12" t="s">
+      <c r="AL1" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AM1" s="12" t="s">
+      <c r="AM1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AN1" s="12" t="s">
+      <c r="AN1" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AO1" s="12" t="s">
+      <c r="AO1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AP1" s="12" t="s">
+      <c r="AP1" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AQ1" s="12" t="s">
+      <c r="AQ1" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="AR1" s="12" t="s">
+      <c r="AR1" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AS1" s="12" t="s">
+      <c r="AS1" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="AT1" s="12" t="s">
+      <c r="AT1" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="AU1" s="12" t="s">
+      <c r="AU1" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="AV1" s="12" t="s">
+      <c r="AV1" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AW1" s="12" t="s">
+      <c r="AW1" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="AX1" s="12" t="s">
+      <c r="AX1" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="AY1" s="12" t="s">
+      <c r="AY1" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="AZ1" s="12" t="s">
+      <c r="AZ1" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="BA1" s="12" t="s">
+      <c r="BA1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="BB1" s="12" t="s">
+      <c r="BB1" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="BC1" s="12" t="s">
+      <c r="BC1" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="BD1" s="12" t="s">
+      <c r="BD1" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="BE1" s="12" t="s">
+      <c r="BE1" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="BF1" s="12" t="s">
+      <c r="BF1" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="BG1" s="12" t="s">
+      <c r="BG1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="BH1" s="12" t="s">
+      <c r="BH1" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="BI1" s="12" t="s">
+      <c r="BI1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="BJ1" s="12" t="s">
+      <c r="BJ1" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="BK1" s="12" t="s">
+      <c r="BK1" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="BL1" s="12" t="s">
+      <c r="BL1" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="BM1" s="12" t="s">
+      <c r="BM1" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="BN1" s="12" t="s">
+      <c r="BN1" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="BO1" s="12" t="s">
+      <c r="BO1" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="BP1" s="12" t="s">
+      <c r="BP1" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="BQ1" s="12" t="s">
+      <c r="BQ1" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="BR1" s="12" t="s">
+      <c r="BR1" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="BS1" s="12" t="s">
+      <c r="BS1" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="BT1" s="12" t="s">
+      <c r="BT1" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="BU1" s="12" t="s">
+      <c r="BU1" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="BV1" s="12" t="s">
+      <c r="BV1" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BW1" s="12" t="s">
+      <c r="BW1" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="BX1" s="12" t="s">
+      <c r="BX1" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="BY1" s="12" t="s">
+      <c r="BY1" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="BZ1" s="12" t="s">
+      <c r="BZ1" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="CA1" s="12" t="s">
+      <c r="CA1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="CB1" s="12" t="s">
+      <c r="CB1" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="CC1" s="12" t="s">
+      <c r="CC1" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="CD1" s="12" t="s">
+      <c r="CD1" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="CE1" s="12" t="s">
+      <c r="CE1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="CF1" s="12" t="s">
+      <c r="CF1" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="CG1" s="12" t="s">
+      <c r="CG1" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="CH1" s="12" t="s">
+      <c r="CH1" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="CI1" s="12" t="s">
+      <c r="CI1" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="CJ1" s="12" t="s">
+      <c r="CJ1" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="CK1" s="12" t="s">
+      <c r="CK1" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="CL1" s="12" t="s">
+      <c r="CL1" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="CM1" s="12" t="s">
+      <c r="CM1" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="CN1" s="12" t="s">
+      <c r="CN1" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="CO1" s="12" t="s">
+      <c r="CO1" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="CP1" s="12" t="s">
+      <c r="CP1" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="CQ1" s="12" t="s">
+      <c r="CQ1" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="CR1" s="12" t="s">
+      <c r="CR1" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="CS1" s="12" t="s">
+      <c r="CS1" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="CT1" s="12" t="s">
+      <c r="CT1" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="CU1" s="12" t="s">
+      <c r="CU1" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="CV1" s="12" t="s">
+      <c r="CV1" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="CW1" s="12" t="s">
+      <c r="CW1" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="CX1" s="12" t="s">
+      <c r="CX1" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="CY1" s="12" t="s">
+      <c r="CY1" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="CZ1" s="12" t="s">
+      <c r="CZ1" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="DA1" s="12" t="s">
+      <c r="DA1" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="DB1" s="12" t="s">
+      <c r="DB1" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="DC1" s="12" t="s">
+      <c r="DC1" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="DD1" s="12" t="s">
+      <c r="DD1" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="DE1" s="12" t="s">
+      <c r="DE1" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="DF1" s="12" t="s">
+      <c r="DF1" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="DG1" s="12" t="s">
+      <c r="DG1" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="DH1" s="12" t="s">
+      <c r="DH1" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="DI1" s="12" t="s">
+      <c r="DI1" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="DJ1" s="12" t="s">
+      <c r="DJ1" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="DK1" s="12" t="s">
+      <c r="DK1" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="DL1" s="12" t="s">
+      <c r="DL1" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="DM1" s="12" t="s">
+      <c r="DM1" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="DN1" s="12" t="s">
+      <c r="DN1" s="11" t="s">
         <v>153</v>
       </c>
+      <c r="DO1" s="26"/>
     </row>
-    <row r="2" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+    <row r="2" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8">
         <f>MAX(A3:A1000) + 1</f>
         <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="28" t="s">
         <v>200</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -1565,10 +1576,10 @@
       <c r="H2" s="2">
         <v>7</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>8400</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="10">
         <v>12000</v>
       </c>
       <c r="K2" s="4">
@@ -1580,174 +1591,175 @@
       <c r="M2" s="2">
         <v>1970</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="O2" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C2)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D2)," ","-")&amp;"-"&amp;E2&amp;"-"&amp;F2))</f>
+      <c r="O2" s="16" t="str">
+        <f t="shared" ref="O2:O21" si="0">LOWER(SUBSTITUTE(TRIM(C2)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D2)," ","-")&amp;"-"&amp;E2&amp;"-"&amp;F2))</f>
         <v>55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="P2" s="21" t="str">
-        <f t="shared" ref="P2:P3" si="0">IF(COUNTIF(O:O, TRIM(O2)) &gt; 1, "Yes", "---")</f>
+      <c r="P2" s="20" t="str">
+        <f t="shared" ref="P2:P3" si="1">IF(COUNTIF(O:O, TRIM(O2)) &gt; 1, "Yes", "---")</f>
         <v>Yes</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="9" t="str">
+      <c r="R2" s="8" t="str">
         <f>IF(Q2="YES", COUNTIF($Q$2:Q2, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q2, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>1st</v>
       </c>
-      <c r="S2" s="13" t="s">
+      <c r="S2" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="W2" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="X2" s="13" t="s">
+      <c r="X2" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="Y2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="Z2" s="13" t="s">
+      <c r="Z2" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="AA2" s="13" t="s">
+      <c r="AA2" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="AB2" s="13" t="s">
+      <c r="AB2" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="AC2" s="13" t="s">
+      <c r="AC2" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AD2" s="13" t="s">
+      <c r="AD2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AE2" s="13" t="s">
+      <c r="AE2" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="AF2" s="13" t="s">
+      <c r="AF2" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="AG2" s="13" t="s">
+      <c r="AG2" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="AH2" s="13" t="s">
+      <c r="AH2" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AI2" s="13" t="s">
+      <c r="AI2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="13" t="s">
+      <c r="AJ2" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="AK2" s="13" t="s">
+      <c r="AK2" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="AL2" s="13" t="s">
+      <c r="AL2" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="AM2" s="13"/>
-      <c r="AN2" s="13"/>
-      <c r="AO2" s="13"/>
-      <c r="AP2" s="13"/>
-      <c r="AQ2" s="13"/>
-      <c r="AR2" s="13"/>
-      <c r="AS2" s="13"/>
-      <c r="AT2" s="13"/>
-      <c r="AU2" s="13"/>
-      <c r="AV2" s="13"/>
-      <c r="AW2" s="13"/>
-      <c r="AX2" s="13"/>
-      <c r="AY2" s="13"/>
-      <c r="AZ2" s="13"/>
-      <c r="BA2" s="13"/>
-      <c r="BB2" s="13"/>
-      <c r="BC2" s="13"/>
-      <c r="BD2" s="13"/>
-      <c r="BE2" s="13"/>
-      <c r="BF2" s="13"/>
-      <c r="BG2" s="13"/>
-      <c r="BH2" s="13"/>
-      <c r="BI2" s="13"/>
-      <c r="BJ2" s="13"/>
-      <c r="BK2" s="13"/>
-      <c r="BL2" s="13"/>
-      <c r="BM2" s="13"/>
-      <c r="BN2" s="13"/>
-      <c r="BO2" s="13"/>
-      <c r="BP2" s="13"/>
-      <c r="BQ2" s="13"/>
-      <c r="BR2" s="13"/>
-      <c r="BS2" s="13"/>
-      <c r="BT2" s="13"/>
-      <c r="BU2" s="13"/>
-      <c r="BV2" s="13"/>
-      <c r="BW2" s="13"/>
-      <c r="BX2" s="13"/>
-      <c r="BY2" s="13"/>
-      <c r="BZ2" s="13"/>
-      <c r="CA2" s="13"/>
-      <c r="CB2" s="13"/>
-      <c r="CC2" s="13"/>
-      <c r="CD2" s="13"/>
-      <c r="CE2" s="13"/>
-      <c r="CF2" s="13"/>
-      <c r="CG2" s="13"/>
-      <c r="CH2" s="13"/>
-      <c r="CI2" s="13"/>
-      <c r="CJ2" s="13"/>
-      <c r="CK2" s="13"/>
-      <c r="CL2" s="13"/>
-      <c r="CM2" s="13"/>
-      <c r="CN2" s="13"/>
-      <c r="CO2" s="13"/>
-      <c r="CP2" s="13"/>
-      <c r="CQ2" s="13"/>
-      <c r="CR2" s="13"/>
-      <c r="CS2" s="13"/>
-      <c r="CT2" s="13"/>
-      <c r="CU2" s="13"/>
-      <c r="CV2" s="13"/>
-      <c r="CW2" s="13"/>
-      <c r="CX2" s="13"/>
-      <c r="CY2" s="13"/>
-      <c r="CZ2" s="13"/>
-      <c r="DA2" s="13"/>
-      <c r="DB2" s="13"/>
-      <c r="DC2" s="13"/>
-      <c r="DD2" s="13"/>
-      <c r="DE2" s="13"/>
-      <c r="DF2" s="13"/>
-      <c r="DG2" s="13"/>
-      <c r="DH2" s="13"/>
-      <c r="DI2" s="13"/>
-      <c r="DJ2" s="13"/>
-      <c r="DK2" s="13"/>
-      <c r="DL2" s="13"/>
-      <c r="DM2" s="13"/>
-      <c r="DN2" s="13"/>
+      <c r="AM2" s="12"/>
+      <c r="AN2" s="12"/>
+      <c r="AO2" s="12"/>
+      <c r="AP2" s="12"/>
+      <c r="AQ2" s="12"/>
+      <c r="AR2" s="12"/>
+      <c r="AS2" s="12"/>
+      <c r="AT2" s="12"/>
+      <c r="AU2" s="12"/>
+      <c r="AV2" s="12"/>
+      <c r="AW2" s="12"/>
+      <c r="AX2" s="12"/>
+      <c r="AY2" s="12"/>
+      <c r="AZ2" s="12"/>
+      <c r="BA2" s="12"/>
+      <c r="BB2" s="12"/>
+      <c r="BC2" s="12"/>
+      <c r="BD2" s="12"/>
+      <c r="BE2" s="12"/>
+      <c r="BF2" s="12"/>
+      <c r="BG2" s="12"/>
+      <c r="BH2" s="12"/>
+      <c r="BI2" s="12"/>
+      <c r="BJ2" s="12"/>
+      <c r="BK2" s="12"/>
+      <c r="BL2" s="12"/>
+      <c r="BM2" s="12"/>
+      <c r="BN2" s="12"/>
+      <c r="BO2" s="12"/>
+      <c r="BP2" s="12"/>
+      <c r="BQ2" s="12"/>
+      <c r="BR2" s="12"/>
+      <c r="BS2" s="12"/>
+      <c r="BT2" s="12"/>
+      <c r="BU2" s="12"/>
+      <c r="BV2" s="12"/>
+      <c r="BW2" s="12"/>
+      <c r="BX2" s="12"/>
+      <c r="BY2" s="12"/>
+      <c r="BZ2" s="12"/>
+      <c r="CA2" s="12"/>
+      <c r="CB2" s="12"/>
+      <c r="CC2" s="12"/>
+      <c r="CD2" s="12"/>
+      <c r="CE2" s="12"/>
+      <c r="CF2" s="12"/>
+      <c r="CG2" s="12"/>
+      <c r="CH2" s="12"/>
+      <c r="CI2" s="12"/>
+      <c r="CJ2" s="12"/>
+      <c r="CK2" s="12"/>
+      <c r="CL2" s="12"/>
+      <c r="CM2" s="12"/>
+      <c r="CN2" s="12"/>
+      <c r="CO2" s="12"/>
+      <c r="CP2" s="12"/>
+      <c r="CQ2" s="12"/>
+      <c r="CR2" s="12"/>
+      <c r="CS2" s="12"/>
+      <c r="CT2" s="12"/>
+      <c r="CU2" s="12"/>
+      <c r="CV2" s="12"/>
+      <c r="CW2" s="12"/>
+      <c r="CX2" s="12"/>
+      <c r="CY2" s="12"/>
+      <c r="CZ2" s="12"/>
+      <c r="DA2" s="12"/>
+      <c r="DB2" s="12"/>
+      <c r="DC2" s="12"/>
+      <c r="DD2" s="12"/>
+      <c r="DE2" s="12"/>
+      <c r="DF2" s="12"/>
+      <c r="DG2" s="12"/>
+      <c r="DH2" s="12"/>
+      <c r="DI2" s="12"/>
+      <c r="DJ2" s="12"/>
+      <c r="DK2" s="12"/>
+      <c r="DL2" s="12"/>
+      <c r="DM2" s="12"/>
+      <c r="DN2" s="12"/>
+      <c r="DO2" s="26"/>
     </row>
-    <row r="3" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20">
-        <f t="shared" ref="A3:A21" si="1">MAX(A4:A1001) + 1</f>
+    <row r="3" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="19">
+        <f t="shared" ref="A3:A21" si="2">MAX(A4:A1001) + 1</f>
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="29" t="s">
         <v>200</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -1756,8 +1768,8 @@
       <c r="E3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="26" t="s">
-        <v>203</v>
+      <c r="F3" s="25" t="s">
+        <v>202</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -1778,132 +1790,135 @@
       <c r="M3" s="5">
         <v>1980</v>
       </c>
-      <c r="N3" s="16"/>
-      <c r="O3" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C3)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D3)," ","-")&amp;"-"&amp;E3&amp;"-"&amp;F3))</f>
+      <c r="N3" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O3" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="P3" s="22" t="str">
-        <f t="shared" si="0"/>
+      <c r="P3" s="21" t="str">
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="Q3" s="5"/>
-      <c r="R3" s="10" t="str">
+      <c r="R3" s="9" t="str">
         <f>IF(Q3="YES", COUNTIF($Q$2:Q3, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q3, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S3" s="14" t="s">
+      <c r="S3" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="14"/>
-      <c r="AO3" s="14"/>
-      <c r="AP3" s="14"/>
-      <c r="AQ3" s="14"/>
-      <c r="AR3" s="14"/>
-      <c r="AS3" s="14"/>
-      <c r="AT3" s="14"/>
-      <c r="AU3" s="14"/>
-      <c r="AV3" s="14"/>
-      <c r="AW3" s="14"/>
-      <c r="AX3" s="14"/>
-      <c r="AY3" s="14"/>
-      <c r="AZ3" s="14"/>
-      <c r="BA3" s="14"/>
-      <c r="BB3" s="14"/>
-      <c r="BC3" s="14"/>
-      <c r="BD3" s="14"/>
-      <c r="BE3" s="14"/>
-      <c r="BF3" s="14"/>
-      <c r="BG3" s="14"/>
-      <c r="BH3" s="14"/>
-      <c r="BI3" s="14"/>
-      <c r="BJ3" s="14"/>
-      <c r="BK3" s="14"/>
-      <c r="BL3" s="14"/>
-      <c r="BM3" s="14"/>
-      <c r="BN3" s="14"/>
-      <c r="BO3" s="14"/>
-      <c r="BP3" s="14"/>
-      <c r="BQ3" s="14"/>
-      <c r="BR3" s="14"/>
-      <c r="BS3" s="14"/>
-      <c r="BT3" s="14"/>
-      <c r="BU3" s="14"/>
-      <c r="BV3" s="14"/>
-      <c r="BW3" s="14"/>
-      <c r="BX3" s="14"/>
-      <c r="BY3" s="14"/>
-      <c r="BZ3" s="14"/>
-      <c r="CA3" s="14"/>
-      <c r="CB3" s="14"/>
-      <c r="CC3" s="14"/>
-      <c r="CD3" s="14"/>
-      <c r="CE3" s="14"/>
-      <c r="CF3" s="14"/>
-      <c r="CG3" s="14"/>
-      <c r="CH3" s="14"/>
-      <c r="CI3" s="14"/>
-      <c r="CJ3" s="14"/>
-      <c r="CK3" s="14"/>
-      <c r="CL3" s="14"/>
-      <c r="CM3" s="14"/>
-      <c r="CN3" s="14"/>
-      <c r="CO3" s="14"/>
-      <c r="CP3" s="14"/>
-      <c r="CQ3" s="14"/>
-      <c r="CR3" s="14"/>
-      <c r="CS3" s="14"/>
-      <c r="CT3" s="14"/>
-      <c r="CU3" s="14"/>
-      <c r="CV3" s="14"/>
-      <c r="CW3" s="14"/>
-      <c r="CX3" s="14"/>
-      <c r="CY3" s="14"/>
-      <c r="CZ3" s="14"/>
-      <c r="DA3" s="14"/>
-      <c r="DB3" s="14"/>
-      <c r="DC3" s="14"/>
-      <c r="DD3" s="14"/>
-      <c r="DE3" s="14"/>
-      <c r="DF3" s="14"/>
-      <c r="DG3" s="14"/>
-      <c r="DH3" s="14"/>
-      <c r="DI3" s="14"/>
-      <c r="DJ3" s="14"/>
-      <c r="DK3" s="14"/>
-      <c r="DL3" s="14"/>
-      <c r="DM3" s="14"/>
-      <c r="DN3" s="14"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="13"/>
+      <c r="AF3" s="13"/>
+      <c r="AG3" s="13"/>
+      <c r="AH3" s="13"/>
+      <c r="AI3" s="13"/>
+      <c r="AJ3" s="13"/>
+      <c r="AK3" s="13"/>
+      <c r="AL3" s="13"/>
+      <c r="AM3" s="13"/>
+      <c r="AN3" s="13"/>
+      <c r="AO3" s="13"/>
+      <c r="AP3" s="13"/>
+      <c r="AQ3" s="13"/>
+      <c r="AR3" s="13"/>
+      <c r="AS3" s="13"/>
+      <c r="AT3" s="13"/>
+      <c r="AU3" s="13"/>
+      <c r="AV3" s="13"/>
+      <c r="AW3" s="13"/>
+      <c r="AX3" s="13"/>
+      <c r="AY3" s="13"/>
+      <c r="AZ3" s="13"/>
+      <c r="BA3" s="13"/>
+      <c r="BB3" s="13"/>
+      <c r="BC3" s="13"/>
+      <c r="BD3" s="13"/>
+      <c r="BE3" s="13"/>
+      <c r="BF3" s="13"/>
+      <c r="BG3" s="13"/>
+      <c r="BH3" s="13"/>
+      <c r="BI3" s="13"/>
+      <c r="BJ3" s="13"/>
+      <c r="BK3" s="13"/>
+      <c r="BL3" s="13"/>
+      <c r="BM3" s="13"/>
+      <c r="BN3" s="13"/>
+      <c r="BO3" s="13"/>
+      <c r="BP3" s="13"/>
+      <c r="BQ3" s="13"/>
+      <c r="BR3" s="13"/>
+      <c r="BS3" s="13"/>
+      <c r="BT3" s="13"/>
+      <c r="BU3" s="13"/>
+      <c r="BV3" s="13"/>
+      <c r="BW3" s="13"/>
+      <c r="BX3" s="13"/>
+      <c r="BY3" s="13"/>
+      <c r="BZ3" s="13"/>
+      <c r="CA3" s="13"/>
+      <c r="CB3" s="13"/>
+      <c r="CC3" s="13"/>
+      <c r="CD3" s="13"/>
+      <c r="CE3" s="13"/>
+      <c r="CF3" s="13"/>
+      <c r="CG3" s="13"/>
+      <c r="CH3" s="13"/>
+      <c r="CI3" s="13"/>
+      <c r="CJ3" s="13"/>
+      <c r="CK3" s="13"/>
+      <c r="CL3" s="13"/>
+      <c r="CM3" s="13"/>
+      <c r="CN3" s="13"/>
+      <c r="CO3" s="13"/>
+      <c r="CP3" s="13"/>
+      <c r="CQ3" s="13"/>
+      <c r="CR3" s="13"/>
+      <c r="CS3" s="13"/>
+      <c r="CT3" s="13"/>
+      <c r="CU3" s="13"/>
+      <c r="CV3" s="13"/>
+      <c r="CW3" s="13"/>
+      <c r="CX3" s="13"/>
+      <c r="CY3" s="13"/>
+      <c r="CZ3" s="13"/>
+      <c r="DA3" s="13"/>
+      <c r="DB3" s="13"/>
+      <c r="DC3" s="13"/>
+      <c r="DD3" s="13"/>
+      <c r="DE3" s="13"/>
+      <c r="DF3" s="13"/>
+      <c r="DG3" s="13"/>
+      <c r="DH3" s="13"/>
+      <c r="DI3" s="13"/>
+      <c r="DJ3" s="13"/>
+      <c r="DK3" s="13"/>
+      <c r="DL3" s="13"/>
+      <c r="DM3" s="13"/>
+      <c r="DN3" s="13"/>
+      <c r="DO3" s="26"/>
     </row>
-    <row r="4" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
-        <f t="shared" si="1"/>
+    <row r="4" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="8">
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="30" t="s">
         <v>200</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -1913,7 +1928,7 @@
         <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G4" s="2">
         <v>4</v>
@@ -1934,134 +1949,137 @@
       <c r="M4" s="2">
         <v>1960</v>
       </c>
-      <c r="N4" s="15"/>
-      <c r="O4" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C4)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D4)," ","-")&amp;"-"&amp;E4&amp;"-"&amp;F4))</f>
+      <c r="N4" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="O4" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>55-e-hamilton-ave-campbell-ca-95008</v>
       </c>
-      <c r="P4" s="21" t="str">
+      <c r="P4" s="20" t="str">
         <f>IF(COUNTIF(O:O, TRIM(O4)) &gt; 1, "Yes", "---")</f>
         <v>Yes</v>
       </c>
       <c r="Q4" s="2"/>
-      <c r="R4" s="9" t="str">
+      <c r="R4" s="8" t="str">
         <f>IF(Q4="YES", COUNTIF($Q$2:Q4, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q4, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="T4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="13"/>
-      <c r="AF4" s="13"/>
-      <c r="AG4" s="13"/>
-      <c r="AH4" s="13"/>
-      <c r="AI4" s="13"/>
-      <c r="AJ4" s="13"/>
-      <c r="AK4" s="13"/>
-      <c r="AL4" s="13"/>
-      <c r="AM4" s="13"/>
-      <c r="AN4" s="13"/>
-      <c r="AO4" s="13"/>
-      <c r="AP4" s="13"/>
-      <c r="AQ4" s="13"/>
-      <c r="AR4" s="13"/>
-      <c r="AS4" s="13"/>
-      <c r="AT4" s="13"/>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="13"/>
-      <c r="AW4" s="13"/>
-      <c r="AX4" s="13"/>
-      <c r="AY4" s="13"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="13"/>
-      <c r="BB4" s="13"/>
-      <c r="BC4" s="13"/>
-      <c r="BD4" s="13"/>
-      <c r="BE4" s="13"/>
-      <c r="BF4" s="13"/>
-      <c r="BG4" s="13"/>
-      <c r="BH4" s="13"/>
-      <c r="BI4" s="13"/>
-      <c r="BJ4" s="13"/>
-      <c r="BK4" s="13"/>
-      <c r="BL4" s="13"/>
-      <c r="BM4" s="13"/>
-      <c r="BN4" s="13"/>
-      <c r="BO4" s="13"/>
-      <c r="BP4" s="13"/>
-      <c r="BQ4" s="13"/>
-      <c r="BR4" s="13"/>
-      <c r="BS4" s="13"/>
-      <c r="BT4" s="13"/>
-      <c r="BU4" s="13"/>
-      <c r="BV4" s="13"/>
-      <c r="BW4" s="13"/>
-      <c r="BX4" s="13"/>
-      <c r="BY4" s="13"/>
-      <c r="BZ4" s="13"/>
-      <c r="CA4" s="13"/>
-      <c r="CB4" s="13"/>
-      <c r="CC4" s="13"/>
-      <c r="CD4" s="13"/>
-      <c r="CE4" s="13"/>
-      <c r="CF4" s="13"/>
-      <c r="CG4" s="13"/>
-      <c r="CH4" s="13"/>
-      <c r="CI4" s="13"/>
-      <c r="CJ4" s="13"/>
-      <c r="CK4" s="13"/>
-      <c r="CL4" s="13"/>
-      <c r="CM4" s="13"/>
-      <c r="CN4" s="13"/>
-      <c r="CO4" s="13"/>
-      <c r="CP4" s="13"/>
-      <c r="CQ4" s="13"/>
-      <c r="CR4" s="13"/>
-      <c r="CS4" s="13"/>
-      <c r="CT4" s="13"/>
-      <c r="CU4" s="13"/>
-      <c r="CV4" s="13"/>
-      <c r="CW4" s="13"/>
-      <c r="CX4" s="13"/>
-      <c r="CY4" s="13"/>
-      <c r="CZ4" s="13"/>
-      <c r="DA4" s="13"/>
-      <c r="DB4" s="13"/>
-      <c r="DC4" s="13"/>
-      <c r="DD4" s="13"/>
-      <c r="DE4" s="13"/>
-      <c r="DF4" s="13"/>
-      <c r="DG4" s="13"/>
-      <c r="DH4" s="13"/>
-      <c r="DI4" s="13"/>
-      <c r="DJ4" s="13"/>
-      <c r="DK4" s="13"/>
-      <c r="DL4" s="13"/>
-      <c r="DM4" s="13"/>
-      <c r="DN4" s="13"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+      <c r="AI4" s="12"/>
+      <c r="AJ4" s="12"/>
+      <c r="AK4" s="12"/>
+      <c r="AL4" s="12"/>
+      <c r="AM4" s="12"/>
+      <c r="AN4" s="12"/>
+      <c r="AO4" s="12"/>
+      <c r="AP4" s="12"/>
+      <c r="AQ4" s="12"/>
+      <c r="AR4" s="12"/>
+      <c r="AS4" s="12"/>
+      <c r="AT4" s="12"/>
+      <c r="AU4" s="12"/>
+      <c r="AV4" s="12"/>
+      <c r="AW4" s="12"/>
+      <c r="AX4" s="12"/>
+      <c r="AY4" s="12"/>
+      <c r="AZ4" s="12"/>
+      <c r="BA4" s="12"/>
+      <c r="BB4" s="12"/>
+      <c r="BC4" s="12"/>
+      <c r="BD4" s="12"/>
+      <c r="BE4" s="12"/>
+      <c r="BF4" s="12"/>
+      <c r="BG4" s="12"/>
+      <c r="BH4" s="12"/>
+      <c r="BI4" s="12"/>
+      <c r="BJ4" s="12"/>
+      <c r="BK4" s="12"/>
+      <c r="BL4" s="12"/>
+      <c r="BM4" s="12"/>
+      <c r="BN4" s="12"/>
+      <c r="BO4" s="12"/>
+      <c r="BP4" s="12"/>
+      <c r="BQ4" s="12"/>
+      <c r="BR4" s="12"/>
+      <c r="BS4" s="12"/>
+      <c r="BT4" s="12"/>
+      <c r="BU4" s="12"/>
+      <c r="BV4" s="12"/>
+      <c r="BW4" s="12"/>
+      <c r="BX4" s="12"/>
+      <c r="BY4" s="12"/>
+      <c r="BZ4" s="12"/>
+      <c r="CA4" s="12"/>
+      <c r="CB4" s="12"/>
+      <c r="CC4" s="12"/>
+      <c r="CD4" s="12"/>
+      <c r="CE4" s="12"/>
+      <c r="CF4" s="12"/>
+      <c r="CG4" s="12"/>
+      <c r="CH4" s="12"/>
+      <c r="CI4" s="12"/>
+      <c r="CJ4" s="12"/>
+      <c r="CK4" s="12"/>
+      <c r="CL4" s="12"/>
+      <c r="CM4" s="12"/>
+      <c r="CN4" s="12"/>
+      <c r="CO4" s="12"/>
+      <c r="CP4" s="12"/>
+      <c r="CQ4" s="12"/>
+      <c r="CR4" s="12"/>
+      <c r="CS4" s="12"/>
+      <c r="CT4" s="12"/>
+      <c r="CU4" s="12"/>
+      <c r="CV4" s="12"/>
+      <c r="CW4" s="12"/>
+      <c r="CX4" s="12"/>
+      <c r="CY4" s="12"/>
+      <c r="CZ4" s="12"/>
+      <c r="DA4" s="12"/>
+      <c r="DB4" s="12"/>
+      <c r="DC4" s="12"/>
+      <c r="DD4" s="12"/>
+      <c r="DE4" s="12"/>
+      <c r="DF4" s="12"/>
+      <c r="DG4" s="12"/>
+      <c r="DH4" s="12"/>
+      <c r="DI4" s="12"/>
+      <c r="DJ4" s="12"/>
+      <c r="DK4" s="12"/>
+      <c r="DL4" s="12"/>
+      <c r="DM4" s="12"/>
+      <c r="DN4" s="12"/>
+      <c r="DO4" s="26"/>
     </row>
-    <row r="5" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20">
-        <f t="shared" si="1"/>
+    <row r="5" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="19">
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="29" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -2092,138 +2110,141 @@
       <c r="M5" s="5">
         <v>1931</v>
       </c>
-      <c r="N5" s="16"/>
-      <c r="O5" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C5)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D5)," ","-")&amp;"-"&amp;E5&amp;"-"&amp;F5))</f>
+      <c r="N5" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O5" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>3271-silver-creek-vista-san-jose-ca-95138</v>
       </c>
-      <c r="P5" s="22" t="str">
-        <f t="shared" ref="P5:P21" si="2">IF(COUNTIF(O:O, TRIM(O5)) &gt; 1, "Yes", "---")</f>
+      <c r="P5" s="21" t="str">
+        <f t="shared" ref="P5:P21" si="3">IF(COUNTIF(O:O, TRIM(O5)) &gt; 1, "Yes", "---")</f>
         <v>---</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R5" s="10" t="str">
+      <c r="R5" s="9" t="str">
         <f>IF(Q5="YES", COUNTIF($Q$2:Q5, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q5, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>2nd</v>
       </c>
-      <c r="S5" s="14" t="s">
+      <c r="S5" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="T5" s="14" t="s">
+      <c r="T5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="U5" s="14" t="s">
+      <c r="U5" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
-      <c r="AF5" s="14"/>
-      <c r="AG5" s="14"/>
-      <c r="AH5" s="14"/>
-      <c r="AI5" s="14"/>
-      <c r="AJ5" s="14"/>
-      <c r="AK5" s="14"/>
-      <c r="AL5" s="14"/>
-      <c r="AM5" s="14"/>
-      <c r="AN5" s="14"/>
-      <c r="AO5" s="14"/>
-      <c r="AP5" s="14"/>
-      <c r="AQ5" s="14"/>
-      <c r="AR5" s="14"/>
-      <c r="AS5" s="14"/>
-      <c r="AT5" s="14"/>
-      <c r="AU5" s="14"/>
-      <c r="AV5" s="14"/>
-      <c r="AW5" s="14"/>
-      <c r="AX5" s="14"/>
-      <c r="AY5" s="14"/>
-      <c r="AZ5" s="14"/>
-      <c r="BA5" s="14"/>
-      <c r="BB5" s="14"/>
-      <c r="BC5" s="14"/>
-      <c r="BD5" s="14"/>
-      <c r="BE5" s="14"/>
-      <c r="BF5" s="14"/>
-      <c r="BG5" s="14"/>
-      <c r="BH5" s="14"/>
-      <c r="BI5" s="14"/>
-      <c r="BJ5" s="14"/>
-      <c r="BK5" s="14"/>
-      <c r="BL5" s="14"/>
-      <c r="BM5" s="14"/>
-      <c r="BN5" s="14"/>
-      <c r="BO5" s="14"/>
-      <c r="BP5" s="14"/>
-      <c r="BQ5" s="14"/>
-      <c r="BR5" s="14"/>
-      <c r="BS5" s="14"/>
-      <c r="BT5" s="14"/>
-      <c r="BU5" s="14"/>
-      <c r="BV5" s="14"/>
-      <c r="BW5" s="14"/>
-      <c r="BX5" s="14"/>
-      <c r="BY5" s="14"/>
-      <c r="BZ5" s="14"/>
-      <c r="CA5" s="14"/>
-      <c r="CB5" s="14"/>
-      <c r="CC5" s="14"/>
-      <c r="CD5" s="14"/>
-      <c r="CE5" s="14"/>
-      <c r="CF5" s="14"/>
-      <c r="CG5" s="14"/>
-      <c r="CH5" s="14"/>
-      <c r="CI5" s="14"/>
-      <c r="CJ5" s="14"/>
-      <c r="CK5" s="14"/>
-      <c r="CL5" s="14"/>
-      <c r="CM5" s="14"/>
-      <c r="CN5" s="14"/>
-      <c r="CO5" s="14"/>
-      <c r="CP5" s="14"/>
-      <c r="CQ5" s="14"/>
-      <c r="CR5" s="14"/>
-      <c r="CS5" s="14"/>
-      <c r="CT5" s="14"/>
-      <c r="CU5" s="14"/>
-      <c r="CV5" s="14"/>
-      <c r="CW5" s="14"/>
-      <c r="CX5" s="14"/>
-      <c r="CY5" s="14"/>
-      <c r="CZ5" s="14"/>
-      <c r="DA5" s="14"/>
-      <c r="DB5" s="14"/>
-      <c r="DC5" s="14"/>
-      <c r="DD5" s="14"/>
-      <c r="DE5" s="14"/>
-      <c r="DF5" s="14"/>
-      <c r="DG5" s="14"/>
-      <c r="DH5" s="14"/>
-      <c r="DI5" s="14"/>
-      <c r="DJ5" s="14"/>
-      <c r="DK5" s="14"/>
-      <c r="DL5" s="14"/>
-      <c r="DM5" s="14"/>
-      <c r="DN5" s="14"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="13"/>
+      <c r="AF5" s="13"/>
+      <c r="AG5" s="13"/>
+      <c r="AH5" s="13"/>
+      <c r="AI5" s="13"/>
+      <c r="AJ5" s="13"/>
+      <c r="AK5" s="13"/>
+      <c r="AL5" s="13"/>
+      <c r="AM5" s="13"/>
+      <c r="AN5" s="13"/>
+      <c r="AO5" s="13"/>
+      <c r="AP5" s="13"/>
+      <c r="AQ5" s="13"/>
+      <c r="AR5" s="13"/>
+      <c r="AS5" s="13"/>
+      <c r="AT5" s="13"/>
+      <c r="AU5" s="13"/>
+      <c r="AV5" s="13"/>
+      <c r="AW5" s="13"/>
+      <c r="AX5" s="13"/>
+      <c r="AY5" s="13"/>
+      <c r="AZ5" s="13"/>
+      <c r="BA5" s="13"/>
+      <c r="BB5" s="13"/>
+      <c r="BC5" s="13"/>
+      <c r="BD5" s="13"/>
+      <c r="BE5" s="13"/>
+      <c r="BF5" s="13"/>
+      <c r="BG5" s="13"/>
+      <c r="BH5" s="13"/>
+      <c r="BI5" s="13"/>
+      <c r="BJ5" s="13"/>
+      <c r="BK5" s="13"/>
+      <c r="BL5" s="13"/>
+      <c r="BM5" s="13"/>
+      <c r="BN5" s="13"/>
+      <c r="BO5" s="13"/>
+      <c r="BP5" s="13"/>
+      <c r="BQ5" s="13"/>
+      <c r="BR5" s="13"/>
+      <c r="BS5" s="13"/>
+      <c r="BT5" s="13"/>
+      <c r="BU5" s="13"/>
+      <c r="BV5" s="13"/>
+      <c r="BW5" s="13"/>
+      <c r="BX5" s="13"/>
+      <c r="BY5" s="13"/>
+      <c r="BZ5" s="13"/>
+      <c r="CA5" s="13"/>
+      <c r="CB5" s="13"/>
+      <c r="CC5" s="13"/>
+      <c r="CD5" s="13"/>
+      <c r="CE5" s="13"/>
+      <c r="CF5" s="13"/>
+      <c r="CG5" s="13"/>
+      <c r="CH5" s="13"/>
+      <c r="CI5" s="13"/>
+      <c r="CJ5" s="13"/>
+      <c r="CK5" s="13"/>
+      <c r="CL5" s="13"/>
+      <c r="CM5" s="13"/>
+      <c r="CN5" s="13"/>
+      <c r="CO5" s="13"/>
+      <c r="CP5" s="13"/>
+      <c r="CQ5" s="13"/>
+      <c r="CR5" s="13"/>
+      <c r="CS5" s="13"/>
+      <c r="CT5" s="13"/>
+      <c r="CU5" s="13"/>
+      <c r="CV5" s="13"/>
+      <c r="CW5" s="13"/>
+      <c r="CX5" s="13"/>
+      <c r="CY5" s="13"/>
+      <c r="CZ5" s="13"/>
+      <c r="DA5" s="13"/>
+      <c r="DB5" s="13"/>
+      <c r="DC5" s="13"/>
+      <c r="DD5" s="13"/>
+      <c r="DE5" s="13"/>
+      <c r="DF5" s="13"/>
+      <c r="DG5" s="13"/>
+      <c r="DH5" s="13"/>
+      <c r="DI5" s="13"/>
+      <c r="DJ5" s="13"/>
+      <c r="DK5" s="13"/>
+      <c r="DL5" s="13"/>
+      <c r="DM5" s="13"/>
+      <c r="DN5" s="13"/>
+      <c r="DO5" s="26"/>
     </row>
-    <row r="6" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
-        <f t="shared" si="1"/>
+    <row r="6" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="30" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -2254,140 +2275,143 @@
       <c r="M6" s="2">
         <v>1990</v>
       </c>
-      <c r="N6" s="15"/>
-      <c r="O6" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C6)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D6)," ","-")&amp;"-"&amp;E6&amp;"-"&amp;F6))</f>
+      <c r="N6" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="O6" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>5045-crescent-park-manor-palo-alto-ca-94301</v>
       </c>
-      <c r="P6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P6" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="9" t="str">
+      <c r="R6" s="8" t="str">
         <f>IF(Q6="YES", COUNTIF($Q$2:Q6, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q6, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>3rd</v>
       </c>
-      <c r="S6" s="13" t="s">
+      <c r="S6" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="T6" s="13" t="s">
+      <c r="T6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="13" t="s">
+      <c r="U6" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="V6" s="13" t="s">
+      <c r="V6" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="13"/>
-      <c r="AO6" s="13"/>
-      <c r="AP6" s="13"/>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="13"/>
-      <c r="AS6" s="13"/>
-      <c r="AT6" s="13"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="13"/>
-      <c r="AX6" s="13"/>
-      <c r="AY6" s="13"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="13"/>
-      <c r="BC6" s="13"/>
-      <c r="BD6" s="13"/>
-      <c r="BE6" s="13"/>
-      <c r="BF6" s="13"/>
-      <c r="BG6" s="13"/>
-      <c r="BH6" s="13"/>
-      <c r="BI6" s="13"/>
-      <c r="BJ6" s="13"/>
-      <c r="BK6" s="13"/>
-      <c r="BL6" s="13"/>
-      <c r="BM6" s="13"/>
-      <c r="BN6" s="13"/>
-      <c r="BO6" s="13"/>
-      <c r="BP6" s="13"/>
-      <c r="BQ6" s="13"/>
-      <c r="BR6" s="13"/>
-      <c r="BS6" s="13"/>
-      <c r="BT6" s="13"/>
-      <c r="BU6" s="13"/>
-      <c r="BV6" s="13"/>
-      <c r="BW6" s="13"/>
-      <c r="BX6" s="13"/>
-      <c r="BY6" s="13"/>
-      <c r="BZ6" s="13"/>
-      <c r="CA6" s="13"/>
-      <c r="CB6" s="13"/>
-      <c r="CC6" s="13"/>
-      <c r="CD6" s="13"/>
-      <c r="CE6" s="13"/>
-      <c r="CF6" s="13"/>
-      <c r="CG6" s="13"/>
-      <c r="CH6" s="13"/>
-      <c r="CI6" s="13"/>
-      <c r="CJ6" s="13"/>
-      <c r="CK6" s="13"/>
-      <c r="CL6" s="13"/>
-      <c r="CM6" s="13"/>
-      <c r="CN6" s="13"/>
-      <c r="CO6" s="13"/>
-      <c r="CP6" s="13"/>
-      <c r="CQ6" s="13"/>
-      <c r="CR6" s="13"/>
-      <c r="CS6" s="13"/>
-      <c r="CT6" s="13"/>
-      <c r="CU6" s="13"/>
-      <c r="CV6" s="13"/>
-      <c r="CW6" s="13"/>
-      <c r="CX6" s="13"/>
-      <c r="CY6" s="13"/>
-      <c r="CZ6" s="13"/>
-      <c r="DA6" s="13"/>
-      <c r="DB6" s="13"/>
-      <c r="DC6" s="13"/>
-      <c r="DD6" s="13"/>
-      <c r="DE6" s="13"/>
-      <c r="DF6" s="13"/>
-      <c r="DG6" s="13"/>
-      <c r="DH6" s="13"/>
-      <c r="DI6" s="13"/>
-      <c r="DJ6" s="13"/>
-      <c r="DK6" s="13"/>
-      <c r="DL6" s="13"/>
-      <c r="DM6" s="13"/>
-      <c r="DN6" s="13"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="12"/>
+      <c r="AG6" s="12"/>
+      <c r="AH6" s="12"/>
+      <c r="AI6" s="12"/>
+      <c r="AJ6" s="12"/>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="12"/>
+      <c r="AM6" s="12"/>
+      <c r="AN6" s="12"/>
+      <c r="AO6" s="12"/>
+      <c r="AP6" s="12"/>
+      <c r="AQ6" s="12"/>
+      <c r="AR6" s="12"/>
+      <c r="AS6" s="12"/>
+      <c r="AT6" s="12"/>
+      <c r="AU6" s="12"/>
+      <c r="AV6" s="12"/>
+      <c r="AW6" s="12"/>
+      <c r="AX6" s="12"/>
+      <c r="AY6" s="12"/>
+      <c r="AZ6" s="12"/>
+      <c r="BA6" s="12"/>
+      <c r="BB6" s="12"/>
+      <c r="BC6" s="12"/>
+      <c r="BD6" s="12"/>
+      <c r="BE6" s="12"/>
+      <c r="BF6" s="12"/>
+      <c r="BG6" s="12"/>
+      <c r="BH6" s="12"/>
+      <c r="BI6" s="12"/>
+      <c r="BJ6" s="12"/>
+      <c r="BK6" s="12"/>
+      <c r="BL6" s="12"/>
+      <c r="BM6" s="12"/>
+      <c r="BN6" s="12"/>
+      <c r="BO6" s="12"/>
+      <c r="BP6" s="12"/>
+      <c r="BQ6" s="12"/>
+      <c r="BR6" s="12"/>
+      <c r="BS6" s="12"/>
+      <c r="BT6" s="12"/>
+      <c r="BU6" s="12"/>
+      <c r="BV6" s="12"/>
+      <c r="BW6" s="12"/>
+      <c r="BX6" s="12"/>
+      <c r="BY6" s="12"/>
+      <c r="BZ6" s="12"/>
+      <c r="CA6" s="12"/>
+      <c r="CB6" s="12"/>
+      <c r="CC6" s="12"/>
+      <c r="CD6" s="12"/>
+      <c r="CE6" s="12"/>
+      <c r="CF6" s="12"/>
+      <c r="CG6" s="12"/>
+      <c r="CH6" s="12"/>
+      <c r="CI6" s="12"/>
+      <c r="CJ6" s="12"/>
+      <c r="CK6" s="12"/>
+      <c r="CL6" s="12"/>
+      <c r="CM6" s="12"/>
+      <c r="CN6" s="12"/>
+      <c r="CO6" s="12"/>
+      <c r="CP6" s="12"/>
+      <c r="CQ6" s="12"/>
+      <c r="CR6" s="12"/>
+      <c r="CS6" s="12"/>
+      <c r="CT6" s="12"/>
+      <c r="CU6" s="12"/>
+      <c r="CV6" s="12"/>
+      <c r="CW6" s="12"/>
+      <c r="CX6" s="12"/>
+      <c r="CY6" s="12"/>
+      <c r="CZ6" s="12"/>
+      <c r="DA6" s="12"/>
+      <c r="DB6" s="12"/>
+      <c r="DC6" s="12"/>
+      <c r="DD6" s="12"/>
+      <c r="DE6" s="12"/>
+      <c r="DF6" s="12"/>
+      <c r="DG6" s="12"/>
+      <c r="DH6" s="12"/>
+      <c r="DI6" s="12"/>
+      <c r="DJ6" s="12"/>
+      <c r="DK6" s="12"/>
+      <c r="DL6" s="12"/>
+      <c r="DM6" s="12"/>
+      <c r="DN6" s="12"/>
+      <c r="DO6" s="26"/>
     </row>
-    <row r="7" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="20">
-        <f t="shared" si="1"/>
+    <row r="7" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="19">
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="29" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
@@ -2418,142 +2442,145 @@
       <c r="M7" s="5">
         <v>2001</v>
       </c>
-      <c r="N7" s="16"/>
-      <c r="O7" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C7)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D7)," ","-")&amp;"-"&amp;E7&amp;"-"&amp;F7))</f>
+      <c r="N7" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O7" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>3044-almaden-country-club-san-jose-ca-95120</v>
       </c>
-      <c r="P7" s="22" t="str">
-        <f t="shared" si="2"/>
+      <c r="P7" s="21" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R7" s="10" t="str">
+      <c r="R7" s="9" t="str">
         <f>IF(Q7="YES", COUNTIF($Q$2:Q7, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q7, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v>4th</v>
       </c>
-      <c r="S7" s="14" t="s">
+      <c r="S7" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="T7" s="14" t="s">
+      <c r="T7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="U7" s="14" t="s">
+      <c r="U7" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="V7" s="14" t="s">
+      <c r="V7" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="W7" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
-      <c r="AD7" s="14"/>
-      <c r="AE7" s="14"/>
-      <c r="AF7" s="14"/>
-      <c r="AG7" s="14"/>
-      <c r="AH7" s="14"/>
-      <c r="AI7" s="14"/>
-      <c r="AJ7" s="14"/>
-      <c r="AK7" s="14"/>
-      <c r="AL7" s="14"/>
-      <c r="AM7" s="14"/>
-      <c r="AN7" s="14"/>
-      <c r="AO7" s="14"/>
-      <c r="AP7" s="14"/>
-      <c r="AQ7" s="14"/>
-      <c r="AR7" s="14"/>
-      <c r="AS7" s="14"/>
-      <c r="AT7" s="14"/>
-      <c r="AU7" s="14"/>
-      <c r="AV7" s="14"/>
-      <c r="AW7" s="14"/>
-      <c r="AX7" s="14"/>
-      <c r="AY7" s="14"/>
-      <c r="AZ7" s="14"/>
-      <c r="BA7" s="14"/>
-      <c r="BB7" s="14"/>
-      <c r="BC7" s="14"/>
-      <c r="BD7" s="14"/>
-      <c r="BE7" s="14"/>
-      <c r="BF7" s="14"/>
-      <c r="BG7" s="14"/>
-      <c r="BH7" s="14"/>
-      <c r="BI7" s="14"/>
-      <c r="BJ7" s="14"/>
-      <c r="BK7" s="14"/>
-      <c r="BL7" s="14"/>
-      <c r="BM7" s="14"/>
-      <c r="BN7" s="14"/>
-      <c r="BO7" s="14"/>
-      <c r="BP7" s="14"/>
-      <c r="BQ7" s="14"/>
-      <c r="BR7" s="14"/>
-      <c r="BS7" s="14"/>
-      <c r="BT7" s="14"/>
-      <c r="BU7" s="14"/>
-      <c r="BV7" s="14"/>
-      <c r="BW7" s="14"/>
-      <c r="BX7" s="14"/>
-      <c r="BY7" s="14"/>
-      <c r="BZ7" s="14"/>
-      <c r="CA7" s="14"/>
-      <c r="CB7" s="14"/>
-      <c r="CC7" s="14"/>
-      <c r="CD7" s="14"/>
-      <c r="CE7" s="14"/>
-      <c r="CF7" s="14"/>
-      <c r="CG7" s="14"/>
-      <c r="CH7" s="14"/>
-      <c r="CI7" s="14"/>
-      <c r="CJ7" s="14"/>
-      <c r="CK7" s="14"/>
-      <c r="CL7" s="14"/>
-      <c r="CM7" s="14"/>
-      <c r="CN7" s="14"/>
-      <c r="CO7" s="14"/>
-      <c r="CP7" s="14"/>
-      <c r="CQ7" s="14"/>
-      <c r="CR7" s="14"/>
-      <c r="CS7" s="14"/>
-      <c r="CT7" s="14"/>
-      <c r="CU7" s="14"/>
-      <c r="CV7" s="14"/>
-      <c r="CW7" s="14"/>
-      <c r="CX7" s="14"/>
-      <c r="CY7" s="14"/>
-      <c r="CZ7" s="14"/>
-      <c r="DA7" s="14"/>
-      <c r="DB7" s="14"/>
-      <c r="DC7" s="14"/>
-      <c r="DD7" s="14"/>
-      <c r="DE7" s="14"/>
-      <c r="DF7" s="14"/>
-      <c r="DG7" s="14"/>
-      <c r="DH7" s="14"/>
-      <c r="DI7" s="14"/>
-      <c r="DJ7" s="14"/>
-      <c r="DK7" s="14"/>
-      <c r="DL7" s="14"/>
-      <c r="DM7" s="14"/>
-      <c r="DN7" s="14"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="13"/>
+      <c r="AI7" s="13"/>
+      <c r="AJ7" s="13"/>
+      <c r="AK7" s="13"/>
+      <c r="AL7" s="13"/>
+      <c r="AM7" s="13"/>
+      <c r="AN7" s="13"/>
+      <c r="AO7" s="13"/>
+      <c r="AP7" s="13"/>
+      <c r="AQ7" s="13"/>
+      <c r="AR7" s="13"/>
+      <c r="AS7" s="13"/>
+      <c r="AT7" s="13"/>
+      <c r="AU7" s="13"/>
+      <c r="AV7" s="13"/>
+      <c r="AW7" s="13"/>
+      <c r="AX7" s="13"/>
+      <c r="AY7" s="13"/>
+      <c r="AZ7" s="13"/>
+      <c r="BA7" s="13"/>
+      <c r="BB7" s="13"/>
+      <c r="BC7" s="13"/>
+      <c r="BD7" s="13"/>
+      <c r="BE7" s="13"/>
+      <c r="BF7" s="13"/>
+      <c r="BG7" s="13"/>
+      <c r="BH7" s="13"/>
+      <c r="BI7" s="13"/>
+      <c r="BJ7" s="13"/>
+      <c r="BK7" s="13"/>
+      <c r="BL7" s="13"/>
+      <c r="BM7" s="13"/>
+      <c r="BN7" s="13"/>
+      <c r="BO7" s="13"/>
+      <c r="BP7" s="13"/>
+      <c r="BQ7" s="13"/>
+      <c r="BR7" s="13"/>
+      <c r="BS7" s="13"/>
+      <c r="BT7" s="13"/>
+      <c r="BU7" s="13"/>
+      <c r="BV7" s="13"/>
+      <c r="BW7" s="13"/>
+      <c r="BX7" s="13"/>
+      <c r="BY7" s="13"/>
+      <c r="BZ7" s="13"/>
+      <c r="CA7" s="13"/>
+      <c r="CB7" s="13"/>
+      <c r="CC7" s="13"/>
+      <c r="CD7" s="13"/>
+      <c r="CE7" s="13"/>
+      <c r="CF7" s="13"/>
+      <c r="CG7" s="13"/>
+      <c r="CH7" s="13"/>
+      <c r="CI7" s="13"/>
+      <c r="CJ7" s="13"/>
+      <c r="CK7" s="13"/>
+      <c r="CL7" s="13"/>
+      <c r="CM7" s="13"/>
+      <c r="CN7" s="13"/>
+      <c r="CO7" s="13"/>
+      <c r="CP7" s="13"/>
+      <c r="CQ7" s="13"/>
+      <c r="CR7" s="13"/>
+      <c r="CS7" s="13"/>
+      <c r="CT7" s="13"/>
+      <c r="CU7" s="13"/>
+      <c r="CV7" s="13"/>
+      <c r="CW7" s="13"/>
+      <c r="CX7" s="13"/>
+      <c r="CY7" s="13"/>
+      <c r="CZ7" s="13"/>
+      <c r="DA7" s="13"/>
+      <c r="DB7" s="13"/>
+      <c r="DC7" s="13"/>
+      <c r="DD7" s="13"/>
+      <c r="DE7" s="13"/>
+      <c r="DF7" s="13"/>
+      <c r="DG7" s="13"/>
+      <c r="DH7" s="13"/>
+      <c r="DI7" s="13"/>
+      <c r="DJ7" s="13"/>
+      <c r="DK7" s="13"/>
+      <c r="DL7" s="13"/>
+      <c r="DM7" s="13"/>
+      <c r="DN7" s="13"/>
+      <c r="DO7" s="26"/>
     </row>
-    <row r="8" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9">
-        <f t="shared" si="1"/>
+    <row r="8" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="30" t="s">
         <v>33</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2584,170 +2611,173 @@
       <c r="M8" s="2">
         <v>2006</v>
       </c>
-      <c r="N8" s="15"/>
-      <c r="O8" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C8)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D8)," ","-")&amp;"-"&amp;E8&amp;"-"&amp;F8))</f>
+      <c r="N8" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="O8" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>14550-big-basin-way-saratoga-ca-95070</v>
       </c>
-      <c r="P8" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P8" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q8" s="2"/>
-      <c r="R8" s="9" t="str">
+      <c r="R8" s="8" t="str">
         <f>IF(Q8="YES", COUNTIF($Q$2:Q8, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q8, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="S8" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="T8" s="13" t="s">
+      <c r="T8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="U8" s="13" t="s">
+      <c r="U8" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="V8" s="13" t="s">
+      <c r="V8" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="W8" s="13" t="s">
+      <c r="W8" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="X8" s="13" t="s">
+      <c r="X8" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="Y8" s="13" t="s">
+      <c r="Y8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="Z8" s="13" t="s">
+      <c r="Z8" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="AA8" s="13" t="s">
+      <c r="AA8" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="AB8" s="13" t="s">
+      <c r="AB8" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="AC8" s="13" t="s">
+      <c r="AC8" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="AD8" s="13" t="s">
+      <c r="AD8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AE8" s="13" t="s">
+      <c r="AE8" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="AF8" s="13" t="s">
+      <c r="AF8" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="AG8" s="13" t="s">
+      <c r="AG8" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="AH8" s="13" t="s">
+      <c r="AH8" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="AI8" s="13" t="s">
+      <c r="AI8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AJ8" s="13" t="s">
+      <c r="AJ8" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="AK8" s="13" t="s">
+      <c r="AK8" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="AL8" s="13" t="s">
+      <c r="AL8" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="AM8" s="13"/>
-      <c r="AN8" s="13"/>
-      <c r="AO8" s="13"/>
-      <c r="AP8" s="13"/>
-      <c r="AQ8" s="13"/>
-      <c r="AR8" s="13"/>
-      <c r="AS8" s="13"/>
-      <c r="AT8" s="13"/>
-      <c r="AU8" s="13"/>
-      <c r="AV8" s="13"/>
-      <c r="AW8" s="13"/>
-      <c r="AX8" s="13"/>
-      <c r="AY8" s="13"/>
-      <c r="AZ8" s="13"/>
-      <c r="BA8" s="13"/>
-      <c r="BB8" s="13"/>
-      <c r="BC8" s="13"/>
-      <c r="BD8" s="13"/>
-      <c r="BE8" s="13"/>
-      <c r="BF8" s="13"/>
-      <c r="BG8" s="13"/>
-      <c r="BH8" s="13"/>
-      <c r="BI8" s="13"/>
-      <c r="BJ8" s="13"/>
-      <c r="BK8" s="13"/>
-      <c r="BL8" s="13"/>
-      <c r="BM8" s="13"/>
-      <c r="BN8" s="13"/>
-      <c r="BO8" s="13"/>
-      <c r="BP8" s="13"/>
-      <c r="BQ8" s="13"/>
-      <c r="BR8" s="13"/>
-      <c r="BS8" s="13"/>
-      <c r="BT8" s="13"/>
-      <c r="BU8" s="13"/>
-      <c r="BV8" s="13"/>
-      <c r="BW8" s="13"/>
-      <c r="BX8" s="13"/>
-      <c r="BY8" s="13"/>
-      <c r="BZ8" s="13"/>
-      <c r="CA8" s="13"/>
-      <c r="CB8" s="13"/>
-      <c r="CC8" s="13"/>
-      <c r="CD8" s="13"/>
-      <c r="CE8" s="13"/>
-      <c r="CF8" s="13"/>
-      <c r="CG8" s="13"/>
-      <c r="CH8" s="13"/>
-      <c r="CI8" s="13"/>
-      <c r="CJ8" s="13"/>
-      <c r="CK8" s="13"/>
-      <c r="CL8" s="13"/>
-      <c r="CM8" s="13"/>
-      <c r="CN8" s="13"/>
-      <c r="CO8" s="13"/>
-      <c r="CP8" s="13"/>
-      <c r="CQ8" s="13"/>
-      <c r="CR8" s="13"/>
-      <c r="CS8" s="13"/>
-      <c r="CT8" s="13"/>
-      <c r="CU8" s="13"/>
-      <c r="CV8" s="13"/>
-      <c r="CW8" s="13"/>
-      <c r="CX8" s="13"/>
-      <c r="CY8" s="13"/>
-      <c r="CZ8" s="13"/>
-      <c r="DA8" s="13"/>
-      <c r="DB8" s="13"/>
-      <c r="DC8" s="13"/>
-      <c r="DD8" s="13"/>
-      <c r="DE8" s="13"/>
-      <c r="DF8" s="13"/>
-      <c r="DG8" s="13"/>
-      <c r="DH8" s="13"/>
-      <c r="DI8" s="13"/>
-      <c r="DJ8" s="13"/>
-      <c r="DK8" s="13"/>
-      <c r="DL8" s="13"/>
-      <c r="DM8" s="13"/>
-      <c r="DN8" s="13"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+      <c r="BI8" s="12"/>
+      <c r="BJ8" s="12"/>
+      <c r="BK8" s="12"/>
+      <c r="BL8" s="12"/>
+      <c r="BM8" s="12"/>
+      <c r="BN8" s="12"/>
+      <c r="BO8" s="12"/>
+      <c r="BP8" s="12"/>
+      <c r="BQ8" s="12"/>
+      <c r="BR8" s="12"/>
+      <c r="BS8" s="12"/>
+      <c r="BT8" s="12"/>
+      <c r="BU8" s="12"/>
+      <c r="BV8" s="12"/>
+      <c r="BW8" s="12"/>
+      <c r="BX8" s="12"/>
+      <c r="BY8" s="12"/>
+      <c r="BZ8" s="12"/>
+      <c r="CA8" s="12"/>
+      <c r="CB8" s="12"/>
+      <c r="CC8" s="12"/>
+      <c r="CD8" s="12"/>
+      <c r="CE8" s="12"/>
+      <c r="CF8" s="12"/>
+      <c r="CG8" s="12"/>
+      <c r="CH8" s="12"/>
+      <c r="CI8" s="12"/>
+      <c r="CJ8" s="12"/>
+      <c r="CK8" s="12"/>
+      <c r="CL8" s="12"/>
+      <c r="CM8" s="12"/>
+      <c r="CN8" s="12"/>
+      <c r="CO8" s="12"/>
+      <c r="CP8" s="12"/>
+      <c r="CQ8" s="12"/>
+      <c r="CR8" s="12"/>
+      <c r="CS8" s="12"/>
+      <c r="CT8" s="12"/>
+      <c r="CU8" s="12"/>
+      <c r="CV8" s="12"/>
+      <c r="CW8" s="12"/>
+      <c r="CX8" s="12"/>
+      <c r="CY8" s="12"/>
+      <c r="CZ8" s="12"/>
+      <c r="DA8" s="12"/>
+      <c r="DB8" s="12"/>
+      <c r="DC8" s="12"/>
+      <c r="DD8" s="12"/>
+      <c r="DE8" s="12"/>
+      <c r="DF8" s="12"/>
+      <c r="DG8" s="12"/>
+      <c r="DH8" s="12"/>
+      <c r="DI8" s="12"/>
+      <c r="DJ8" s="12"/>
+      <c r="DK8" s="12"/>
+      <c r="DL8" s="12"/>
+      <c r="DM8" s="12"/>
+      <c r="DN8" s="12"/>
+      <c r="DO8" s="26"/>
     </row>
-    <row r="9" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20">
-        <f t="shared" si="1"/>
+    <row r="9" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="6" t="s">
@@ -2778,170 +2808,173 @@
       <c r="M9" s="5">
         <v>2021</v>
       </c>
-      <c r="N9" s="16"/>
-      <c r="O9" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C9)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D9)," ","-")&amp;"-"&amp;E9&amp;"-"&amp;F9))</f>
+      <c r="N9" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O9" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>210-shannon-road-los-gatos-ca-95032</v>
       </c>
-      <c r="P9" s="22" t="str">
-        <f t="shared" si="2"/>
+      <c r="P9" s="21" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q9" s="5"/>
-      <c r="R9" s="10" t="str">
+      <c r="R9" s="9" t="str">
         <f>IF(Q9="YES", COUNTIF($Q$2:Q9, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q9, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="S9" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="T9" s="14" t="s">
+      <c r="T9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="14" t="s">
+      <c r="U9" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="V9" s="14" t="s">
+      <c r="V9" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="W9" s="14" t="s">
+      <c r="W9" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="X9" s="14" t="s">
+      <c r="X9" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="Y9" s="14" t="s">
+      <c r="Y9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="Z9" s="14" t="s">
+      <c r="Z9" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="AA9" s="14" t="s">
+      <c r="AA9" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AB9" s="14" t="s">
+      <c r="AB9" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AC9" s="14" t="s">
+      <c r="AC9" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="AD9" s="14" t="s">
+      <c r="AD9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="AE9" s="14" t="s">
+      <c r="AE9" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="AF9" s="14" t="s">
+      <c r="AF9" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AG9" s="14" t="s">
+      <c r="AG9" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AH9" s="14" t="s">
+      <c r="AH9" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="AI9" s="14" t="s">
+      <c r="AI9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="AJ9" s="14" t="s">
+      <c r="AJ9" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="AK9" s="14" t="s">
+      <c r="AK9" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AL9" s="14" t="s">
+      <c r="AL9" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AM9" s="14"/>
-      <c r="AN9" s="14"/>
-      <c r="AO9" s="14"/>
-      <c r="AP9" s="14"/>
-      <c r="AQ9" s="14"/>
-      <c r="AR9" s="14"/>
-      <c r="AS9" s="14"/>
-      <c r="AT9" s="14"/>
-      <c r="AU9" s="14"/>
-      <c r="AV9" s="14"/>
-      <c r="AW9" s="14"/>
-      <c r="AX9" s="14"/>
-      <c r="AY9" s="14"/>
-      <c r="AZ9" s="14"/>
-      <c r="BA9" s="14"/>
-      <c r="BB9" s="14"/>
-      <c r="BC9" s="14"/>
-      <c r="BD9" s="14"/>
-      <c r="BE9" s="14"/>
-      <c r="BF9" s="14"/>
-      <c r="BG9" s="14"/>
-      <c r="BH9" s="14"/>
-      <c r="BI9" s="14"/>
-      <c r="BJ9" s="14"/>
-      <c r="BK9" s="14"/>
-      <c r="BL9" s="14"/>
-      <c r="BM9" s="14"/>
-      <c r="BN9" s="14"/>
-      <c r="BO9" s="14"/>
-      <c r="BP9" s="14"/>
-      <c r="BQ9" s="14"/>
-      <c r="BR9" s="14"/>
-      <c r="BS9" s="14"/>
-      <c r="BT9" s="14"/>
-      <c r="BU9" s="14"/>
-      <c r="BV9" s="14"/>
-      <c r="BW9" s="14"/>
-      <c r="BX9" s="14"/>
-      <c r="BY9" s="14"/>
-      <c r="BZ9" s="14"/>
-      <c r="CA9" s="14"/>
-      <c r="CB9" s="14"/>
-      <c r="CC9" s="14"/>
-      <c r="CD9" s="14"/>
-      <c r="CE9" s="14"/>
-      <c r="CF9" s="14"/>
-      <c r="CG9" s="14"/>
-      <c r="CH9" s="14"/>
-      <c r="CI9" s="14"/>
-      <c r="CJ9" s="14"/>
-      <c r="CK9" s="14"/>
-      <c r="CL9" s="14"/>
-      <c r="CM9" s="14"/>
-      <c r="CN9" s="14"/>
-      <c r="CO9" s="14"/>
-      <c r="CP9" s="14"/>
-      <c r="CQ9" s="14"/>
-      <c r="CR9" s="14"/>
-      <c r="CS9" s="14"/>
-      <c r="CT9" s="14"/>
-      <c r="CU9" s="14"/>
-      <c r="CV9" s="14"/>
-      <c r="CW9" s="14"/>
-      <c r="CX9" s="14"/>
-      <c r="CY9" s="14"/>
-      <c r="CZ9" s="14"/>
-      <c r="DA9" s="14"/>
-      <c r="DB9" s="14"/>
-      <c r="DC9" s="14"/>
-      <c r="DD9" s="14"/>
-      <c r="DE9" s="14"/>
-      <c r="DF9" s="14"/>
-      <c r="DG9" s="14"/>
-      <c r="DH9" s="14"/>
-      <c r="DI9" s="14"/>
-      <c r="DJ9" s="14"/>
-      <c r="DK9" s="14"/>
-      <c r="DL9" s="14"/>
-      <c r="DM9" s="14"/>
-      <c r="DN9" s="14"/>
+      <c r="AM9" s="13"/>
+      <c r="AN9" s="13"/>
+      <c r="AO9" s="13"/>
+      <c r="AP9" s="13"/>
+      <c r="AQ9" s="13"/>
+      <c r="AR9" s="13"/>
+      <c r="AS9" s="13"/>
+      <c r="AT9" s="13"/>
+      <c r="AU9" s="13"/>
+      <c r="AV9" s="13"/>
+      <c r="AW9" s="13"/>
+      <c r="AX9" s="13"/>
+      <c r="AY9" s="13"/>
+      <c r="AZ9" s="13"/>
+      <c r="BA9" s="13"/>
+      <c r="BB9" s="13"/>
+      <c r="BC9" s="13"/>
+      <c r="BD9" s="13"/>
+      <c r="BE9" s="13"/>
+      <c r="BF9" s="13"/>
+      <c r="BG9" s="13"/>
+      <c r="BH9" s="13"/>
+      <c r="BI9" s="13"/>
+      <c r="BJ9" s="13"/>
+      <c r="BK9" s="13"/>
+      <c r="BL9" s="13"/>
+      <c r="BM9" s="13"/>
+      <c r="BN9" s="13"/>
+      <c r="BO9" s="13"/>
+      <c r="BP9" s="13"/>
+      <c r="BQ9" s="13"/>
+      <c r="BR9" s="13"/>
+      <c r="BS9" s="13"/>
+      <c r="BT9" s="13"/>
+      <c r="BU9" s="13"/>
+      <c r="BV9" s="13"/>
+      <c r="BW9" s="13"/>
+      <c r="BX9" s="13"/>
+      <c r="BY9" s="13"/>
+      <c r="BZ9" s="13"/>
+      <c r="CA9" s="13"/>
+      <c r="CB9" s="13"/>
+      <c r="CC9" s="13"/>
+      <c r="CD9" s="13"/>
+      <c r="CE9" s="13"/>
+      <c r="CF9" s="13"/>
+      <c r="CG9" s="13"/>
+      <c r="CH9" s="13"/>
+      <c r="CI9" s="13"/>
+      <c r="CJ9" s="13"/>
+      <c r="CK9" s="13"/>
+      <c r="CL9" s="13"/>
+      <c r="CM9" s="13"/>
+      <c r="CN9" s="13"/>
+      <c r="CO9" s="13"/>
+      <c r="CP9" s="13"/>
+      <c r="CQ9" s="13"/>
+      <c r="CR9" s="13"/>
+      <c r="CS9" s="13"/>
+      <c r="CT9" s="13"/>
+      <c r="CU9" s="13"/>
+      <c r="CV9" s="13"/>
+      <c r="CW9" s="13"/>
+      <c r="CX9" s="13"/>
+      <c r="CY9" s="13"/>
+      <c r="CZ9" s="13"/>
+      <c r="DA9" s="13"/>
+      <c r="DB9" s="13"/>
+      <c r="DC9" s="13"/>
+      <c r="DD9" s="13"/>
+      <c r="DE9" s="13"/>
+      <c r="DF9" s="13"/>
+      <c r="DG9" s="13"/>
+      <c r="DH9" s="13"/>
+      <c r="DI9" s="13"/>
+      <c r="DJ9" s="13"/>
+      <c r="DK9" s="13"/>
+      <c r="DL9" s="13"/>
+      <c r="DM9" s="13"/>
+      <c r="DN9" s="13"/>
+      <c r="DO9" s="26"/>
     </row>
-    <row r="10" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9">
-        <f t="shared" si="1"/>
+    <row r="10" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="30" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -2972,170 +3005,173 @@
       <c r="M10" s="2">
         <v>1945</v>
       </c>
-      <c r="N10" s="15"/>
-      <c r="O10" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C10)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D10)," ","-")&amp;"-"&amp;E10&amp;"-"&amp;F10))</f>
+      <c r="N10" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="O10" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>16200-greenwood-lane-monte-sereno-ca-95030</v>
       </c>
-      <c r="P10" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P10" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q10" s="2"/>
-      <c r="R10" s="9" t="str">
+      <c r="R10" s="8" t="str">
         <f>IF(Q10="YES", COUNTIF($Q$2:Q10, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q10, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S10" s="13" t="s">
+      <c r="S10" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="T10" s="13" t="s">
+      <c r="T10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="U10" s="13" t="s">
+      <c r="U10" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="V10" s="13" t="s">
+      <c r="V10" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="W10" s="13" t="s">
+      <c r="W10" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="X10" s="13" t="s">
+      <c r="X10" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="Y10" s="13" t="s">
+      <c r="Y10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="Z10" s="13" t="s">
+      <c r="Z10" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="AA10" s="13" t="s">
+      <c r="AA10" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="AB10" s="13" t="s">
+      <c r="AB10" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="AC10" s="13" t="s">
+      <c r="AC10" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="AD10" s="13" t="s">
+      <c r="AD10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AE10" s="13" t="s">
+      <c r="AE10" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="AF10" s="13" t="s">
+      <c r="AF10" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="AG10" s="13" t="s">
+      <c r="AG10" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="AH10" s="13" t="s">
+      <c r="AH10" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="AI10" s="13" t="s">
+      <c r="AI10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AJ10" s="13" t="s">
+      <c r="AJ10" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="AK10" s="13" t="s">
+      <c r="AK10" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="AL10" s="13" t="s">
+      <c r="AL10" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="AM10" s="13"/>
-      <c r="AN10" s="13"/>
-      <c r="AO10" s="13"/>
-      <c r="AP10" s="13"/>
-      <c r="AQ10" s="13"/>
-      <c r="AR10" s="13"/>
-      <c r="AS10" s="13"/>
-      <c r="AT10" s="13"/>
-      <c r="AU10" s="13"/>
-      <c r="AV10" s="13"/>
-      <c r="AW10" s="13"/>
-      <c r="AX10" s="13"/>
-      <c r="AY10" s="13"/>
-      <c r="AZ10" s="13"/>
-      <c r="BA10" s="13"/>
-      <c r="BB10" s="13"/>
-      <c r="BC10" s="13"/>
-      <c r="BD10" s="13"/>
-      <c r="BE10" s="13"/>
-      <c r="BF10" s="13"/>
-      <c r="BG10" s="13"/>
-      <c r="BH10" s="13"/>
-      <c r="BI10" s="13"/>
-      <c r="BJ10" s="13"/>
-      <c r="BK10" s="13"/>
-      <c r="BL10" s="13"/>
-      <c r="BM10" s="13"/>
-      <c r="BN10" s="13"/>
-      <c r="BO10" s="13"/>
-      <c r="BP10" s="13"/>
-      <c r="BQ10" s="13"/>
-      <c r="BR10" s="13"/>
-      <c r="BS10" s="13"/>
-      <c r="BT10" s="13"/>
-      <c r="BU10" s="13"/>
-      <c r="BV10" s="13"/>
-      <c r="BW10" s="13"/>
-      <c r="BX10" s="13"/>
-      <c r="BY10" s="13"/>
-      <c r="BZ10" s="13"/>
-      <c r="CA10" s="13"/>
-      <c r="CB10" s="13"/>
-      <c r="CC10" s="13"/>
-      <c r="CD10" s="13"/>
-      <c r="CE10" s="13"/>
-      <c r="CF10" s="13"/>
-      <c r="CG10" s="13"/>
-      <c r="CH10" s="13"/>
-      <c r="CI10" s="13"/>
-      <c r="CJ10" s="13"/>
-      <c r="CK10" s="13"/>
-      <c r="CL10" s="13"/>
-      <c r="CM10" s="13"/>
-      <c r="CN10" s="13"/>
-      <c r="CO10" s="13"/>
-      <c r="CP10" s="13"/>
-      <c r="CQ10" s="13"/>
-      <c r="CR10" s="13"/>
-      <c r="CS10" s="13"/>
-      <c r="CT10" s="13"/>
-      <c r="CU10" s="13"/>
-      <c r="CV10" s="13"/>
-      <c r="CW10" s="13"/>
-      <c r="CX10" s="13"/>
-      <c r="CY10" s="13"/>
-      <c r="CZ10" s="13"/>
-      <c r="DA10" s="13"/>
-      <c r="DB10" s="13"/>
-      <c r="DC10" s="13"/>
-      <c r="DD10" s="13"/>
-      <c r="DE10" s="13"/>
-      <c r="DF10" s="13"/>
-      <c r="DG10" s="13"/>
-      <c r="DH10" s="13"/>
-      <c r="DI10" s="13"/>
-      <c r="DJ10" s="13"/>
-      <c r="DK10" s="13"/>
-      <c r="DL10" s="13"/>
-      <c r="DM10" s="13"/>
-      <c r="DN10" s="13"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+      <c r="BI10" s="12"/>
+      <c r="BJ10" s="12"/>
+      <c r="BK10" s="12"/>
+      <c r="BL10" s="12"/>
+      <c r="BM10" s="12"/>
+      <c r="BN10" s="12"/>
+      <c r="BO10" s="12"/>
+      <c r="BP10" s="12"/>
+      <c r="BQ10" s="12"/>
+      <c r="BR10" s="12"/>
+      <c r="BS10" s="12"/>
+      <c r="BT10" s="12"/>
+      <c r="BU10" s="12"/>
+      <c r="BV10" s="12"/>
+      <c r="BW10" s="12"/>
+      <c r="BX10" s="12"/>
+      <c r="BY10" s="12"/>
+      <c r="BZ10" s="12"/>
+      <c r="CA10" s="12"/>
+      <c r="CB10" s="12"/>
+      <c r="CC10" s="12"/>
+      <c r="CD10" s="12"/>
+      <c r="CE10" s="12"/>
+      <c r="CF10" s="12"/>
+      <c r="CG10" s="12"/>
+      <c r="CH10" s="12"/>
+      <c r="CI10" s="12"/>
+      <c r="CJ10" s="12"/>
+      <c r="CK10" s="12"/>
+      <c r="CL10" s="12"/>
+      <c r="CM10" s="12"/>
+      <c r="CN10" s="12"/>
+      <c r="CO10" s="12"/>
+      <c r="CP10" s="12"/>
+      <c r="CQ10" s="12"/>
+      <c r="CR10" s="12"/>
+      <c r="CS10" s="12"/>
+      <c r="CT10" s="12"/>
+      <c r="CU10" s="12"/>
+      <c r="CV10" s="12"/>
+      <c r="CW10" s="12"/>
+      <c r="CX10" s="12"/>
+      <c r="CY10" s="12"/>
+      <c r="CZ10" s="12"/>
+      <c r="DA10" s="12"/>
+      <c r="DB10" s="12"/>
+      <c r="DC10" s="12"/>
+      <c r="DD10" s="12"/>
+      <c r="DE10" s="12"/>
+      <c r="DF10" s="12"/>
+      <c r="DG10" s="12"/>
+      <c r="DH10" s="12"/>
+      <c r="DI10" s="12"/>
+      <c r="DJ10" s="12"/>
+      <c r="DK10" s="12"/>
+      <c r="DL10" s="12"/>
+      <c r="DM10" s="12"/>
+      <c r="DN10" s="12"/>
+      <c r="DO10" s="26"/>
     </row>
-    <row r="11" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="20">
-        <f t="shared" si="1"/>
+    <row r="11" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="29" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -3166,170 +3202,173 @@
       <c r="M11" s="5">
         <v>1950</v>
       </c>
-      <c r="N11" s="16"/>
-      <c r="O11" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C11)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D11)," ","-")&amp;"-"&amp;E11&amp;"-"&amp;F11))</f>
+      <c r="N11" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O11" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>389-university-avenue-los-altos-ca-94022</v>
       </c>
-      <c r="P11" s="22" t="str">
-        <f t="shared" si="2"/>
+      <c r="P11" s="21" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q11" s="5"/>
-      <c r="R11" s="10" t="str">
+      <c r="R11" s="9" t="str">
         <f>IF(Q11="YES", COUNTIF($Q$2:Q11, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q11, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="S11" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="T11" s="14" t="s">
+      <c r="T11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="U11" s="14" t="s">
+      <c r="U11" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="V11" s="14" t="s">
+      <c r="V11" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="W11" s="14" t="s">
+      <c r="W11" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="X11" s="14" t="s">
+      <c r="X11" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="Y11" s="14" t="s">
+      <c r="Y11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="Z11" s="14" t="s">
+      <c r="Z11" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AA11" s="14" t="s">
+      <c r="AA11" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AB11" s="14" t="s">
+      <c r="AB11" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AC11" s="14" t="s">
+      <c r="AC11" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="AD11" s="14" t="s">
+      <c r="AD11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AE11" s="14" t="s">
+      <c r="AE11" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AF11" s="14" t="s">
+      <c r="AF11" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AG11" s="14" t="s">
+      <c r="AG11" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AH11" s="14" t="s">
+      <c r="AH11" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="AI11" s="14" t="s">
+      <c r="AI11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AJ11" s="14" t="s">
+      <c r="AJ11" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AK11" s="14" t="s">
+      <c r="AK11" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AL11" s="14" t="s">
+      <c r="AL11" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AM11" s="14"/>
-      <c r="AN11" s="14"/>
-      <c r="AO11" s="14"/>
-      <c r="AP11" s="14"/>
-      <c r="AQ11" s="14"/>
-      <c r="AR11" s="14"/>
-      <c r="AS11" s="14"/>
-      <c r="AT11" s="14"/>
-      <c r="AU11" s="14"/>
-      <c r="AV11" s="14"/>
-      <c r="AW11" s="14"/>
-      <c r="AX11" s="14"/>
-      <c r="AY11" s="14"/>
-      <c r="AZ11" s="14"/>
-      <c r="BA11" s="14"/>
-      <c r="BB11" s="14"/>
-      <c r="BC11" s="14"/>
-      <c r="BD11" s="14"/>
-      <c r="BE11" s="14"/>
-      <c r="BF11" s="14"/>
-      <c r="BG11" s="14"/>
-      <c r="BH11" s="14"/>
-      <c r="BI11" s="14"/>
-      <c r="BJ11" s="14"/>
-      <c r="BK11" s="14"/>
-      <c r="BL11" s="14"/>
-      <c r="BM11" s="14"/>
-      <c r="BN11" s="14"/>
-      <c r="BO11" s="14"/>
-      <c r="BP11" s="14"/>
-      <c r="BQ11" s="14"/>
-      <c r="BR11" s="14"/>
-      <c r="BS11" s="14"/>
-      <c r="BT11" s="14"/>
-      <c r="BU11" s="14"/>
-      <c r="BV11" s="14"/>
-      <c r="BW11" s="14"/>
-      <c r="BX11" s="14"/>
-      <c r="BY11" s="14"/>
-      <c r="BZ11" s="14"/>
-      <c r="CA11" s="14"/>
-      <c r="CB11" s="14"/>
-      <c r="CC11" s="14"/>
-      <c r="CD11" s="14"/>
-      <c r="CE11" s="14"/>
-      <c r="CF11" s="14"/>
-      <c r="CG11" s="14"/>
-      <c r="CH11" s="14"/>
-      <c r="CI11" s="14"/>
-      <c r="CJ11" s="14"/>
-      <c r="CK11" s="14"/>
-      <c r="CL11" s="14"/>
-      <c r="CM11" s="14"/>
-      <c r="CN11" s="14"/>
-      <c r="CO11" s="14"/>
-      <c r="CP11" s="14"/>
-      <c r="CQ11" s="14"/>
-      <c r="CR11" s="14"/>
-      <c r="CS11" s="14"/>
-      <c r="CT11" s="14"/>
-      <c r="CU11" s="14"/>
-      <c r="CV11" s="14"/>
-      <c r="CW11" s="14"/>
-      <c r="CX11" s="14"/>
-      <c r="CY11" s="14"/>
-      <c r="CZ11" s="14"/>
-      <c r="DA11" s="14"/>
-      <c r="DB11" s="14"/>
-      <c r="DC11" s="14"/>
-      <c r="DD11" s="14"/>
-      <c r="DE11" s="14"/>
-      <c r="DF11" s="14"/>
-      <c r="DG11" s="14"/>
-      <c r="DH11" s="14"/>
-      <c r="DI11" s="14"/>
-      <c r="DJ11" s="14"/>
-      <c r="DK11" s="14"/>
-      <c r="DL11" s="14"/>
-      <c r="DM11" s="14"/>
-      <c r="DN11" s="14"/>
+      <c r="AM11" s="13"/>
+      <c r="AN11" s="13"/>
+      <c r="AO11" s="13"/>
+      <c r="AP11" s="13"/>
+      <c r="AQ11" s="13"/>
+      <c r="AR11" s="13"/>
+      <c r="AS11" s="13"/>
+      <c r="AT11" s="13"/>
+      <c r="AU11" s="13"/>
+      <c r="AV11" s="13"/>
+      <c r="AW11" s="13"/>
+      <c r="AX11" s="13"/>
+      <c r="AY11" s="13"/>
+      <c r="AZ11" s="13"/>
+      <c r="BA11" s="13"/>
+      <c r="BB11" s="13"/>
+      <c r="BC11" s="13"/>
+      <c r="BD11" s="13"/>
+      <c r="BE11" s="13"/>
+      <c r="BF11" s="13"/>
+      <c r="BG11" s="13"/>
+      <c r="BH11" s="13"/>
+      <c r="BI11" s="13"/>
+      <c r="BJ11" s="13"/>
+      <c r="BK11" s="13"/>
+      <c r="BL11" s="13"/>
+      <c r="BM11" s="13"/>
+      <c r="BN11" s="13"/>
+      <c r="BO11" s="13"/>
+      <c r="BP11" s="13"/>
+      <c r="BQ11" s="13"/>
+      <c r="BR11" s="13"/>
+      <c r="BS11" s="13"/>
+      <c r="BT11" s="13"/>
+      <c r="BU11" s="13"/>
+      <c r="BV11" s="13"/>
+      <c r="BW11" s="13"/>
+      <c r="BX11" s="13"/>
+      <c r="BY11" s="13"/>
+      <c r="BZ11" s="13"/>
+      <c r="CA11" s="13"/>
+      <c r="CB11" s="13"/>
+      <c r="CC11" s="13"/>
+      <c r="CD11" s="13"/>
+      <c r="CE11" s="13"/>
+      <c r="CF11" s="13"/>
+      <c r="CG11" s="13"/>
+      <c r="CH11" s="13"/>
+      <c r="CI11" s="13"/>
+      <c r="CJ11" s="13"/>
+      <c r="CK11" s="13"/>
+      <c r="CL11" s="13"/>
+      <c r="CM11" s="13"/>
+      <c r="CN11" s="13"/>
+      <c r="CO11" s="13"/>
+      <c r="CP11" s="13"/>
+      <c r="CQ11" s="13"/>
+      <c r="CR11" s="13"/>
+      <c r="CS11" s="13"/>
+      <c r="CT11" s="13"/>
+      <c r="CU11" s="13"/>
+      <c r="CV11" s="13"/>
+      <c r="CW11" s="13"/>
+      <c r="CX11" s="13"/>
+      <c r="CY11" s="13"/>
+      <c r="CZ11" s="13"/>
+      <c r="DA11" s="13"/>
+      <c r="DB11" s="13"/>
+      <c r="DC11" s="13"/>
+      <c r="DD11" s="13"/>
+      <c r="DE11" s="13"/>
+      <c r="DF11" s="13"/>
+      <c r="DG11" s="13"/>
+      <c r="DH11" s="13"/>
+      <c r="DI11" s="13"/>
+      <c r="DJ11" s="13"/>
+      <c r="DK11" s="13"/>
+      <c r="DL11" s="13"/>
+      <c r="DM11" s="13"/>
+      <c r="DN11" s="13"/>
+      <c r="DO11" s="26"/>
     </row>
-    <row r="12" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9">
-        <f t="shared" si="1"/>
+    <row r="12" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="30" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -3360,170 +3399,173 @@
       <c r="M12" s="2">
         <v>1940</v>
       </c>
-      <c r="N12" s="15"/>
-      <c r="O12" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C12)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D12)," ","-")&amp;"-"&amp;E12&amp;"-"&amp;F12))</f>
+      <c r="N12" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="O12" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>1050-waverley-street-palo-alto-ca-94301</v>
       </c>
-      <c r="P12" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P12" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q12" s="2"/>
-      <c r="R12" s="9" t="str">
+      <c r="R12" s="8" t="str">
         <f>IF(Q12="YES", COUNTIF($Q$2:Q12, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q12, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S12" s="13" t="s">
+      <c r="S12" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="T12" s="13" t="s">
+      <c r="T12" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="U12" s="13" t="s">
+      <c r="U12" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="V12" s="13" t="s">
+      <c r="V12" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="W12" s="13" t="s">
+      <c r="W12" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="X12" s="13" t="s">
+      <c r="X12" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="Y12" s="13" t="s">
+      <c r="Y12" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="Z12" s="13" t="s">
+      <c r="Z12" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="AA12" s="13" t="s">
+      <c r="AA12" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="AB12" s="13" t="s">
+      <c r="AB12" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="AC12" s="13" t="s">
+      <c r="AC12" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="AD12" s="13" t="s">
+      <c r="AD12" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="AE12" s="13" t="s">
+      <c r="AE12" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="AF12" s="13" t="s">
+      <c r="AF12" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="AG12" s="13" t="s">
+      <c r="AG12" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="AH12" s="13" t="s">
+      <c r="AH12" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="AI12" s="13" t="s">
+      <c r="AI12" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="AJ12" s="13" t="s">
+      <c r="AJ12" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="AK12" s="13" t="s">
+      <c r="AK12" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="AL12" s="13" t="s">
+      <c r="AL12" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="AM12" s="13"/>
-      <c r="AN12" s="13"/>
-      <c r="AO12" s="13"/>
-      <c r="AP12" s="13"/>
-      <c r="AQ12" s="13"/>
-      <c r="AR12" s="13"/>
-      <c r="AS12" s="13"/>
-      <c r="AT12" s="13"/>
-      <c r="AU12" s="13"/>
-      <c r="AV12" s="13"/>
-      <c r="AW12" s="13"/>
-      <c r="AX12" s="13"/>
-      <c r="AY12" s="13"/>
-      <c r="AZ12" s="13"/>
-      <c r="BA12" s="13"/>
-      <c r="BB12" s="13"/>
-      <c r="BC12" s="13"/>
-      <c r="BD12" s="13"/>
-      <c r="BE12" s="13"/>
-      <c r="BF12" s="13"/>
-      <c r="BG12" s="13"/>
-      <c r="BH12" s="13"/>
-      <c r="BI12" s="13"/>
-      <c r="BJ12" s="13"/>
-      <c r="BK12" s="13"/>
-      <c r="BL12" s="13"/>
-      <c r="BM12" s="13"/>
-      <c r="BN12" s="13"/>
-      <c r="BO12" s="13"/>
-      <c r="BP12" s="13"/>
-      <c r="BQ12" s="13"/>
-      <c r="BR12" s="13"/>
-      <c r="BS12" s="13"/>
-      <c r="BT12" s="13"/>
-      <c r="BU12" s="13"/>
-      <c r="BV12" s="13"/>
-      <c r="BW12" s="13"/>
-      <c r="BX12" s="13"/>
-      <c r="BY12" s="13"/>
-      <c r="BZ12" s="13"/>
-      <c r="CA12" s="13"/>
-      <c r="CB12" s="13"/>
-      <c r="CC12" s="13"/>
-      <c r="CD12" s="13"/>
-      <c r="CE12" s="13"/>
-      <c r="CF12" s="13"/>
-      <c r="CG12" s="13"/>
-      <c r="CH12" s="13"/>
-      <c r="CI12" s="13"/>
-      <c r="CJ12" s="13"/>
-      <c r="CK12" s="13"/>
-      <c r="CL12" s="13"/>
-      <c r="CM12" s="13"/>
-      <c r="CN12" s="13"/>
-      <c r="CO12" s="13"/>
-      <c r="CP12" s="13"/>
-      <c r="CQ12" s="13"/>
-      <c r="CR12" s="13"/>
-      <c r="CS12" s="13"/>
-      <c r="CT12" s="13"/>
-      <c r="CU12" s="13"/>
-      <c r="CV12" s="13"/>
-      <c r="CW12" s="13"/>
-      <c r="CX12" s="13"/>
-      <c r="CY12" s="13"/>
-      <c r="CZ12" s="13"/>
-      <c r="DA12" s="13"/>
-      <c r="DB12" s="13"/>
-      <c r="DC12" s="13"/>
-      <c r="DD12" s="13"/>
-      <c r="DE12" s="13"/>
-      <c r="DF12" s="13"/>
-      <c r="DG12" s="13"/>
-      <c r="DH12" s="13"/>
-      <c r="DI12" s="13"/>
-      <c r="DJ12" s="13"/>
-      <c r="DK12" s="13"/>
-      <c r="DL12" s="13"/>
-      <c r="DM12" s="13"/>
-      <c r="DN12" s="13"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+      <c r="BI12" s="12"/>
+      <c r="BJ12" s="12"/>
+      <c r="BK12" s="12"/>
+      <c r="BL12" s="12"/>
+      <c r="BM12" s="12"/>
+      <c r="BN12" s="12"/>
+      <c r="BO12" s="12"/>
+      <c r="BP12" s="12"/>
+      <c r="BQ12" s="12"/>
+      <c r="BR12" s="12"/>
+      <c r="BS12" s="12"/>
+      <c r="BT12" s="12"/>
+      <c r="BU12" s="12"/>
+      <c r="BV12" s="12"/>
+      <c r="BW12" s="12"/>
+      <c r="BX12" s="12"/>
+      <c r="BY12" s="12"/>
+      <c r="BZ12" s="12"/>
+      <c r="CA12" s="12"/>
+      <c r="CB12" s="12"/>
+      <c r="CC12" s="12"/>
+      <c r="CD12" s="12"/>
+      <c r="CE12" s="12"/>
+      <c r="CF12" s="12"/>
+      <c r="CG12" s="12"/>
+      <c r="CH12" s="12"/>
+      <c r="CI12" s="12"/>
+      <c r="CJ12" s="12"/>
+      <c r="CK12" s="12"/>
+      <c r="CL12" s="12"/>
+      <c r="CM12" s="12"/>
+      <c r="CN12" s="12"/>
+      <c r="CO12" s="12"/>
+      <c r="CP12" s="12"/>
+      <c r="CQ12" s="12"/>
+      <c r="CR12" s="12"/>
+      <c r="CS12" s="12"/>
+      <c r="CT12" s="12"/>
+      <c r="CU12" s="12"/>
+      <c r="CV12" s="12"/>
+      <c r="CW12" s="12"/>
+      <c r="CX12" s="12"/>
+      <c r="CY12" s="12"/>
+      <c r="CZ12" s="12"/>
+      <c r="DA12" s="12"/>
+      <c r="DB12" s="12"/>
+      <c r="DC12" s="12"/>
+      <c r="DD12" s="12"/>
+      <c r="DE12" s="12"/>
+      <c r="DF12" s="12"/>
+      <c r="DG12" s="12"/>
+      <c r="DH12" s="12"/>
+      <c r="DI12" s="12"/>
+      <c r="DJ12" s="12"/>
+      <c r="DK12" s="12"/>
+      <c r="DL12" s="12"/>
+      <c r="DM12" s="12"/>
+      <c r="DN12" s="12"/>
+      <c r="DO12" s="26"/>
     </row>
-    <row r="13" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20">
-        <f t="shared" si="1"/>
+    <row r="13" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="19">
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="29" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -3554,170 +3596,173 @@
       <c r="M13" s="5">
         <v>1931</v>
       </c>
-      <c r="N13" s="16"/>
-      <c r="O13" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C13)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D13)," ","-")&amp;"-"&amp;E13&amp;"-"&amp;F13))</f>
+      <c r="N13" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O13" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>6220-country-club-pkwy-san-jose-ca-95138</v>
       </c>
-      <c r="P13" s="22" t="str">
-        <f t="shared" si="2"/>
+      <c r="P13" s="21" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q13" s="5"/>
-      <c r="R13" s="10" t="str">
+      <c r="R13" s="9" t="str">
         <f>IF(Q13="YES", COUNTIF($Q$2:Q13, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q13, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S13" s="14" t="s">
+      <c r="S13" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="T13" s="14" t="s">
+      <c r="T13" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="U13" s="14" t="s">
+      <c r="U13" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="V13" s="14" t="s">
+      <c r="V13" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="W13" s="14" t="s">
+      <c r="W13" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="X13" s="14" t="s">
+      <c r="X13" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="Y13" s="14" t="s">
+      <c r="Y13" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="Z13" s="14" t="s">
+      <c r="Z13" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AA13" s="14" t="s">
+      <c r="AA13" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AB13" s="14" t="s">
+      <c r="AB13" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AC13" s="14" t="s">
+      <c r="AC13" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AD13" s="14" t="s">
+      <c r="AD13" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="AE13" s="14" t="s">
+      <c r="AE13" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AF13" s="14" t="s">
+      <c r="AF13" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AG13" s="14" t="s">
+      <c r="AG13" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AH13" s="14" t="s">
+      <c r="AH13" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AI13" s="14" t="s">
+      <c r="AI13" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="AJ13" s="14" t="s">
+      <c r="AJ13" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AK13" s="14" t="s">
+      <c r="AK13" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AL13" s="14" t="s">
+      <c r="AL13" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AM13" s="14"/>
-      <c r="AN13" s="14"/>
-      <c r="AO13" s="14"/>
-      <c r="AP13" s="14"/>
-      <c r="AQ13" s="14"/>
-      <c r="AR13" s="14"/>
-      <c r="AS13" s="14"/>
-      <c r="AT13" s="14"/>
-      <c r="AU13" s="14"/>
-      <c r="AV13" s="14"/>
-      <c r="AW13" s="14"/>
-      <c r="AX13" s="14"/>
-      <c r="AY13" s="14"/>
-      <c r="AZ13" s="14"/>
-      <c r="BA13" s="14"/>
-      <c r="BB13" s="14"/>
-      <c r="BC13" s="14"/>
-      <c r="BD13" s="14"/>
-      <c r="BE13" s="14"/>
-      <c r="BF13" s="14"/>
-      <c r="BG13" s="14"/>
-      <c r="BH13" s="14"/>
-      <c r="BI13" s="14"/>
-      <c r="BJ13" s="14"/>
-      <c r="BK13" s="14"/>
-      <c r="BL13" s="14"/>
-      <c r="BM13" s="14"/>
-      <c r="BN13" s="14"/>
-      <c r="BO13" s="14"/>
-      <c r="BP13" s="14"/>
-      <c r="BQ13" s="14"/>
-      <c r="BR13" s="14"/>
-      <c r="BS13" s="14"/>
-      <c r="BT13" s="14"/>
-      <c r="BU13" s="14"/>
-      <c r="BV13" s="14"/>
-      <c r="BW13" s="14"/>
-      <c r="BX13" s="14"/>
-      <c r="BY13" s="14"/>
-      <c r="BZ13" s="14"/>
-      <c r="CA13" s="14"/>
-      <c r="CB13" s="14"/>
-      <c r="CC13" s="14"/>
-      <c r="CD13" s="14"/>
-      <c r="CE13" s="14"/>
-      <c r="CF13" s="14"/>
-      <c r="CG13" s="14"/>
-      <c r="CH13" s="14"/>
-      <c r="CI13" s="14"/>
-      <c r="CJ13" s="14"/>
-      <c r="CK13" s="14"/>
-      <c r="CL13" s="14"/>
-      <c r="CM13" s="14"/>
-      <c r="CN13" s="14"/>
-      <c r="CO13" s="14"/>
-      <c r="CP13" s="14"/>
-      <c r="CQ13" s="14"/>
-      <c r="CR13" s="14"/>
-      <c r="CS13" s="14"/>
-      <c r="CT13" s="14"/>
-      <c r="CU13" s="14"/>
-      <c r="CV13" s="14"/>
-      <c r="CW13" s="14"/>
-      <c r="CX13" s="14"/>
-      <c r="CY13" s="14"/>
-      <c r="CZ13" s="14"/>
-      <c r="DA13" s="14"/>
-      <c r="DB13" s="14"/>
-      <c r="DC13" s="14"/>
-      <c r="DD13" s="14"/>
-      <c r="DE13" s="14"/>
-      <c r="DF13" s="14"/>
-      <c r="DG13" s="14"/>
-      <c r="DH13" s="14"/>
-      <c r="DI13" s="14"/>
-      <c r="DJ13" s="14"/>
-      <c r="DK13" s="14"/>
-      <c r="DL13" s="14"/>
-      <c r="DM13" s="14"/>
-      <c r="DN13" s="14"/>
+      <c r="AM13" s="13"/>
+      <c r="AN13" s="13"/>
+      <c r="AO13" s="13"/>
+      <c r="AP13" s="13"/>
+      <c r="AQ13" s="13"/>
+      <c r="AR13" s="13"/>
+      <c r="AS13" s="13"/>
+      <c r="AT13" s="13"/>
+      <c r="AU13" s="13"/>
+      <c r="AV13" s="13"/>
+      <c r="AW13" s="13"/>
+      <c r="AX13" s="13"/>
+      <c r="AY13" s="13"/>
+      <c r="AZ13" s="13"/>
+      <c r="BA13" s="13"/>
+      <c r="BB13" s="13"/>
+      <c r="BC13" s="13"/>
+      <c r="BD13" s="13"/>
+      <c r="BE13" s="13"/>
+      <c r="BF13" s="13"/>
+      <c r="BG13" s="13"/>
+      <c r="BH13" s="13"/>
+      <c r="BI13" s="13"/>
+      <c r="BJ13" s="13"/>
+      <c r="BK13" s="13"/>
+      <c r="BL13" s="13"/>
+      <c r="BM13" s="13"/>
+      <c r="BN13" s="13"/>
+      <c r="BO13" s="13"/>
+      <c r="BP13" s="13"/>
+      <c r="BQ13" s="13"/>
+      <c r="BR13" s="13"/>
+      <c r="BS13" s="13"/>
+      <c r="BT13" s="13"/>
+      <c r="BU13" s="13"/>
+      <c r="BV13" s="13"/>
+      <c r="BW13" s="13"/>
+      <c r="BX13" s="13"/>
+      <c r="BY13" s="13"/>
+      <c r="BZ13" s="13"/>
+      <c r="CA13" s="13"/>
+      <c r="CB13" s="13"/>
+      <c r="CC13" s="13"/>
+      <c r="CD13" s="13"/>
+      <c r="CE13" s="13"/>
+      <c r="CF13" s="13"/>
+      <c r="CG13" s="13"/>
+      <c r="CH13" s="13"/>
+      <c r="CI13" s="13"/>
+      <c r="CJ13" s="13"/>
+      <c r="CK13" s="13"/>
+      <c r="CL13" s="13"/>
+      <c r="CM13" s="13"/>
+      <c r="CN13" s="13"/>
+      <c r="CO13" s="13"/>
+      <c r="CP13" s="13"/>
+      <c r="CQ13" s="13"/>
+      <c r="CR13" s="13"/>
+      <c r="CS13" s="13"/>
+      <c r="CT13" s="13"/>
+      <c r="CU13" s="13"/>
+      <c r="CV13" s="13"/>
+      <c r="CW13" s="13"/>
+      <c r="CX13" s="13"/>
+      <c r="CY13" s="13"/>
+      <c r="CZ13" s="13"/>
+      <c r="DA13" s="13"/>
+      <c r="DB13" s="13"/>
+      <c r="DC13" s="13"/>
+      <c r="DD13" s="13"/>
+      <c r="DE13" s="13"/>
+      <c r="DF13" s="13"/>
+      <c r="DG13" s="13"/>
+      <c r="DH13" s="13"/>
+      <c r="DI13" s="13"/>
+      <c r="DJ13" s="13"/>
+      <c r="DK13" s="13"/>
+      <c r="DL13" s="13"/>
+      <c r="DM13" s="13"/>
+      <c r="DN13" s="13"/>
+      <c r="DO13" s="26"/>
     </row>
-    <row r="14" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9">
-        <f t="shared" si="1"/>
+    <row r="14" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="30" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -3748,170 +3793,173 @@
       <c r="M14" s="2">
         <v>1950</v>
       </c>
-      <c r="N14" s="15"/>
-      <c r="O14" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C14)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D14)," ","-")&amp;"-"&amp;E14&amp;"-"&amp;F14))</f>
+      <c r="N14" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="O14" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>19540-glen-una-drive-saratoga-ca-95070</v>
       </c>
-      <c r="P14" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P14" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q14" s="2"/>
-      <c r="R14" s="9" t="str">
+      <c r="R14" s="8" t="str">
         <f>IF(Q14="YES", COUNTIF($Q$2:Q14, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q14, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S14" s="13" t="s">
+      <c r="S14" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="T14" s="13" t="s">
+      <c r="T14" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="U14" s="13" t="s">
+      <c r="U14" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="V14" s="13" t="s">
+      <c r="V14" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="W14" s="13" t="s">
+      <c r="W14" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="X14" s="13" t="s">
+      <c r="X14" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="Y14" s="13" t="s">
+      <c r="Y14" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="Z14" s="13" t="s">
+      <c r="Z14" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="AA14" s="13" t="s">
+      <c r="AA14" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AB14" s="13" t="s">
+      <c r="AB14" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="AC14" s="13" t="s">
+      <c r="AC14" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="AD14" s="13" t="s">
+      <c r="AD14" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="AE14" s="13" t="s">
+      <c r="AE14" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="AF14" s="13" t="s">
+      <c r="AF14" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AG14" s="13" t="s">
+      <c r="AG14" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="AH14" s="13" t="s">
+      <c r="AH14" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="AI14" s="13" t="s">
+      <c r="AI14" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="AJ14" s="13" t="s">
+      <c r="AJ14" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="AK14" s="13" t="s">
+      <c r="AK14" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AL14" s="13" t="s">
+      <c r="AL14" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="AM14" s="13"/>
-      <c r="AN14" s="13"/>
-      <c r="AO14" s="13"/>
-      <c r="AP14" s="13"/>
-      <c r="AQ14" s="13"/>
-      <c r="AR14" s="13"/>
-      <c r="AS14" s="13"/>
-      <c r="AT14" s="13"/>
-      <c r="AU14" s="13"/>
-      <c r="AV14" s="13"/>
-      <c r="AW14" s="13"/>
-      <c r="AX14" s="13"/>
-      <c r="AY14" s="13"/>
-      <c r="AZ14" s="13"/>
-      <c r="BA14" s="13"/>
-      <c r="BB14" s="13"/>
-      <c r="BC14" s="13"/>
-      <c r="BD14" s="13"/>
-      <c r="BE14" s="13"/>
-      <c r="BF14" s="13"/>
-      <c r="BG14" s="13"/>
-      <c r="BH14" s="13"/>
-      <c r="BI14" s="13"/>
-      <c r="BJ14" s="13"/>
-      <c r="BK14" s="13"/>
-      <c r="BL14" s="13"/>
-      <c r="BM14" s="13"/>
-      <c r="BN14" s="13"/>
-      <c r="BO14" s="13"/>
-      <c r="BP14" s="13"/>
-      <c r="BQ14" s="13"/>
-      <c r="BR14" s="13"/>
-      <c r="BS14" s="13"/>
-      <c r="BT14" s="13"/>
-      <c r="BU14" s="13"/>
-      <c r="BV14" s="13"/>
-      <c r="BW14" s="13"/>
-      <c r="BX14" s="13"/>
-      <c r="BY14" s="13"/>
-      <c r="BZ14" s="13"/>
-      <c r="CA14" s="13"/>
-      <c r="CB14" s="13"/>
-      <c r="CC14" s="13"/>
-      <c r="CD14" s="13"/>
-      <c r="CE14" s="13"/>
-      <c r="CF14" s="13"/>
-      <c r="CG14" s="13"/>
-      <c r="CH14" s="13"/>
-      <c r="CI14" s="13"/>
-      <c r="CJ14" s="13"/>
-      <c r="CK14" s="13"/>
-      <c r="CL14" s="13"/>
-      <c r="CM14" s="13"/>
-      <c r="CN14" s="13"/>
-      <c r="CO14" s="13"/>
-      <c r="CP14" s="13"/>
-      <c r="CQ14" s="13"/>
-      <c r="CR14" s="13"/>
-      <c r="CS14" s="13"/>
-      <c r="CT14" s="13"/>
-      <c r="CU14" s="13"/>
-      <c r="CV14" s="13"/>
-      <c r="CW14" s="13"/>
-      <c r="CX14" s="13"/>
-      <c r="CY14" s="13"/>
-      <c r="CZ14" s="13"/>
-      <c r="DA14" s="13"/>
-      <c r="DB14" s="13"/>
-      <c r="DC14" s="13"/>
-      <c r="DD14" s="13"/>
-      <c r="DE14" s="13"/>
-      <c r="DF14" s="13"/>
-      <c r="DG14" s="13"/>
-      <c r="DH14" s="13"/>
-      <c r="DI14" s="13"/>
-      <c r="DJ14" s="13"/>
-      <c r="DK14" s="13"/>
-      <c r="DL14" s="13"/>
-      <c r="DM14" s="13"/>
-      <c r="DN14" s="13"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+      <c r="BI14" s="12"/>
+      <c r="BJ14" s="12"/>
+      <c r="BK14" s="12"/>
+      <c r="BL14" s="12"/>
+      <c r="BM14" s="12"/>
+      <c r="BN14" s="12"/>
+      <c r="BO14" s="12"/>
+      <c r="BP14" s="12"/>
+      <c r="BQ14" s="12"/>
+      <c r="BR14" s="12"/>
+      <c r="BS14" s="12"/>
+      <c r="BT14" s="12"/>
+      <c r="BU14" s="12"/>
+      <c r="BV14" s="12"/>
+      <c r="BW14" s="12"/>
+      <c r="BX14" s="12"/>
+      <c r="BY14" s="12"/>
+      <c r="BZ14" s="12"/>
+      <c r="CA14" s="12"/>
+      <c r="CB14" s="12"/>
+      <c r="CC14" s="12"/>
+      <c r="CD14" s="12"/>
+      <c r="CE14" s="12"/>
+      <c r="CF14" s="12"/>
+      <c r="CG14" s="12"/>
+      <c r="CH14" s="12"/>
+      <c r="CI14" s="12"/>
+      <c r="CJ14" s="12"/>
+      <c r="CK14" s="12"/>
+      <c r="CL14" s="12"/>
+      <c r="CM14" s="12"/>
+      <c r="CN14" s="12"/>
+      <c r="CO14" s="12"/>
+      <c r="CP14" s="12"/>
+      <c r="CQ14" s="12"/>
+      <c r="CR14" s="12"/>
+      <c r="CS14" s="12"/>
+      <c r="CT14" s="12"/>
+      <c r="CU14" s="12"/>
+      <c r="CV14" s="12"/>
+      <c r="CW14" s="12"/>
+      <c r="CX14" s="12"/>
+      <c r="CY14" s="12"/>
+      <c r="CZ14" s="12"/>
+      <c r="DA14" s="12"/>
+      <c r="DB14" s="12"/>
+      <c r="DC14" s="12"/>
+      <c r="DD14" s="12"/>
+      <c r="DE14" s="12"/>
+      <c r="DF14" s="12"/>
+      <c r="DG14" s="12"/>
+      <c r="DH14" s="12"/>
+      <c r="DI14" s="12"/>
+      <c r="DJ14" s="12"/>
+      <c r="DK14" s="12"/>
+      <c r="DL14" s="12"/>
+      <c r="DM14" s="12"/>
+      <c r="DN14" s="12"/>
+      <c r="DO14" s="26"/>
     </row>
-    <row r="15" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="20">
-        <f t="shared" si="1"/>
+    <row r="15" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="19">
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="29" t="s">
         <v>45</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -3942,170 +3990,173 @@
       <c r="M15" s="5">
         <v>1960</v>
       </c>
-      <c r="N15" s="16"/>
-      <c r="O15" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C15)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D15)," ","-")&amp;"-"&amp;E15&amp;"-"&amp;F15))</f>
+      <c r="N15" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O15" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>15420-francis-oaks-way-los-gatos-ca-95032</v>
       </c>
-      <c r="P15" s="22" t="str">
-        <f t="shared" si="2"/>
+      <c r="P15" s="21" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q15" s="5"/>
-      <c r="R15" s="10" t="str">
+      <c r="R15" s="9" t="str">
         <f>IF(Q15="YES", COUNTIF($Q$2:Q15, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q15, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S15" s="14" t="s">
+      <c r="S15" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="T15" s="14" t="s">
+      <c r="T15" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="U15" s="14" t="s">
+      <c r="U15" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="V15" s="14" t="s">
+      <c r="V15" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="W15" s="14" t="s">
+      <c r="W15" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="X15" s="14" t="s">
+      <c r="X15" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="Y15" s="14" t="s">
+      <c r="Y15" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="Z15" s="14" t="s">
+      <c r="Z15" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AA15" s="14" t="s">
+      <c r="AA15" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AB15" s="14" t="s">
+      <c r="AB15" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="AC15" s="14" t="s">
+      <c r="AC15" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AD15" s="14" t="s">
+      <c r="AD15" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AE15" s="14" t="s">
+      <c r="AE15" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AF15" s="14" t="s">
+      <c r="AF15" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AG15" s="14" t="s">
+      <c r="AG15" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="AH15" s="14" t="s">
+      <c r="AH15" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AI15" s="14" t="s">
+      <c r="AI15" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AJ15" s="14" t="s">
+      <c r="AJ15" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AK15" s="14" t="s">
+      <c r="AK15" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AL15" s="14" t="s">
+      <c r="AL15" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="AM15" s="14"/>
-      <c r="AN15" s="14"/>
-      <c r="AO15" s="14"/>
-      <c r="AP15" s="14"/>
-      <c r="AQ15" s="14"/>
-      <c r="AR15" s="14"/>
-      <c r="AS15" s="14"/>
-      <c r="AT15" s="14"/>
-      <c r="AU15" s="14"/>
-      <c r="AV15" s="14"/>
-      <c r="AW15" s="14"/>
-      <c r="AX15" s="14"/>
-      <c r="AY15" s="14"/>
-      <c r="AZ15" s="14"/>
-      <c r="BA15" s="14"/>
-      <c r="BB15" s="14"/>
-      <c r="BC15" s="14"/>
-      <c r="BD15" s="14"/>
-      <c r="BE15" s="14"/>
-      <c r="BF15" s="14"/>
-      <c r="BG15" s="14"/>
-      <c r="BH15" s="14"/>
-      <c r="BI15" s="14"/>
-      <c r="BJ15" s="14"/>
-      <c r="BK15" s="14"/>
-      <c r="BL15" s="14"/>
-      <c r="BM15" s="14"/>
-      <c r="BN15" s="14"/>
-      <c r="BO15" s="14"/>
-      <c r="BP15" s="14"/>
-      <c r="BQ15" s="14"/>
-      <c r="BR15" s="14"/>
-      <c r="BS15" s="14"/>
-      <c r="BT15" s="14"/>
-      <c r="BU15" s="14"/>
-      <c r="BV15" s="14"/>
-      <c r="BW15" s="14"/>
-      <c r="BX15" s="14"/>
-      <c r="BY15" s="14"/>
-      <c r="BZ15" s="14"/>
-      <c r="CA15" s="14"/>
-      <c r="CB15" s="14"/>
-      <c r="CC15" s="14"/>
-      <c r="CD15" s="14"/>
-      <c r="CE15" s="14"/>
-      <c r="CF15" s="14"/>
-      <c r="CG15" s="14"/>
-      <c r="CH15" s="14"/>
-      <c r="CI15" s="14"/>
-      <c r="CJ15" s="14"/>
-      <c r="CK15" s="14"/>
-      <c r="CL15" s="14"/>
-      <c r="CM15" s="14"/>
-      <c r="CN15" s="14"/>
-      <c r="CO15" s="14"/>
-      <c r="CP15" s="14"/>
-      <c r="CQ15" s="14"/>
-      <c r="CR15" s="14"/>
-      <c r="CS15" s="14"/>
-      <c r="CT15" s="14"/>
-      <c r="CU15" s="14"/>
-      <c r="CV15" s="14"/>
-      <c r="CW15" s="14"/>
-      <c r="CX15" s="14"/>
-      <c r="CY15" s="14"/>
-      <c r="CZ15" s="14"/>
-      <c r="DA15" s="14"/>
-      <c r="DB15" s="14"/>
-      <c r="DC15" s="14"/>
-      <c r="DD15" s="14"/>
-      <c r="DE15" s="14"/>
-      <c r="DF15" s="14"/>
-      <c r="DG15" s="14"/>
-      <c r="DH15" s="14"/>
-      <c r="DI15" s="14"/>
-      <c r="DJ15" s="14"/>
-      <c r="DK15" s="14"/>
-      <c r="DL15" s="14"/>
-      <c r="DM15" s="14"/>
-      <c r="DN15" s="14"/>
+      <c r="AM15" s="13"/>
+      <c r="AN15" s="13"/>
+      <c r="AO15" s="13"/>
+      <c r="AP15" s="13"/>
+      <c r="AQ15" s="13"/>
+      <c r="AR15" s="13"/>
+      <c r="AS15" s="13"/>
+      <c r="AT15" s="13"/>
+      <c r="AU15" s="13"/>
+      <c r="AV15" s="13"/>
+      <c r="AW15" s="13"/>
+      <c r="AX15" s="13"/>
+      <c r="AY15" s="13"/>
+      <c r="AZ15" s="13"/>
+      <c r="BA15" s="13"/>
+      <c r="BB15" s="13"/>
+      <c r="BC15" s="13"/>
+      <c r="BD15" s="13"/>
+      <c r="BE15" s="13"/>
+      <c r="BF15" s="13"/>
+      <c r="BG15" s="13"/>
+      <c r="BH15" s="13"/>
+      <c r="BI15" s="13"/>
+      <c r="BJ15" s="13"/>
+      <c r="BK15" s="13"/>
+      <c r="BL15" s="13"/>
+      <c r="BM15" s="13"/>
+      <c r="BN15" s="13"/>
+      <c r="BO15" s="13"/>
+      <c r="BP15" s="13"/>
+      <c r="BQ15" s="13"/>
+      <c r="BR15" s="13"/>
+      <c r="BS15" s="13"/>
+      <c r="BT15" s="13"/>
+      <c r="BU15" s="13"/>
+      <c r="BV15" s="13"/>
+      <c r="BW15" s="13"/>
+      <c r="BX15" s="13"/>
+      <c r="BY15" s="13"/>
+      <c r="BZ15" s="13"/>
+      <c r="CA15" s="13"/>
+      <c r="CB15" s="13"/>
+      <c r="CC15" s="13"/>
+      <c r="CD15" s="13"/>
+      <c r="CE15" s="13"/>
+      <c r="CF15" s="13"/>
+      <c r="CG15" s="13"/>
+      <c r="CH15" s="13"/>
+      <c r="CI15" s="13"/>
+      <c r="CJ15" s="13"/>
+      <c r="CK15" s="13"/>
+      <c r="CL15" s="13"/>
+      <c r="CM15" s="13"/>
+      <c r="CN15" s="13"/>
+      <c r="CO15" s="13"/>
+      <c r="CP15" s="13"/>
+      <c r="CQ15" s="13"/>
+      <c r="CR15" s="13"/>
+      <c r="CS15" s="13"/>
+      <c r="CT15" s="13"/>
+      <c r="CU15" s="13"/>
+      <c r="CV15" s="13"/>
+      <c r="CW15" s="13"/>
+      <c r="CX15" s="13"/>
+      <c r="CY15" s="13"/>
+      <c r="CZ15" s="13"/>
+      <c r="DA15" s="13"/>
+      <c r="DB15" s="13"/>
+      <c r="DC15" s="13"/>
+      <c r="DD15" s="13"/>
+      <c r="DE15" s="13"/>
+      <c r="DF15" s="13"/>
+      <c r="DG15" s="13"/>
+      <c r="DH15" s="13"/>
+      <c r="DI15" s="13"/>
+      <c r="DJ15" s="13"/>
+      <c r="DK15" s="13"/>
+      <c r="DL15" s="13"/>
+      <c r="DM15" s="13"/>
+      <c r="DN15" s="13"/>
+      <c r="DO15" s="26"/>
     </row>
-    <row r="16" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9">
-        <f t="shared" si="1"/>
+    <row r="16" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="30" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -4136,170 +4187,173 @@
       <c r="M16" s="2">
         <v>1951</v>
       </c>
-      <c r="N16" s="15"/>
-      <c r="O16" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C16)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D16)," ","-")&amp;"-"&amp;E16&amp;"-"&amp;F16))</f>
+      <c r="N16" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="O16" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>18230-daves-avenue-monte-sereno-ca-95030</v>
       </c>
-      <c r="P16" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P16" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q16" s="2"/>
-      <c r="R16" s="9" t="str">
+      <c r="R16" s="8" t="str">
         <f>IF(Q16="YES", COUNTIF($Q$2:Q16, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q16, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S16" s="13" t="s">
+      <c r="S16" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="T16" s="13" t="s">
+      <c r="T16" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="U16" s="13" t="s">
+      <c r="U16" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="V16" s="13" t="s">
+      <c r="V16" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="W16" s="13" t="s">
+      <c r="W16" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="X16" s="13" t="s">
+      <c r="X16" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="Y16" s="13" t="s">
+      <c r="Y16" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="Z16" s="13" t="s">
+      <c r="Z16" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AA16" s="13" t="s">
+      <c r="AA16" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="AB16" s="13" t="s">
+      <c r="AB16" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="AC16" s="13" t="s">
+      <c r="AC16" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="AD16" s="13" t="s">
+      <c r="AD16" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="AE16" s="13" t="s">
+      <c r="AE16" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AF16" s="13" t="s">
+      <c r="AF16" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="AG16" s="13" t="s">
+      <c r="AG16" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="AH16" s="13" t="s">
+      <c r="AH16" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="AI16" s="13" t="s">
+      <c r="AI16" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="AJ16" s="13" t="s">
+      <c r="AJ16" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AK16" s="13" t="s">
+      <c r="AK16" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="AL16" s="13" t="s">
+      <c r="AL16" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="AM16" s="13"/>
-      <c r="AN16" s="13"/>
-      <c r="AO16" s="13"/>
-      <c r="AP16" s="13"/>
-      <c r="AQ16" s="13"/>
-      <c r="AR16" s="13"/>
-      <c r="AS16" s="13"/>
-      <c r="AT16" s="13"/>
-      <c r="AU16" s="13"/>
-      <c r="AV16" s="13"/>
-      <c r="AW16" s="13"/>
-      <c r="AX16" s="13"/>
-      <c r="AY16" s="13"/>
-      <c r="AZ16" s="13"/>
-      <c r="BA16" s="13"/>
-      <c r="BB16" s="13"/>
-      <c r="BC16" s="13"/>
-      <c r="BD16" s="13"/>
-      <c r="BE16" s="13"/>
-      <c r="BF16" s="13"/>
-      <c r="BG16" s="13"/>
-      <c r="BH16" s="13"/>
-      <c r="BI16" s="13"/>
-      <c r="BJ16" s="13"/>
-      <c r="BK16" s="13"/>
-      <c r="BL16" s="13"/>
-      <c r="BM16" s="13"/>
-      <c r="BN16" s="13"/>
-      <c r="BO16" s="13"/>
-      <c r="BP16" s="13"/>
-      <c r="BQ16" s="13"/>
-      <c r="BR16" s="13"/>
-      <c r="BS16" s="13"/>
-      <c r="BT16" s="13"/>
-      <c r="BU16" s="13"/>
-      <c r="BV16" s="13"/>
-      <c r="BW16" s="13"/>
-      <c r="BX16" s="13"/>
-      <c r="BY16" s="13"/>
-      <c r="BZ16" s="13"/>
-      <c r="CA16" s="13"/>
-      <c r="CB16" s="13"/>
-      <c r="CC16" s="13"/>
-      <c r="CD16" s="13"/>
-      <c r="CE16" s="13"/>
-      <c r="CF16" s="13"/>
-      <c r="CG16" s="13"/>
-      <c r="CH16" s="13"/>
-      <c r="CI16" s="13"/>
-      <c r="CJ16" s="13"/>
-      <c r="CK16" s="13"/>
-      <c r="CL16" s="13"/>
-      <c r="CM16" s="13"/>
-      <c r="CN16" s="13"/>
-      <c r="CO16" s="13"/>
-      <c r="CP16" s="13"/>
-      <c r="CQ16" s="13"/>
-      <c r="CR16" s="13"/>
-      <c r="CS16" s="13"/>
-      <c r="CT16" s="13"/>
-      <c r="CU16" s="13"/>
-      <c r="CV16" s="13"/>
-      <c r="CW16" s="13"/>
-      <c r="CX16" s="13"/>
-      <c r="CY16" s="13"/>
-      <c r="CZ16" s="13"/>
-      <c r="DA16" s="13"/>
-      <c r="DB16" s="13"/>
-      <c r="DC16" s="13"/>
-      <c r="DD16" s="13"/>
-      <c r="DE16" s="13"/>
-      <c r="DF16" s="13"/>
-      <c r="DG16" s="13"/>
-      <c r="DH16" s="13"/>
-      <c r="DI16" s="13"/>
-      <c r="DJ16" s="13"/>
-      <c r="DK16" s="13"/>
-      <c r="DL16" s="13"/>
-      <c r="DM16" s="13"/>
-      <c r="DN16" s="13"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+      <c r="BI16" s="12"/>
+      <c r="BJ16" s="12"/>
+      <c r="BK16" s="12"/>
+      <c r="BL16" s="12"/>
+      <c r="BM16" s="12"/>
+      <c r="BN16" s="12"/>
+      <c r="BO16" s="12"/>
+      <c r="BP16" s="12"/>
+      <c r="BQ16" s="12"/>
+      <c r="BR16" s="12"/>
+      <c r="BS16" s="12"/>
+      <c r="BT16" s="12"/>
+      <c r="BU16" s="12"/>
+      <c r="BV16" s="12"/>
+      <c r="BW16" s="12"/>
+      <c r="BX16" s="12"/>
+      <c r="BY16" s="12"/>
+      <c r="BZ16" s="12"/>
+      <c r="CA16" s="12"/>
+      <c r="CB16" s="12"/>
+      <c r="CC16" s="12"/>
+      <c r="CD16" s="12"/>
+      <c r="CE16" s="12"/>
+      <c r="CF16" s="12"/>
+      <c r="CG16" s="12"/>
+      <c r="CH16" s="12"/>
+      <c r="CI16" s="12"/>
+      <c r="CJ16" s="12"/>
+      <c r="CK16" s="12"/>
+      <c r="CL16" s="12"/>
+      <c r="CM16" s="12"/>
+      <c r="CN16" s="12"/>
+      <c r="CO16" s="12"/>
+      <c r="CP16" s="12"/>
+      <c r="CQ16" s="12"/>
+      <c r="CR16" s="12"/>
+      <c r="CS16" s="12"/>
+      <c r="CT16" s="12"/>
+      <c r="CU16" s="12"/>
+      <c r="CV16" s="12"/>
+      <c r="CW16" s="12"/>
+      <c r="CX16" s="12"/>
+      <c r="CY16" s="12"/>
+      <c r="CZ16" s="12"/>
+      <c r="DA16" s="12"/>
+      <c r="DB16" s="12"/>
+      <c r="DC16" s="12"/>
+      <c r="DD16" s="12"/>
+      <c r="DE16" s="12"/>
+      <c r="DF16" s="12"/>
+      <c r="DG16" s="12"/>
+      <c r="DH16" s="12"/>
+      <c r="DI16" s="12"/>
+      <c r="DJ16" s="12"/>
+      <c r="DK16" s="12"/>
+      <c r="DL16" s="12"/>
+      <c r="DM16" s="12"/>
+      <c r="DN16" s="12"/>
+      <c r="DO16" s="26"/>
     </row>
-    <row r="17" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="20">
-        <f t="shared" si="1"/>
+    <row r="17" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="19">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="29" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -4330,170 +4384,173 @@
       <c r="M17" s="5">
         <v>2023</v>
       </c>
-      <c r="N17" s="16"/>
-      <c r="O17" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C17)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D17)," ","-")&amp;"-"&amp;E17&amp;"-"&amp;F17))</f>
+      <c r="N17" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O17" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>23000-congress-springs-rd-saratoga-ca-95070</v>
       </c>
-      <c r="P17" s="22" t="str">
-        <f t="shared" si="2"/>
+      <c r="P17" s="21" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q17" s="5"/>
-      <c r="R17" s="10" t="str">
+      <c r="R17" s="9" t="str">
         <f>IF(Q17="YES", COUNTIF($Q$2:Q17, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q17, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S17" s="14" t="s">
+      <c r="S17" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="T17" s="14" t="s">
+      <c r="T17" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="U17" s="14" t="s">
+      <c r="U17" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="V17" s="14" t="s">
+      <c r="V17" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="W17" s="14" t="s">
+      <c r="W17" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="X17" s="14" t="s">
+      <c r="X17" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="Y17" s="14" t="s">
+      <c r="Y17" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="Z17" s="14" t="s">
+      <c r="Z17" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AA17" s="14" t="s">
+      <c r="AA17" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AB17" s="14" t="s">
+      <c r="AB17" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="AC17" s="14" t="s">
+      <c r="AC17" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AD17" s="14" t="s">
+      <c r="AD17" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="AE17" s="14" t="s">
+      <c r="AE17" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AF17" s="14" t="s">
+      <c r="AF17" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AG17" s="14" t="s">
+      <c r="AG17" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="AH17" s="14" t="s">
+      <c r="AH17" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AI17" s="14" t="s">
+      <c r="AI17" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="AJ17" s="14" t="s">
+      <c r="AJ17" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AK17" s="14" t="s">
+      <c r="AK17" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AL17" s="14" t="s">
+      <c r="AL17" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="AM17" s="14"/>
-      <c r="AN17" s="14"/>
-      <c r="AO17" s="14"/>
-      <c r="AP17" s="14"/>
-      <c r="AQ17" s="14"/>
-      <c r="AR17" s="14"/>
-      <c r="AS17" s="14"/>
-      <c r="AT17" s="14"/>
-      <c r="AU17" s="14"/>
-      <c r="AV17" s="14"/>
-      <c r="AW17" s="14"/>
-      <c r="AX17" s="14"/>
-      <c r="AY17" s="14"/>
-      <c r="AZ17" s="14"/>
-      <c r="BA17" s="14"/>
-      <c r="BB17" s="14"/>
-      <c r="BC17" s="14"/>
-      <c r="BD17" s="14"/>
-      <c r="BE17" s="14"/>
-      <c r="BF17" s="14"/>
-      <c r="BG17" s="14"/>
-      <c r="BH17" s="14"/>
-      <c r="BI17" s="14"/>
-      <c r="BJ17" s="14"/>
-      <c r="BK17" s="14"/>
-      <c r="BL17" s="14"/>
-      <c r="BM17" s="14"/>
-      <c r="BN17" s="14"/>
-      <c r="BO17" s="14"/>
-      <c r="BP17" s="14"/>
-      <c r="BQ17" s="14"/>
-      <c r="BR17" s="14"/>
-      <c r="BS17" s="14"/>
-      <c r="BT17" s="14"/>
-      <c r="BU17" s="14"/>
-      <c r="BV17" s="14"/>
-      <c r="BW17" s="14"/>
-      <c r="BX17" s="14"/>
-      <c r="BY17" s="14"/>
-      <c r="BZ17" s="14"/>
-      <c r="CA17" s="14"/>
-      <c r="CB17" s="14"/>
-      <c r="CC17" s="14"/>
-      <c r="CD17" s="14"/>
-      <c r="CE17" s="14"/>
-      <c r="CF17" s="14"/>
-      <c r="CG17" s="14"/>
-      <c r="CH17" s="14"/>
-      <c r="CI17" s="14"/>
-      <c r="CJ17" s="14"/>
-      <c r="CK17" s="14"/>
-      <c r="CL17" s="14"/>
-      <c r="CM17" s="14"/>
-      <c r="CN17" s="14"/>
-      <c r="CO17" s="14"/>
-      <c r="CP17" s="14"/>
-      <c r="CQ17" s="14"/>
-      <c r="CR17" s="14"/>
-      <c r="CS17" s="14"/>
-      <c r="CT17" s="14"/>
-      <c r="CU17" s="14"/>
-      <c r="CV17" s="14"/>
-      <c r="CW17" s="14"/>
-      <c r="CX17" s="14"/>
-      <c r="CY17" s="14"/>
-      <c r="CZ17" s="14"/>
-      <c r="DA17" s="14"/>
-      <c r="DB17" s="14"/>
-      <c r="DC17" s="14"/>
-      <c r="DD17" s="14"/>
-      <c r="DE17" s="14"/>
-      <c r="DF17" s="14"/>
-      <c r="DG17" s="14"/>
-      <c r="DH17" s="14"/>
-      <c r="DI17" s="14"/>
-      <c r="DJ17" s="14"/>
-      <c r="DK17" s="14"/>
-      <c r="DL17" s="14"/>
-      <c r="DM17" s="14"/>
-      <c r="DN17" s="14"/>
+      <c r="AM17" s="13"/>
+      <c r="AN17" s="13"/>
+      <c r="AO17" s="13"/>
+      <c r="AP17" s="13"/>
+      <c r="AQ17" s="13"/>
+      <c r="AR17" s="13"/>
+      <c r="AS17" s="13"/>
+      <c r="AT17" s="13"/>
+      <c r="AU17" s="13"/>
+      <c r="AV17" s="13"/>
+      <c r="AW17" s="13"/>
+      <c r="AX17" s="13"/>
+      <c r="AY17" s="13"/>
+      <c r="AZ17" s="13"/>
+      <c r="BA17" s="13"/>
+      <c r="BB17" s="13"/>
+      <c r="BC17" s="13"/>
+      <c r="BD17" s="13"/>
+      <c r="BE17" s="13"/>
+      <c r="BF17" s="13"/>
+      <c r="BG17" s="13"/>
+      <c r="BH17" s="13"/>
+      <c r="BI17" s="13"/>
+      <c r="BJ17" s="13"/>
+      <c r="BK17" s="13"/>
+      <c r="BL17" s="13"/>
+      <c r="BM17" s="13"/>
+      <c r="BN17" s="13"/>
+      <c r="BO17" s="13"/>
+      <c r="BP17" s="13"/>
+      <c r="BQ17" s="13"/>
+      <c r="BR17" s="13"/>
+      <c r="BS17" s="13"/>
+      <c r="BT17" s="13"/>
+      <c r="BU17" s="13"/>
+      <c r="BV17" s="13"/>
+      <c r="BW17" s="13"/>
+      <c r="BX17" s="13"/>
+      <c r="BY17" s="13"/>
+      <c r="BZ17" s="13"/>
+      <c r="CA17" s="13"/>
+      <c r="CB17" s="13"/>
+      <c r="CC17" s="13"/>
+      <c r="CD17" s="13"/>
+      <c r="CE17" s="13"/>
+      <c r="CF17" s="13"/>
+      <c r="CG17" s="13"/>
+      <c r="CH17" s="13"/>
+      <c r="CI17" s="13"/>
+      <c r="CJ17" s="13"/>
+      <c r="CK17" s="13"/>
+      <c r="CL17" s="13"/>
+      <c r="CM17" s="13"/>
+      <c r="CN17" s="13"/>
+      <c r="CO17" s="13"/>
+      <c r="CP17" s="13"/>
+      <c r="CQ17" s="13"/>
+      <c r="CR17" s="13"/>
+      <c r="CS17" s="13"/>
+      <c r="CT17" s="13"/>
+      <c r="CU17" s="13"/>
+      <c r="CV17" s="13"/>
+      <c r="CW17" s="13"/>
+      <c r="CX17" s="13"/>
+      <c r="CY17" s="13"/>
+      <c r="CZ17" s="13"/>
+      <c r="DA17" s="13"/>
+      <c r="DB17" s="13"/>
+      <c r="DC17" s="13"/>
+      <c r="DD17" s="13"/>
+      <c r="DE17" s="13"/>
+      <c r="DF17" s="13"/>
+      <c r="DG17" s="13"/>
+      <c r="DH17" s="13"/>
+      <c r="DI17" s="13"/>
+      <c r="DJ17" s="13"/>
+      <c r="DK17" s="13"/>
+      <c r="DL17" s="13"/>
+      <c r="DM17" s="13"/>
+      <c r="DN17" s="13"/>
+      <c r="DO17" s="26"/>
     </row>
-    <row r="18" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="9">
-        <f t="shared" si="1"/>
+    <row r="18" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="30" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -4524,170 +4581,173 @@
       <c r="M18" s="2">
         <v>1997</v>
       </c>
-      <c r="N18" s="15"/>
-      <c r="O18" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C18)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D18)," ","-")&amp;"-"&amp;E18&amp;"-"&amp;F18))</f>
+      <c r="N18" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="O18" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>750-university-avenue-los-altos-ca-94022</v>
       </c>
-      <c r="P18" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P18" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q18" s="2"/>
-      <c r="R18" s="9" t="str">
+      <c r="R18" s="8" t="str">
         <f>IF(Q18="YES", COUNTIF($Q$2:Q18, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q18, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S18" s="13" t="s">
+      <c r="S18" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="T18" s="13" t="s">
+      <c r="T18" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="U18" s="13" t="s">
+      <c r="U18" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="V18" s="13" t="s">
+      <c r="V18" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="W18" s="13" t="s">
+      <c r="W18" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="X18" s="13" t="s">
+      <c r="X18" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="Y18" s="13" t="s">
+      <c r="Y18" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="Z18" s="13" t="s">
+      <c r="Z18" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="AA18" s="13" t="s">
+      <c r="AA18" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AB18" s="13" t="s">
+      <c r="AB18" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="AC18" s="13" t="s">
+      <c r="AC18" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AD18" s="13" t="s">
+      <c r="AD18" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="AE18" s="13" t="s">
+      <c r="AE18" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="AF18" s="13" t="s">
+      <c r="AF18" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AG18" s="13" t="s">
+      <c r="AG18" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="AH18" s="13" t="s">
+      <c r="AH18" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AI18" s="13" t="s">
+      <c r="AI18" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="AJ18" s="13" t="s">
+      <c r="AJ18" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="AK18" s="13" t="s">
+      <c r="AK18" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AL18" s="13" t="s">
+      <c r="AL18" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="AM18" s="13"/>
-      <c r="AN18" s="13"/>
-      <c r="AO18" s="13"/>
-      <c r="AP18" s="13"/>
-      <c r="AQ18" s="13"/>
-      <c r="AR18" s="13"/>
-      <c r="AS18" s="13"/>
-      <c r="AT18" s="13"/>
-      <c r="AU18" s="13"/>
-      <c r="AV18" s="13"/>
-      <c r="AW18" s="13"/>
-      <c r="AX18" s="13"/>
-      <c r="AY18" s="13"/>
-      <c r="AZ18" s="13"/>
-      <c r="BA18" s="13"/>
-      <c r="BB18" s="13"/>
-      <c r="BC18" s="13"/>
-      <c r="BD18" s="13"/>
-      <c r="BE18" s="13"/>
-      <c r="BF18" s="13"/>
-      <c r="BG18" s="13"/>
-      <c r="BH18" s="13"/>
-      <c r="BI18" s="13"/>
-      <c r="BJ18" s="13"/>
-      <c r="BK18" s="13"/>
-      <c r="BL18" s="13"/>
-      <c r="BM18" s="13"/>
-      <c r="BN18" s="13"/>
-      <c r="BO18" s="13"/>
-      <c r="BP18" s="13"/>
-      <c r="BQ18" s="13"/>
-      <c r="BR18" s="13"/>
-      <c r="BS18" s="13"/>
-      <c r="BT18" s="13"/>
-      <c r="BU18" s="13"/>
-      <c r="BV18" s="13"/>
-      <c r="BW18" s="13"/>
-      <c r="BX18" s="13"/>
-      <c r="BY18" s="13"/>
-      <c r="BZ18" s="13"/>
-      <c r="CA18" s="13"/>
-      <c r="CB18" s="13"/>
-      <c r="CC18" s="13"/>
-      <c r="CD18" s="13"/>
-      <c r="CE18" s="13"/>
-      <c r="CF18" s="13"/>
-      <c r="CG18" s="13"/>
-      <c r="CH18" s="13"/>
-      <c r="CI18" s="13"/>
-      <c r="CJ18" s="13"/>
-      <c r="CK18" s="13"/>
-      <c r="CL18" s="13"/>
-      <c r="CM18" s="13"/>
-      <c r="CN18" s="13"/>
-      <c r="CO18" s="13"/>
-      <c r="CP18" s="13"/>
-      <c r="CQ18" s="13"/>
-      <c r="CR18" s="13"/>
-      <c r="CS18" s="13"/>
-      <c r="CT18" s="13"/>
-      <c r="CU18" s="13"/>
-      <c r="CV18" s="13"/>
-      <c r="CW18" s="13"/>
-      <c r="CX18" s="13"/>
-      <c r="CY18" s="13"/>
-      <c r="CZ18" s="13"/>
-      <c r="DA18" s="13"/>
-      <c r="DB18" s="13"/>
-      <c r="DC18" s="13"/>
-      <c r="DD18" s="13"/>
-      <c r="DE18" s="13"/>
-      <c r="DF18" s="13"/>
-      <c r="DG18" s="13"/>
-      <c r="DH18" s="13"/>
-      <c r="DI18" s="13"/>
-      <c r="DJ18" s="13"/>
-      <c r="DK18" s="13"/>
-      <c r="DL18" s="13"/>
-      <c r="DM18" s="13"/>
-      <c r="DN18" s="13"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+      <c r="BI18" s="12"/>
+      <c r="BJ18" s="12"/>
+      <c r="BK18" s="12"/>
+      <c r="BL18" s="12"/>
+      <c r="BM18" s="12"/>
+      <c r="BN18" s="12"/>
+      <c r="BO18" s="12"/>
+      <c r="BP18" s="12"/>
+      <c r="BQ18" s="12"/>
+      <c r="BR18" s="12"/>
+      <c r="BS18" s="12"/>
+      <c r="BT18" s="12"/>
+      <c r="BU18" s="12"/>
+      <c r="BV18" s="12"/>
+      <c r="BW18" s="12"/>
+      <c r="BX18" s="12"/>
+      <c r="BY18" s="12"/>
+      <c r="BZ18" s="12"/>
+      <c r="CA18" s="12"/>
+      <c r="CB18" s="12"/>
+      <c r="CC18" s="12"/>
+      <c r="CD18" s="12"/>
+      <c r="CE18" s="12"/>
+      <c r="CF18" s="12"/>
+      <c r="CG18" s="12"/>
+      <c r="CH18" s="12"/>
+      <c r="CI18" s="12"/>
+      <c r="CJ18" s="12"/>
+      <c r="CK18" s="12"/>
+      <c r="CL18" s="12"/>
+      <c r="CM18" s="12"/>
+      <c r="CN18" s="12"/>
+      <c r="CO18" s="12"/>
+      <c r="CP18" s="12"/>
+      <c r="CQ18" s="12"/>
+      <c r="CR18" s="12"/>
+      <c r="CS18" s="12"/>
+      <c r="CT18" s="12"/>
+      <c r="CU18" s="12"/>
+      <c r="CV18" s="12"/>
+      <c r="CW18" s="12"/>
+      <c r="CX18" s="12"/>
+      <c r="CY18" s="12"/>
+      <c r="CZ18" s="12"/>
+      <c r="DA18" s="12"/>
+      <c r="DB18" s="12"/>
+      <c r="DC18" s="12"/>
+      <c r="DD18" s="12"/>
+      <c r="DE18" s="12"/>
+      <c r="DF18" s="12"/>
+      <c r="DG18" s="12"/>
+      <c r="DH18" s="12"/>
+      <c r="DI18" s="12"/>
+      <c r="DJ18" s="12"/>
+      <c r="DK18" s="12"/>
+      <c r="DL18" s="12"/>
+      <c r="DM18" s="12"/>
+      <c r="DN18" s="12"/>
+      <c r="DO18" s="26"/>
     </row>
-    <row r="19" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="20">
-        <f t="shared" si="1"/>
+    <row r="19" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="19">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="29" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -4718,170 +4778,173 @@
       <c r="M19" s="5">
         <v>1994</v>
       </c>
-      <c r="N19" s="16"/>
-      <c r="O19" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C19)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D19)," ","-")&amp;"-"&amp;E19&amp;"-"&amp;F19))</f>
+      <c r="N19" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O19" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>16100-kennedy-road-los-gatos-ca-95032</v>
       </c>
-      <c r="P19" s="22" t="str">
-        <f t="shared" si="2"/>
+      <c r="P19" s="21" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q19" s="5"/>
-      <c r="R19" s="10" t="str">
+      <c r="R19" s="9" t="str">
         <f>IF(Q19="YES", COUNTIF($Q$2:Q19, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q19, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S19" s="14" t="s">
+      <c r="S19" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="T19" s="14" t="s">
+      <c r="T19" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="U19" s="14" t="s">
+      <c r="U19" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="V19" s="14" t="s">
+      <c r="V19" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="W19" s="14" t="s">
+      <c r="W19" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="X19" s="14" t="s">
+      <c r="X19" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="Y19" s="14" t="s">
+      <c r="Y19" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="Z19" s="14" t="s">
+      <c r="Z19" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AA19" s="14" t="s">
+      <c r="AA19" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AB19" s="14" t="s">
+      <c r="AB19" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="AC19" s="14" t="s">
+      <c r="AC19" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AD19" s="14" t="s">
+      <c r="AD19" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="AE19" s="14" t="s">
+      <c r="AE19" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AF19" s="14" t="s">
+      <c r="AF19" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AG19" s="14" t="s">
+      <c r="AG19" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="AH19" s="14" t="s">
+      <c r="AH19" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AI19" s="14" t="s">
+      <c r="AI19" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="AJ19" s="14" t="s">
+      <c r="AJ19" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AK19" s="14" t="s">
+      <c r="AK19" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AL19" s="14" t="s">
+      <c r="AL19" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="AM19" s="14"/>
-      <c r="AN19" s="14"/>
-      <c r="AO19" s="14"/>
-      <c r="AP19" s="14"/>
-      <c r="AQ19" s="14"/>
-      <c r="AR19" s="14"/>
-      <c r="AS19" s="14"/>
-      <c r="AT19" s="14"/>
-      <c r="AU19" s="14"/>
-      <c r="AV19" s="14"/>
-      <c r="AW19" s="14"/>
-      <c r="AX19" s="14"/>
-      <c r="AY19" s="14"/>
-      <c r="AZ19" s="14"/>
-      <c r="BA19" s="14"/>
-      <c r="BB19" s="14"/>
-      <c r="BC19" s="14"/>
-      <c r="BD19" s="14"/>
-      <c r="BE19" s="14"/>
-      <c r="BF19" s="14"/>
-      <c r="BG19" s="14"/>
-      <c r="BH19" s="14"/>
-      <c r="BI19" s="14"/>
-      <c r="BJ19" s="14"/>
-      <c r="BK19" s="14"/>
-      <c r="BL19" s="14"/>
-      <c r="BM19" s="14"/>
-      <c r="BN19" s="14"/>
-      <c r="BO19" s="14"/>
-      <c r="BP19" s="14"/>
-      <c r="BQ19" s="14"/>
-      <c r="BR19" s="14"/>
-      <c r="BS19" s="14"/>
-      <c r="BT19" s="14"/>
-      <c r="BU19" s="14"/>
-      <c r="BV19" s="14"/>
-      <c r="BW19" s="14"/>
-      <c r="BX19" s="14"/>
-      <c r="BY19" s="14"/>
-      <c r="BZ19" s="14"/>
-      <c r="CA19" s="14"/>
-      <c r="CB19" s="14"/>
-      <c r="CC19" s="14"/>
-      <c r="CD19" s="14"/>
-      <c r="CE19" s="14"/>
-      <c r="CF19" s="14"/>
-      <c r="CG19" s="14"/>
-      <c r="CH19" s="14"/>
-      <c r="CI19" s="14"/>
-      <c r="CJ19" s="14"/>
-      <c r="CK19" s="14"/>
-      <c r="CL19" s="14"/>
-      <c r="CM19" s="14"/>
-      <c r="CN19" s="14"/>
-      <c r="CO19" s="14"/>
-      <c r="CP19" s="14"/>
-      <c r="CQ19" s="14"/>
-      <c r="CR19" s="14"/>
-      <c r="CS19" s="14"/>
-      <c r="CT19" s="14"/>
-      <c r="CU19" s="14"/>
-      <c r="CV19" s="14"/>
-      <c r="CW19" s="14"/>
-      <c r="CX19" s="14"/>
-      <c r="CY19" s="14"/>
-      <c r="CZ19" s="14"/>
-      <c r="DA19" s="14"/>
-      <c r="DB19" s="14"/>
-      <c r="DC19" s="14"/>
-      <c r="DD19" s="14"/>
-      <c r="DE19" s="14"/>
-      <c r="DF19" s="14"/>
-      <c r="DG19" s="14"/>
-      <c r="DH19" s="14"/>
-      <c r="DI19" s="14"/>
-      <c r="DJ19" s="14"/>
-      <c r="DK19" s="14"/>
-      <c r="DL19" s="14"/>
-      <c r="DM19" s="14"/>
-      <c r="DN19" s="14"/>
+      <c r="AM19" s="13"/>
+      <c r="AN19" s="13"/>
+      <c r="AO19" s="13"/>
+      <c r="AP19" s="13"/>
+      <c r="AQ19" s="13"/>
+      <c r="AR19" s="13"/>
+      <c r="AS19" s="13"/>
+      <c r="AT19" s="13"/>
+      <c r="AU19" s="13"/>
+      <c r="AV19" s="13"/>
+      <c r="AW19" s="13"/>
+      <c r="AX19" s="13"/>
+      <c r="AY19" s="13"/>
+      <c r="AZ19" s="13"/>
+      <c r="BA19" s="13"/>
+      <c r="BB19" s="13"/>
+      <c r="BC19" s="13"/>
+      <c r="BD19" s="13"/>
+      <c r="BE19" s="13"/>
+      <c r="BF19" s="13"/>
+      <c r="BG19" s="13"/>
+      <c r="BH19" s="13"/>
+      <c r="BI19" s="13"/>
+      <c r="BJ19" s="13"/>
+      <c r="BK19" s="13"/>
+      <c r="BL19" s="13"/>
+      <c r="BM19" s="13"/>
+      <c r="BN19" s="13"/>
+      <c r="BO19" s="13"/>
+      <c r="BP19" s="13"/>
+      <c r="BQ19" s="13"/>
+      <c r="BR19" s="13"/>
+      <c r="BS19" s="13"/>
+      <c r="BT19" s="13"/>
+      <c r="BU19" s="13"/>
+      <c r="BV19" s="13"/>
+      <c r="BW19" s="13"/>
+      <c r="BX19" s="13"/>
+      <c r="BY19" s="13"/>
+      <c r="BZ19" s="13"/>
+      <c r="CA19" s="13"/>
+      <c r="CB19" s="13"/>
+      <c r="CC19" s="13"/>
+      <c r="CD19" s="13"/>
+      <c r="CE19" s="13"/>
+      <c r="CF19" s="13"/>
+      <c r="CG19" s="13"/>
+      <c r="CH19" s="13"/>
+      <c r="CI19" s="13"/>
+      <c r="CJ19" s="13"/>
+      <c r="CK19" s="13"/>
+      <c r="CL19" s="13"/>
+      <c r="CM19" s="13"/>
+      <c r="CN19" s="13"/>
+      <c r="CO19" s="13"/>
+      <c r="CP19" s="13"/>
+      <c r="CQ19" s="13"/>
+      <c r="CR19" s="13"/>
+      <c r="CS19" s="13"/>
+      <c r="CT19" s="13"/>
+      <c r="CU19" s="13"/>
+      <c r="CV19" s="13"/>
+      <c r="CW19" s="13"/>
+      <c r="CX19" s="13"/>
+      <c r="CY19" s="13"/>
+      <c r="CZ19" s="13"/>
+      <c r="DA19" s="13"/>
+      <c r="DB19" s="13"/>
+      <c r="DC19" s="13"/>
+      <c r="DD19" s="13"/>
+      <c r="DE19" s="13"/>
+      <c r="DF19" s="13"/>
+      <c r="DG19" s="13"/>
+      <c r="DH19" s="13"/>
+      <c r="DI19" s="13"/>
+      <c r="DJ19" s="13"/>
+      <c r="DK19" s="13"/>
+      <c r="DL19" s="13"/>
+      <c r="DM19" s="13"/>
+      <c r="DN19" s="13"/>
+      <c r="DO19" s="26"/>
     </row>
-    <row r="20" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="9">
-        <f t="shared" si="1"/>
+    <row r="20" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="30" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -4912,170 +4975,173 @@
       <c r="M20" s="2">
         <v>1980</v>
       </c>
-      <c r="N20" s="15"/>
-      <c r="O20" s="17" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C20)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D20)," ","-")&amp;"-"&amp;E20&amp;"-"&amp;F20))</f>
+      <c r="N20" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="O20" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>21540-almaden-road-san-jose-ca-95120</v>
       </c>
-      <c r="P20" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P20" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q20" s="2"/>
-      <c r="R20" s="9" t="str">
+      <c r="R20" s="8" t="str">
         <f>IF(Q20="YES", COUNTIF($Q$2:Q20, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q20, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S20" s="13" t="s">
+      <c r="S20" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="T20" s="13" t="s">
+      <c r="T20" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="U20" s="13" t="s">
+      <c r="U20" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="V20" s="13" t="s">
+      <c r="V20" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="W20" s="13" t="s">
+      <c r="W20" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="X20" s="13" t="s">
+      <c r="X20" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="Y20" s="13" t="s">
+      <c r="Y20" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="Z20" s="13" t="s">
+      <c r="Z20" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AA20" s="13" t="s">
+      <c r="AA20" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="AB20" s="13" t="s">
+      <c r="AB20" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="AC20" s="13" t="s">
+      <c r="AC20" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="AD20" s="13" t="s">
+      <c r="AD20" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="AE20" s="13" t="s">
+      <c r="AE20" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AF20" s="13" t="s">
+      <c r="AF20" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="AG20" s="13" t="s">
+      <c r="AG20" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="AH20" s="13" t="s">
+      <c r="AH20" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="AI20" s="13" t="s">
+      <c r="AI20" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="AJ20" s="13" t="s">
+      <c r="AJ20" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AK20" s="13" t="s">
+      <c r="AK20" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="AL20" s="13" t="s">
+      <c r="AL20" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="AM20" s="13"/>
-      <c r="AN20" s="13"/>
-      <c r="AO20" s="13"/>
-      <c r="AP20" s="13"/>
-      <c r="AQ20" s="13"/>
-      <c r="AR20" s="13"/>
-      <c r="AS20" s="13"/>
-      <c r="AT20" s="13"/>
-      <c r="AU20" s="13"/>
-      <c r="AV20" s="13"/>
-      <c r="AW20" s="13"/>
-      <c r="AX20" s="13"/>
-      <c r="AY20" s="13"/>
-      <c r="AZ20" s="13"/>
-      <c r="BA20" s="13"/>
-      <c r="BB20" s="13"/>
-      <c r="BC20" s="13"/>
-      <c r="BD20" s="13"/>
-      <c r="BE20" s="13"/>
-      <c r="BF20" s="13"/>
-      <c r="BG20" s="13"/>
-      <c r="BH20" s="13"/>
-      <c r="BI20" s="13"/>
-      <c r="BJ20" s="13"/>
-      <c r="BK20" s="13"/>
-      <c r="BL20" s="13"/>
-      <c r="BM20" s="13"/>
-      <c r="BN20" s="13"/>
-      <c r="BO20" s="13"/>
-      <c r="BP20" s="13"/>
-      <c r="BQ20" s="13"/>
-      <c r="BR20" s="13"/>
-      <c r="BS20" s="13"/>
-      <c r="BT20" s="13"/>
-      <c r="BU20" s="13"/>
-      <c r="BV20" s="13"/>
-      <c r="BW20" s="13"/>
-      <c r="BX20" s="13"/>
-      <c r="BY20" s="13"/>
-      <c r="BZ20" s="13"/>
-      <c r="CA20" s="13"/>
-      <c r="CB20" s="13"/>
-      <c r="CC20" s="13"/>
-      <c r="CD20" s="13"/>
-      <c r="CE20" s="13"/>
-      <c r="CF20" s="13"/>
-      <c r="CG20" s="13"/>
-      <c r="CH20" s="13"/>
-      <c r="CI20" s="13"/>
-      <c r="CJ20" s="13"/>
-      <c r="CK20" s="13"/>
-      <c r="CL20" s="13"/>
-      <c r="CM20" s="13"/>
-      <c r="CN20" s="13"/>
-      <c r="CO20" s="13"/>
-      <c r="CP20" s="13"/>
-      <c r="CQ20" s="13"/>
-      <c r="CR20" s="13"/>
-      <c r="CS20" s="13"/>
-      <c r="CT20" s="13"/>
-      <c r="CU20" s="13"/>
-      <c r="CV20" s="13"/>
-      <c r="CW20" s="13"/>
-      <c r="CX20" s="13"/>
-      <c r="CY20" s="13"/>
-      <c r="CZ20" s="13"/>
-      <c r="DA20" s="13"/>
-      <c r="DB20" s="13"/>
-      <c r="DC20" s="13"/>
-      <c r="DD20" s="13"/>
-      <c r="DE20" s="13"/>
-      <c r="DF20" s="13"/>
-      <c r="DG20" s="13"/>
-      <c r="DH20" s="13"/>
-      <c r="DI20" s="13"/>
-      <c r="DJ20" s="13"/>
-      <c r="DK20" s="13"/>
-      <c r="DL20" s="13"/>
-      <c r="DM20" s="13"/>
-      <c r="DN20" s="13"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+      <c r="BI20" s="12"/>
+      <c r="BJ20" s="12"/>
+      <c r="BK20" s="12"/>
+      <c r="BL20" s="12"/>
+      <c r="BM20" s="12"/>
+      <c r="BN20" s="12"/>
+      <c r="BO20" s="12"/>
+      <c r="BP20" s="12"/>
+      <c r="BQ20" s="12"/>
+      <c r="BR20" s="12"/>
+      <c r="BS20" s="12"/>
+      <c r="BT20" s="12"/>
+      <c r="BU20" s="12"/>
+      <c r="BV20" s="12"/>
+      <c r="BW20" s="12"/>
+      <c r="BX20" s="12"/>
+      <c r="BY20" s="12"/>
+      <c r="BZ20" s="12"/>
+      <c r="CA20" s="12"/>
+      <c r="CB20" s="12"/>
+      <c r="CC20" s="12"/>
+      <c r="CD20" s="12"/>
+      <c r="CE20" s="12"/>
+      <c r="CF20" s="12"/>
+      <c r="CG20" s="12"/>
+      <c r="CH20" s="12"/>
+      <c r="CI20" s="12"/>
+      <c r="CJ20" s="12"/>
+      <c r="CK20" s="12"/>
+      <c r="CL20" s="12"/>
+      <c r="CM20" s="12"/>
+      <c r="CN20" s="12"/>
+      <c r="CO20" s="12"/>
+      <c r="CP20" s="12"/>
+      <c r="CQ20" s="12"/>
+      <c r="CR20" s="12"/>
+      <c r="CS20" s="12"/>
+      <c r="CT20" s="12"/>
+      <c r="CU20" s="12"/>
+      <c r="CV20" s="12"/>
+      <c r="CW20" s="12"/>
+      <c r="CX20" s="12"/>
+      <c r="CY20" s="12"/>
+      <c r="CZ20" s="12"/>
+      <c r="DA20" s="12"/>
+      <c r="DB20" s="12"/>
+      <c r="DC20" s="12"/>
+      <c r="DD20" s="12"/>
+      <c r="DE20" s="12"/>
+      <c r="DF20" s="12"/>
+      <c r="DG20" s="12"/>
+      <c r="DH20" s="12"/>
+      <c r="DI20" s="12"/>
+      <c r="DJ20" s="12"/>
+      <c r="DK20" s="12"/>
+      <c r="DL20" s="12"/>
+      <c r="DM20" s="12"/>
+      <c r="DN20" s="12"/>
+      <c r="DO20" s="26"/>
     </row>
-    <row r="21" spans="1:118" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="20">
-        <f t="shared" si="1"/>
+    <row r="21" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="19">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="29" t="s">
         <v>51</v>
       </c>
       <c r="D21" s="6" t="s">
@@ -5106,162 +5172,289 @@
       <c r="M21" s="5">
         <v>1951</v>
       </c>
-      <c r="N21" s="16"/>
-      <c r="O21" s="18" t="str">
-        <f>LOWER(SUBSTITUTE(TRIM(C21)," ","-")&amp;"-"&amp;(SUBSTITUTE(TRIM(D21)," ","-")&amp;"-"&amp;E21&amp;"-"&amp;F21))</f>
+      <c r="N21" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O21" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>4120-miranda-avenue-palo-alto-ca-94306</v>
       </c>
-      <c r="P21" s="22" t="str">
-        <f t="shared" si="2"/>
+      <c r="P21" s="21" t="str">
+        <f t="shared" si="3"/>
         <v>---</v>
       </c>
       <c r="Q21" s="5"/>
-      <c r="R21" s="10" t="str">
+      <c r="R21" s="9" t="str">
         <f>IF(Q21="YES", COUNTIF($Q$2:Q21, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q21, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
         <v/>
       </c>
-      <c r="S21" s="14" t="s">
+      <c r="S21" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="T21" s="14" t="s">
+      <c r="T21" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="U21" s="14" t="s">
+      <c r="U21" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="V21" s="14" t="s">
+      <c r="V21" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="W21" s="14" t="s">
+      <c r="W21" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="X21" s="14" t="s">
+      <c r="X21" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="Y21" s="14" t="s">
+      <c r="Y21" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="Z21" s="14" t="s">
+      <c r="Z21" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AA21" s="14" t="s">
+      <c r="AA21" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AB21" s="14" t="s">
+      <c r="AB21" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AC21" s="14" t="s">
+      <c r="AC21" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AD21" s="14" t="s">
+      <c r="AD21" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="AE21" s="14" t="s">
+      <c r="AE21" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AF21" s="14" t="s">
+      <c r="AF21" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AG21" s="14" t="s">
+      <c r="AG21" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AH21" s="14" t="s">
+      <c r="AH21" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AI21" s="14" t="s">
+      <c r="AI21" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="AJ21" s="14" t="s">
+      <c r="AJ21" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AK21" s="14" t="s">
+      <c r="AK21" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AL21" s="14" t="s">
+      <c r="AL21" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AM21" s="14"/>
-      <c r="AN21" s="14"/>
-      <c r="AO21" s="14"/>
-      <c r="AP21" s="14"/>
-      <c r="AQ21" s="14"/>
-      <c r="AR21" s="14"/>
-      <c r="AS21" s="14"/>
-      <c r="AT21" s="14"/>
-      <c r="AU21" s="14"/>
-      <c r="AV21" s="14"/>
-      <c r="AW21" s="14"/>
-      <c r="AX21" s="14"/>
-      <c r="AY21" s="14"/>
-      <c r="AZ21" s="14"/>
-      <c r="BA21" s="14"/>
-      <c r="BB21" s="14"/>
-      <c r="BC21" s="14"/>
-      <c r="BD21" s="14"/>
-      <c r="BE21" s="14"/>
-      <c r="BF21" s="14"/>
-      <c r="BG21" s="14"/>
-      <c r="BH21" s="14"/>
-      <c r="BI21" s="14"/>
-      <c r="BJ21" s="14"/>
-      <c r="BK21" s="14"/>
-      <c r="BL21" s="14"/>
-      <c r="BM21" s="14"/>
-      <c r="BN21" s="14"/>
-      <c r="BO21" s="14"/>
-      <c r="BP21" s="14"/>
-      <c r="BQ21" s="14"/>
-      <c r="BR21" s="14"/>
-      <c r="BS21" s="14"/>
-      <c r="BT21" s="14"/>
-      <c r="BU21" s="14"/>
-      <c r="BV21" s="14"/>
-      <c r="BW21" s="14"/>
-      <c r="BX21" s="14"/>
-      <c r="BY21" s="14"/>
-      <c r="BZ21" s="14"/>
-      <c r="CA21" s="14"/>
-      <c r="CB21" s="14"/>
-      <c r="CC21" s="14"/>
-      <c r="CD21" s="14"/>
-      <c r="CE21" s="14"/>
-      <c r="CF21" s="14"/>
-      <c r="CG21" s="14"/>
-      <c r="CH21" s="14"/>
-      <c r="CI21" s="14"/>
-      <c r="CJ21" s="14"/>
-      <c r="CK21" s="14"/>
-      <c r="CL21" s="14"/>
-      <c r="CM21" s="14"/>
-      <c r="CN21" s="14"/>
-      <c r="CO21" s="14"/>
-      <c r="CP21" s="14"/>
-      <c r="CQ21" s="14"/>
-      <c r="CR21" s="14"/>
-      <c r="CS21" s="14"/>
-      <c r="CT21" s="14"/>
-      <c r="CU21" s="14"/>
-      <c r="CV21" s="14"/>
-      <c r="CW21" s="14"/>
-      <c r="CX21" s="14"/>
-      <c r="CY21" s="14"/>
-      <c r="CZ21" s="14"/>
-      <c r="DA21" s="14"/>
-      <c r="DB21" s="14"/>
-      <c r="DC21" s="14"/>
-      <c r="DD21" s="14"/>
-      <c r="DE21" s="14"/>
-      <c r="DF21" s="14"/>
-      <c r="DG21" s="14"/>
-      <c r="DH21" s="14"/>
-      <c r="DI21" s="14"/>
-      <c r="DJ21" s="14"/>
-      <c r="DK21" s="14"/>
-      <c r="DL21" s="14"/>
-      <c r="DM21" s="14"/>
-      <c r="DN21" s="14"/>
+      <c r="AM21" s="13"/>
+      <c r="AN21" s="13"/>
+      <c r="AO21" s="13"/>
+      <c r="AP21" s="13"/>
+      <c r="AQ21" s="13"/>
+      <c r="AR21" s="13"/>
+      <c r="AS21" s="13"/>
+      <c r="AT21" s="13"/>
+      <c r="AU21" s="13"/>
+      <c r="AV21" s="13"/>
+      <c r="AW21" s="13"/>
+      <c r="AX21" s="13"/>
+      <c r="AY21" s="13"/>
+      <c r="AZ21" s="13"/>
+      <c r="BA21" s="13"/>
+      <c r="BB21" s="13"/>
+      <c r="BC21" s="13"/>
+      <c r="BD21" s="13"/>
+      <c r="BE21" s="13"/>
+      <c r="BF21" s="13"/>
+      <c r="BG21" s="13"/>
+      <c r="BH21" s="13"/>
+      <c r="BI21" s="13"/>
+      <c r="BJ21" s="13"/>
+      <c r="BK21" s="13"/>
+      <c r="BL21" s="13"/>
+      <c r="BM21" s="13"/>
+      <c r="BN21" s="13"/>
+      <c r="BO21" s="13"/>
+      <c r="BP21" s="13"/>
+      <c r="BQ21" s="13"/>
+      <c r="BR21" s="13"/>
+      <c r="BS21" s="13"/>
+      <c r="BT21" s="13"/>
+      <c r="BU21" s="13"/>
+      <c r="BV21" s="13"/>
+      <c r="BW21" s="13"/>
+      <c r="BX21" s="13"/>
+      <c r="BY21" s="13"/>
+      <c r="BZ21" s="13"/>
+      <c r="CA21" s="13"/>
+      <c r="CB21" s="13"/>
+      <c r="CC21" s="13"/>
+      <c r="CD21" s="13"/>
+      <c r="CE21" s="13"/>
+      <c r="CF21" s="13"/>
+      <c r="CG21" s="13"/>
+      <c r="CH21" s="13"/>
+      <c r="CI21" s="13"/>
+      <c r="CJ21" s="13"/>
+      <c r="CK21" s="13"/>
+      <c r="CL21" s="13"/>
+      <c r="CM21" s="13"/>
+      <c r="CN21" s="13"/>
+      <c r="CO21" s="13"/>
+      <c r="CP21" s="13"/>
+      <c r="CQ21" s="13"/>
+      <c r="CR21" s="13"/>
+      <c r="CS21" s="13"/>
+      <c r="CT21" s="13"/>
+      <c r="CU21" s="13"/>
+      <c r="CV21" s="13"/>
+      <c r="CW21" s="13"/>
+      <c r="CX21" s="13"/>
+      <c r="CY21" s="13"/>
+      <c r="CZ21" s="13"/>
+      <c r="DA21" s="13"/>
+      <c r="DB21" s="13"/>
+      <c r="DC21" s="13"/>
+      <c r="DD21" s="13"/>
+      <c r="DE21" s="13"/>
+      <c r="DF21" s="13"/>
+      <c r="DG21" s="13"/>
+      <c r="DH21" s="13"/>
+      <c r="DI21" s="13"/>
+      <c r="DJ21" s="13"/>
+      <c r="DK21" s="13"/>
+      <c r="DL21" s="13"/>
+      <c r="DM21" s="13"/>
+      <c r="DN21" s="13"/>
+      <c r="DO21" s="26"/>
+    </row>
+    <row r="22" spans="1:119" x14ac:dyDescent="0.35">
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="26"/>
+      <c r="W22" s="26"/>
+      <c r="X22" s="26"/>
+      <c r="Y22" s="26"/>
+      <c r="Z22" s="26"/>
+      <c r="AA22" s="26"/>
+      <c r="AB22" s="26"/>
+      <c r="AC22" s="26"/>
+      <c r="AD22" s="26"/>
+      <c r="AE22" s="26"/>
+      <c r="AF22" s="26"/>
+      <c r="AG22" s="26"/>
+      <c r="AH22" s="26"/>
+      <c r="AI22" s="26"/>
+      <c r="AJ22" s="26"/>
+      <c r="AK22" s="26"/>
+      <c r="AL22" s="26"/>
+      <c r="AM22" s="26"/>
+      <c r="AN22" s="26"/>
+      <c r="AO22" s="26"/>
+      <c r="AP22" s="26"/>
+      <c r="AQ22" s="26"/>
+      <c r="AR22" s="26"/>
+      <c r="AS22" s="26"/>
+      <c r="AT22" s="26"/>
+      <c r="AU22" s="26"/>
+      <c r="AV22" s="26"/>
+      <c r="AW22" s="26"/>
+      <c r="AX22" s="26"/>
+      <c r="AY22" s="26"/>
+      <c r="AZ22" s="26"/>
+      <c r="BA22" s="26"/>
+      <c r="BB22" s="26"/>
+      <c r="BC22" s="26"/>
+      <c r="BD22" s="26"/>
+      <c r="BE22" s="26"/>
+      <c r="BF22" s="26"/>
+      <c r="BG22" s="26"/>
+      <c r="BH22" s="26"/>
+      <c r="BI22" s="26"/>
+      <c r="BJ22" s="26"/>
+      <c r="BK22" s="26"/>
+      <c r="BL22" s="26"/>
+      <c r="BM22" s="26"/>
+      <c r="BN22" s="26"/>
+      <c r="BO22" s="26"/>
+      <c r="BP22" s="26"/>
+      <c r="BQ22" s="26"/>
+      <c r="BR22" s="26"/>
+      <c r="BS22" s="26"/>
+      <c r="BT22" s="26"/>
+      <c r="BU22" s="26"/>
+      <c r="BV22" s="26"/>
+      <c r="BW22" s="26"/>
+      <c r="BX22" s="26"/>
+      <c r="BY22" s="26"/>
+      <c r="BZ22" s="26"/>
+      <c r="CA22" s="26"/>
+      <c r="CB22" s="26"/>
+      <c r="CC22" s="26"/>
+      <c r="CD22" s="26"/>
+      <c r="CE22" s="26"/>
+      <c r="CF22" s="26"/>
+      <c r="CG22" s="26"/>
+      <c r="CH22" s="26"/>
+      <c r="CI22" s="26"/>
+      <c r="CJ22" s="26"/>
+      <c r="CK22" s="26"/>
+      <c r="CL22" s="26"/>
+      <c r="CM22" s="26"/>
+      <c r="CN22" s="26"/>
+      <c r="CO22" s="26"/>
+      <c r="CP22" s="26"/>
+      <c r="CQ22" s="26"/>
+      <c r="CR22" s="26"/>
+      <c r="CS22" s="26"/>
+      <c r="CT22" s="26"/>
+      <c r="CU22" s="26"/>
+      <c r="CV22" s="26"/>
+      <c r="CW22" s="26"/>
+      <c r="CX22" s="26"/>
+      <c r="CY22" s="26"/>
+      <c r="CZ22" s="26"/>
+      <c r="DA22" s="26"/>
+      <c r="DB22" s="26"/>
+      <c r="DC22" s="26"/>
+      <c r="DD22" s="26"/>
+      <c r="DE22" s="26"/>
+      <c r="DF22" s="26"/>
+      <c r="DG22" s="26"/>
+      <c r="DH22" s="26"/>
+      <c r="DI22" s="26"/>
+      <c r="DJ22" s="26"/>
+      <c r="DK22" s="26"/>
+      <c r="DL22" s="26"/>
+      <c r="DM22" s="26"/>
+      <c r="DN22" s="26"/>
+      <c r="DO22" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="F1:F21" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/properties.xlsx
+++ b/src/data/properties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE74AFD8-EF86-4A44-A666-41FE82E0E531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84549F4B-67AD-4A6A-B21F-8A389EC018BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9680" yWindow="2990" windowWidth="26980" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7480" yWindow="3280" windowWidth="26980" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="205">
   <si>
     <t>status</t>
   </si>
@@ -653,6 +653,9 @@
   </si>
   <si>
     <t>check-duplicated-slug</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -778,7 +781,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -843,9 +846,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -867,6 +867,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1200,10 +1206,10 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="30" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1233,19 +1239,19 @@
       <c r="M1" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="O1" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="P1" s="26" t="s">
         <v>203</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="24" t="s">
+      <c r="R1" s="23" t="s">
         <v>167</v>
       </c>
       <c r="S1" s="11" t="s">
@@ -1548,7 +1554,7 @@
       <c r="DN1" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="DO1" s="26"/>
+      <c r="DO1" s="25"/>
     </row>
     <row r="2" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
@@ -1558,7 +1564,7 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="27" t="s">
         <v>200</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -1606,7 +1612,7 @@
         <v>14</v>
       </c>
       <c r="R2" s="8" t="str">
-        <f>IF(Q2="YES", COUNTIF($Q$2:Q2, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q2, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+        <f>IF(Q2="YES", COUNTIF($Q$2:Q2, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q2, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>1st</v>
       </c>
       <c r="S2" s="12" t="s">
@@ -1749,7 +1755,7 @@
       <c r="DL2" s="12"/>
       <c r="DM2" s="12"/>
       <c r="DN2" s="12"/>
-      <c r="DO2" s="26"/>
+      <c r="DO2" s="25"/>
     </row>
     <row r="3" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19">
@@ -1759,7 +1765,7 @@
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>200</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -1768,7 +1774,7 @@
       <c r="E3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="24" t="s">
         <v>202</v>
       </c>
       <c r="G3" s="5">
@@ -1803,8 +1809,8 @@
       </c>
       <c r="Q3" s="5"/>
       <c r="R3" s="9" t="str">
-        <f>IF(Q3="YES", COUNTIF($Q$2:Q3, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q3, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q3="YES", COUNTIF($Q$2:Q3, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q3, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S3" s="13" t="s">
         <v>192</v>
@@ -1908,7 +1914,7 @@
       <c r="DL3" s="13"/>
       <c r="DM3" s="13"/>
       <c r="DN3" s="13"/>
-      <c r="DO3" s="26"/>
+      <c r="DO3" s="25"/>
     </row>
     <row r="4" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
@@ -1918,7 +1924,7 @@
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>200</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -1962,8 +1968,8 @@
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="8" t="str">
-        <f>IF(Q4="YES", COUNTIF($Q$2:Q4, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q4, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q4="YES", COUNTIF($Q$2:Q4, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q4, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S4" s="12" t="s">
         <v>193</v>
@@ -2069,7 +2075,7 @@
       <c r="DL4" s="12"/>
       <c r="DM4" s="12"/>
       <c r="DN4" s="12"/>
-      <c r="DO4" s="26"/>
+      <c r="DO4" s="25"/>
     </row>
     <row r="5" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19">
@@ -2079,7 +2085,7 @@
       <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="28" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -2125,7 +2131,7 @@
         <v>14</v>
       </c>
       <c r="R5" s="9" t="str">
-        <f>IF(Q5="YES", COUNTIF($Q$2:Q5, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q5, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+        <f>IF(Q5="YES", COUNTIF($Q$2:Q5, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q5, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>2nd</v>
       </c>
       <c r="S5" s="13" t="s">
@@ -2234,7 +2240,7 @@
       <c r="DL5" s="13"/>
       <c r="DM5" s="13"/>
       <c r="DN5" s="13"/>
-      <c r="DO5" s="26"/>
+      <c r="DO5" s="25"/>
     </row>
     <row r="6" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
@@ -2244,7 +2250,7 @@
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -2290,7 +2296,7 @@
         <v>14</v>
       </c>
       <c r="R6" s="8" t="str">
-        <f>IF(Q6="YES", COUNTIF($Q$2:Q6, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q6, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+        <f>IF(Q6="YES", COUNTIF($Q$2:Q6, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q6, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>3rd</v>
       </c>
       <c r="S6" s="12" t="s">
@@ -2401,7 +2407,7 @@
       <c r="DL6" s="12"/>
       <c r="DM6" s="12"/>
       <c r="DN6" s="12"/>
-      <c r="DO6" s="26"/>
+      <c r="DO6" s="25"/>
     </row>
     <row r="7" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19">
@@ -2411,7 +2417,7 @@
       <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="28" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
@@ -2457,7 +2463,7 @@
         <v>14</v>
       </c>
       <c r="R7" s="9" t="str">
-        <f>IF(Q7="YES", COUNTIF($Q$2:Q7, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q7, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+        <f>IF(Q7="YES", COUNTIF($Q$2:Q7, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q7, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>4th</v>
       </c>
       <c r="S7" s="13" t="s">
@@ -2570,7 +2576,7 @@
       <c r="DL7" s="13"/>
       <c r="DM7" s="13"/>
       <c r="DN7" s="13"/>
-      <c r="DO7" s="26"/>
+      <c r="DO7" s="25"/>
     </row>
     <row r="8" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
@@ -2580,7 +2586,7 @@
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="29" t="s">
         <v>33</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2622,10 +2628,12 @@
         <f t="shared" si="3"/>
         <v>---</v>
       </c>
-      <c r="Q8" s="2"/>
+      <c r="Q8" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="R8" s="8" t="str">
-        <f>IF(Q8="YES", COUNTIF($Q$2:Q8, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q8, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q8="YES", COUNTIF($Q$2:Q8, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q8, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>5th</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>196</v>
@@ -2767,7 +2775,7 @@
       <c r="DL8" s="12"/>
       <c r="DM8" s="12"/>
       <c r="DN8" s="12"/>
-      <c r="DO8" s="26"/>
+      <c r="DO8" s="25"/>
     </row>
     <row r="9" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19">
@@ -2777,7 +2785,7 @@
       <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="6" t="s">
@@ -2821,8 +2829,8 @@
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="9" t="str">
-        <f>IF(Q9="YES", COUNTIF($Q$2:Q9, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q9, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q9="YES", COUNTIF($Q$2:Q9, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q9, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S9" s="13" t="s">
         <v>180</v>
@@ -2964,7 +2972,7 @@
       <c r="DL9" s="13"/>
       <c r="DM9" s="13"/>
       <c r="DN9" s="13"/>
-      <c r="DO9" s="26"/>
+      <c r="DO9" s="25"/>
     </row>
     <row r="10" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
@@ -2974,7 +2982,7 @@
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="29" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -3018,8 +3026,8 @@
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="8" t="str">
-        <f>IF(Q10="YES", COUNTIF($Q$2:Q10, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q10, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q10="YES", COUNTIF($Q$2:Q10, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q10, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S10" s="12" t="s">
         <v>181</v>
@@ -3161,7 +3169,7 @@
       <c r="DL10" s="12"/>
       <c r="DM10" s="12"/>
       <c r="DN10" s="12"/>
-      <c r="DO10" s="26"/>
+      <c r="DO10" s="25"/>
     </row>
     <row r="11" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19">
@@ -3171,7 +3179,7 @@
       <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="28" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -3215,8 +3223,8 @@
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="9" t="str">
-        <f>IF(Q11="YES", COUNTIF($Q$2:Q11, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q11, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q11="YES", COUNTIF($Q$2:Q11, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q11, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S11" s="13" t="s">
         <v>182</v>
@@ -3358,7 +3366,7 @@
       <c r="DL11" s="13"/>
       <c r="DM11" s="13"/>
       <c r="DN11" s="13"/>
-      <c r="DO11" s="26"/>
+      <c r="DO11" s="25"/>
     </row>
     <row r="12" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
@@ -3368,7 +3376,7 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="29" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -3412,8 +3420,8 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="8" t="str">
-        <f>IF(Q12="YES", COUNTIF($Q$2:Q12, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q12, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q12="YES", COUNTIF($Q$2:Q12, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q12, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S12" s="12" t="s">
         <v>183</v>
@@ -3555,7 +3563,7 @@
       <c r="DL12" s="12"/>
       <c r="DM12" s="12"/>
       <c r="DN12" s="12"/>
-      <c r="DO12" s="26"/>
+      <c r="DO12" s="25"/>
     </row>
     <row r="13" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19">
@@ -3565,7 +3573,7 @@
       <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="28" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -3609,8 +3617,8 @@
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="9" t="str">
-        <f>IF(Q13="YES", COUNTIF($Q$2:Q13, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q13, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q13="YES", COUNTIF($Q$2:Q13, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q13, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S13" s="13" t="s">
         <v>184</v>
@@ -3752,7 +3760,7 @@
       <c r="DL13" s="13"/>
       <c r="DM13" s="13"/>
       <c r="DN13" s="13"/>
-      <c r="DO13" s="26"/>
+      <c r="DO13" s="25"/>
     </row>
     <row r="14" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
@@ -3762,7 +3770,7 @@
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -3806,8 +3814,8 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="8" t="str">
-        <f>IF(Q14="YES", COUNTIF($Q$2:Q14, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q14, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q14="YES", COUNTIF($Q$2:Q14, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q14, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S14" s="12" t="s">
         <v>185</v>
@@ -3949,7 +3957,7 @@
       <c r="DL14" s="12"/>
       <c r="DM14" s="12"/>
       <c r="DN14" s="12"/>
-      <c r="DO14" s="26"/>
+      <c r="DO14" s="25"/>
     </row>
     <row r="15" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="19">
@@ -3959,7 +3967,7 @@
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="28" t="s">
         <v>45</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -4003,8 +4011,8 @@
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="9" t="str">
-        <f>IF(Q15="YES", COUNTIF($Q$2:Q15, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q15, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q15="YES", COUNTIF($Q$2:Q15, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q15, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S15" s="13" t="s">
         <v>186</v>
@@ -4146,7 +4154,7 @@
       <c r="DL15" s="13"/>
       <c r="DM15" s="13"/>
       <c r="DN15" s="13"/>
-      <c r="DO15" s="26"/>
+      <c r="DO15" s="25"/>
     </row>
     <row r="16" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
@@ -4156,7 +4164,7 @@
       <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -4200,8 +4208,8 @@
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="8" t="str">
-        <f>IF(Q16="YES", COUNTIF($Q$2:Q16, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q16, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q16="YES", COUNTIF($Q$2:Q16, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q16, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S16" s="12" t="s">
         <v>187</v>
@@ -4343,7 +4351,7 @@
       <c r="DL16" s="12"/>
       <c r="DM16" s="12"/>
       <c r="DN16" s="12"/>
-      <c r="DO16" s="26"/>
+      <c r="DO16" s="25"/>
     </row>
     <row r="17" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19">
@@ -4353,7 +4361,7 @@
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="28" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -4397,8 +4405,8 @@
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="9" t="str">
-        <f>IF(Q17="YES", COUNTIF($Q$2:Q17, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q17, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q17="YES", COUNTIF($Q$2:Q17, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q17, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S17" s="13" t="s">
         <v>188</v>
@@ -4540,7 +4548,7 @@
       <c r="DL17" s="13"/>
       <c r="DM17" s="13"/>
       <c r="DN17" s="13"/>
-      <c r="DO17" s="26"/>
+      <c r="DO17" s="25"/>
     </row>
     <row r="18" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
@@ -4550,7 +4558,7 @@
       <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -4594,8 +4602,8 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="8" t="str">
-        <f>IF(Q18="YES", COUNTIF($Q$2:Q18, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q18, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q18="YES", COUNTIF($Q$2:Q18, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q18, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S18" s="12" t="s">
         <v>189</v>
@@ -4737,7 +4745,7 @@
       <c r="DL18" s="12"/>
       <c r="DM18" s="12"/>
       <c r="DN18" s="12"/>
-      <c r="DO18" s="26"/>
+      <c r="DO18" s="25"/>
     </row>
     <row r="19" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="19">
@@ -4747,7 +4755,7 @@
       <c r="B19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="28" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -4791,8 +4799,8 @@
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="9" t="str">
-        <f>IF(Q19="YES", COUNTIF($Q$2:Q19, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q19, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q19="YES", COUNTIF($Q$2:Q19, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q19, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S19" s="13" t="s">
         <v>190</v>
@@ -4934,7 +4942,7 @@
       <c r="DL19" s="13"/>
       <c r="DM19" s="13"/>
       <c r="DN19" s="13"/>
-      <c r="DO19" s="26"/>
+      <c r="DO19" s="25"/>
     </row>
     <row r="20" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
@@ -4944,7 +4952,7 @@
       <c r="B20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="29" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -4988,8 +4996,8 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="8" t="str">
-        <f>IF(Q20="YES", COUNTIF($Q$2:Q20, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q20, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q20="YES", COUNTIF($Q$2:Q20, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q20, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S20" s="12" t="s">
         <v>189</v>
@@ -5131,7 +5139,7 @@
       <c r="DL20" s="12"/>
       <c r="DM20" s="12"/>
       <c r="DN20" s="12"/>
-      <c r="DO20" s="26"/>
+      <c r="DO20" s="25"/>
     </row>
     <row r="21" spans="1:119" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19">
@@ -5141,7 +5149,7 @@
       <c r="B21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="28" t="s">
         <v>51</v>
       </c>
       <c r="D21" s="6" t="s">
@@ -5185,8 +5193,8 @@
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="9" t="str">
-        <f>IF(Q21="YES", COUNTIF($Q$2:Q21, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q21, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
+        <f>IF(Q21="YES", COUNTIF($Q$2:Q21, "YES") &amp; CHOOSE(MIN(COUNTIF($Q$2:Q21, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
       </c>
       <c r="S21" s="13" t="s">
         <v>190</v>
@@ -5328,128 +5336,128 @@
       <c r="DL21" s="13"/>
       <c r="DM21" s="13"/>
       <c r="DN21" s="13"/>
-      <c r="DO21" s="26"/>
+      <c r="DO21" s="25"/>
     </row>
     <row r="22" spans="1:119" x14ac:dyDescent="0.35">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-      <c r="V22" s="26"/>
-      <c r="W22" s="26"/>
-      <c r="X22" s="26"/>
-      <c r="Y22" s="26"/>
-      <c r="Z22" s="26"/>
-      <c r="AA22" s="26"/>
-      <c r="AB22" s="26"/>
-      <c r="AC22" s="26"/>
-      <c r="AD22" s="26"/>
-      <c r="AE22" s="26"/>
-      <c r="AF22" s="26"/>
-      <c r="AG22" s="26"/>
-      <c r="AH22" s="26"/>
-      <c r="AI22" s="26"/>
-      <c r="AJ22" s="26"/>
-      <c r="AK22" s="26"/>
-      <c r="AL22" s="26"/>
-      <c r="AM22" s="26"/>
-      <c r="AN22" s="26"/>
-      <c r="AO22" s="26"/>
-      <c r="AP22" s="26"/>
-      <c r="AQ22" s="26"/>
-      <c r="AR22" s="26"/>
-      <c r="AS22" s="26"/>
-      <c r="AT22" s="26"/>
-      <c r="AU22" s="26"/>
-      <c r="AV22" s="26"/>
-      <c r="AW22" s="26"/>
-      <c r="AX22" s="26"/>
-      <c r="AY22" s="26"/>
-      <c r="AZ22" s="26"/>
-      <c r="BA22" s="26"/>
-      <c r="BB22" s="26"/>
-      <c r="BC22" s="26"/>
-      <c r="BD22" s="26"/>
-      <c r="BE22" s="26"/>
-      <c r="BF22" s="26"/>
-      <c r="BG22" s="26"/>
-      <c r="BH22" s="26"/>
-      <c r="BI22" s="26"/>
-      <c r="BJ22" s="26"/>
-      <c r="BK22" s="26"/>
-      <c r="BL22" s="26"/>
-      <c r="BM22" s="26"/>
-      <c r="BN22" s="26"/>
-      <c r="BO22" s="26"/>
-      <c r="BP22" s="26"/>
-      <c r="BQ22" s="26"/>
-      <c r="BR22" s="26"/>
-      <c r="BS22" s="26"/>
-      <c r="BT22" s="26"/>
-      <c r="BU22" s="26"/>
-      <c r="BV22" s="26"/>
-      <c r="BW22" s="26"/>
-      <c r="BX22" s="26"/>
-      <c r="BY22" s="26"/>
-      <c r="BZ22" s="26"/>
-      <c r="CA22" s="26"/>
-      <c r="CB22" s="26"/>
-      <c r="CC22" s="26"/>
-      <c r="CD22" s="26"/>
-      <c r="CE22" s="26"/>
-      <c r="CF22" s="26"/>
-      <c r="CG22" s="26"/>
-      <c r="CH22" s="26"/>
-      <c r="CI22" s="26"/>
-      <c r="CJ22" s="26"/>
-      <c r="CK22" s="26"/>
-      <c r="CL22" s="26"/>
-      <c r="CM22" s="26"/>
-      <c r="CN22" s="26"/>
-      <c r="CO22" s="26"/>
-      <c r="CP22" s="26"/>
-      <c r="CQ22" s="26"/>
-      <c r="CR22" s="26"/>
-      <c r="CS22" s="26"/>
-      <c r="CT22" s="26"/>
-      <c r="CU22" s="26"/>
-      <c r="CV22" s="26"/>
-      <c r="CW22" s="26"/>
-      <c r="CX22" s="26"/>
-      <c r="CY22" s="26"/>
-      <c r="CZ22" s="26"/>
-      <c r="DA22" s="26"/>
-      <c r="DB22" s="26"/>
-      <c r="DC22" s="26"/>
-      <c r="DD22" s="26"/>
-      <c r="DE22" s="26"/>
-      <c r="DF22" s="26"/>
-      <c r="DG22" s="26"/>
-      <c r="DH22" s="26"/>
-      <c r="DI22" s="26"/>
-      <c r="DJ22" s="26"/>
-      <c r="DK22" s="26"/>
-      <c r="DL22" s="26"/>
-      <c r="DM22" s="26"/>
-      <c r="DN22" s="26"/>
-      <c r="DO22" s="26"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="25"/>
+      <c r="AI22" s="25"/>
+      <c r="AJ22" s="25"/>
+      <c r="AK22" s="25"/>
+      <c r="AL22" s="25"/>
+      <c r="AM22" s="25"/>
+      <c r="AN22" s="25"/>
+      <c r="AO22" s="25"/>
+      <c r="AP22" s="25"/>
+      <c r="AQ22" s="25"/>
+      <c r="AR22" s="25"/>
+      <c r="AS22" s="25"/>
+      <c r="AT22" s="25"/>
+      <c r="AU22" s="25"/>
+      <c r="AV22" s="25"/>
+      <c r="AW22" s="25"/>
+      <c r="AX22" s="25"/>
+      <c r="AY22" s="25"/>
+      <c r="AZ22" s="25"/>
+      <c r="BA22" s="25"/>
+      <c r="BB22" s="25"/>
+      <c r="BC22" s="25"/>
+      <c r="BD22" s="25"/>
+      <c r="BE22" s="25"/>
+      <c r="BF22" s="25"/>
+      <c r="BG22" s="25"/>
+      <c r="BH22" s="25"/>
+      <c r="BI22" s="25"/>
+      <c r="BJ22" s="25"/>
+      <c r="BK22" s="25"/>
+      <c r="BL22" s="25"/>
+      <c r="BM22" s="25"/>
+      <c r="BN22" s="25"/>
+      <c r="BO22" s="25"/>
+      <c r="BP22" s="25"/>
+      <c r="BQ22" s="25"/>
+      <c r="BR22" s="25"/>
+      <c r="BS22" s="25"/>
+      <c r="BT22" s="25"/>
+      <c r="BU22" s="25"/>
+      <c r="BV22" s="25"/>
+      <c r="BW22" s="25"/>
+      <c r="BX22" s="25"/>
+      <c r="BY22" s="25"/>
+      <c r="BZ22" s="25"/>
+      <c r="CA22" s="25"/>
+      <c r="CB22" s="25"/>
+      <c r="CC22" s="25"/>
+      <c r="CD22" s="25"/>
+      <c r="CE22" s="25"/>
+      <c r="CF22" s="25"/>
+      <c r="CG22" s="25"/>
+      <c r="CH22" s="25"/>
+      <c r="CI22" s="25"/>
+      <c r="CJ22" s="25"/>
+      <c r="CK22" s="25"/>
+      <c r="CL22" s="25"/>
+      <c r="CM22" s="25"/>
+      <c r="CN22" s="25"/>
+      <c r="CO22" s="25"/>
+      <c r="CP22" s="25"/>
+      <c r="CQ22" s="25"/>
+      <c r="CR22" s="25"/>
+      <c r="CS22" s="25"/>
+      <c r="CT22" s="25"/>
+      <c r="CU22" s="25"/>
+      <c r="CV22" s="25"/>
+      <c r="CW22" s="25"/>
+      <c r="CX22" s="25"/>
+      <c r="CY22" s="25"/>
+      <c r="CZ22" s="25"/>
+      <c r="DA22" s="25"/>
+      <c r="DB22" s="25"/>
+      <c r="DC22" s="25"/>
+      <c r="DD22" s="25"/>
+      <c r="DE22" s="25"/>
+      <c r="DF22" s="25"/>
+      <c r="DG22" s="25"/>
+      <c r="DH22" s="25"/>
+      <c r="DI22" s="25"/>
+      <c r="DJ22" s="25"/>
+      <c r="DK22" s="25"/>
+      <c r="DL22" s="25"/>
+      <c r="DM22" s="25"/>
+      <c r="DN22" s="25"/>
+      <c r="DO22" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
